--- a/data.xlsx
+++ b/data.xlsx
@@ -19,9 +19,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="637" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="49">
   <si>
     <t>مكان_البانر</t>
+  </si>
+  <si>
+    <t>الاسم</t>
   </si>
   <si>
     <t>صورة</t>
@@ -30,70 +33,49 @@
     <t>القسم_المستهدف</t>
   </si>
   <si>
+    <t>مقسم_يمين</t>
+  </si>
+  <si>
+    <t>السعر الأساسي</t>
+  </si>
+  <si>
     <t>images/slider_1.jpg</t>
   </si>
   <si>
-    <t>مقسم_يمين</t>
+    <t>السعر بعد الخصم</t>
+  </si>
+  <si>
+    <t>images/split1.jpg</t>
+  </si>
+  <si>
+    <t>الوحدة</t>
+  </si>
+  <si>
+    <t>متوفر</t>
   </si>
   <si>
     <t>قسم البقالة</t>
   </si>
   <si>
+    <t>مقسم_يسار</t>
+  </si>
+  <si>
+    <t>طماطم بلدي</t>
+  </si>
+  <si>
+    <t>images/split2.jpg</t>
+  </si>
+  <si>
     <t>images/slider_2.jpg</t>
   </si>
   <si>
-    <t>images/split1.jpg</t>
+    <t>رئيسي_ثابت</t>
   </si>
   <si>
     <t>قسم المنظفات</t>
   </si>
   <si>
-    <t>مقسم_يسار</t>
-  </si>
-  <si>
-    <t>images/split2.jpg</t>
-  </si>
-  <si>
-    <t>رئيسي_ثابت</t>
-  </si>
-  <si>
     <t>images/static_banner.jpg</t>
-  </si>
-  <si>
-    <t>الاسم</t>
-  </si>
-  <si>
-    <t>رقم_الصفحة</t>
-  </si>
-  <si>
-    <t>السعر الأساسي</t>
-  </si>
-  <si>
-    <t>السعر بعد الخصم</t>
-  </si>
-  <si>
-    <t>images/offer_page_1.jpg</t>
-  </si>
-  <si>
-    <t>الوحدة</t>
-  </si>
-  <si>
-    <t>images/offer_page_2.jpg</t>
-  </si>
-  <si>
-    <t>متوفر</t>
-  </si>
-  <si>
-    <t>images/offer_page_3.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_4.jpg</t>
-  </si>
-  <si>
-    <t>طماطم بلدي</t>
-  </si>
-  <si>
-    <t>images/offer_page_5.jpg</t>
   </si>
   <si>
     <t>كيلو</t>
@@ -105,16 +87,43 @@
     <t>نعم</t>
   </si>
   <si>
+    <t>images/slider_3.jpg</t>
+  </si>
+  <si>
     <t>سكر الأسرة</t>
+  </si>
+  <si>
+    <t>قسم التسالي</t>
   </si>
   <si>
     <t>كيس</t>
   </si>
   <si>
-    <t>الإعداد</t>
+    <t>images/slider_4.jpg</t>
   </si>
   <si>
-    <t>أرز مصري</t>
+    <t>قسم الخضاروالفاكهة</t>
+  </si>
+  <si>
+    <t>رقم_الصفحة</t>
+  </si>
+  <si>
+    <t>images/offer_page_1.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_2.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_3.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_4.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_5.jpg</t>
+  </si>
+  <si>
+    <t>الإعداد</t>
   </si>
   <si>
     <t>القيمة</t>
@@ -148,6 +157,9 @@
   </si>
   <si>
     <t>images/qr_site.jpg</t>
+  </si>
+  <si>
+    <t>أرز مصري</t>
   </si>
   <si>
     <t>مسحوق غسيل</t>
@@ -207,14 +219,20 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="top"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -474,75 +492,55 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
+      <c r="A2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>8</v>
+      <c r="A3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>5</v>
+      <c r="A4" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>8</v>
+      <c r="A5" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B6" s="2"/>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="B7" s="2"/>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>5</v>
-      </c>
+      <c r="B8" s="2"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>8</v>
-      </c>
+      <c r="B9" s="2"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -1549,31 +1547,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>10</v>
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
+      <c r="A4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2582,442 +2580,442 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="B2" s="3">
+        <v>22.0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
+      <c r="F2" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B2" s="2">
-        <v>22.0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B3" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B3" s="2">
-        <v>40.0</v>
-      </c>
-      <c r="C3" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>27</v>
+      <c r="E3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F4" s="1" t="s">
+      <c r="B5" s="3">
+        <v>58.0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="F5" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="2">
-        <v>58.0</v>
-      </c>
-      <c r="C5" s="2">
-        <v>53.0</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B6" s="3">
+        <v>76.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>71.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B6" s="2">
-        <v>76.0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>71.0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
+      <c r="E6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F7" s="1" t="s">
+      <c r="B8" s="3">
+        <v>94.0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>89.0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
+      <c r="F8" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="2">
-        <v>94.0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>89.0</v>
-      </c>
-      <c r="D8" s="3" t="s">
+      <c r="B9" s="3">
+        <v>112.0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>107.0</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B9" s="2">
-        <v>112.0</v>
-      </c>
-      <c r="C9" s="2">
-        <v>107.0</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>27</v>
+      <c r="E9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F10" s="1" t="s">
+      <c r="B11" s="3">
+        <v>130.0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>125.0</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
+      <c r="F11" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B11" s="2">
-        <v>130.0</v>
-      </c>
-      <c r="C11" s="2">
-        <v>125.0</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="B12" s="3">
+        <v>148.0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>143.0</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B12" s="2">
-        <v>148.0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>143.0</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>27</v>
+      <c r="E12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1" t="s">
+      <c r="B14" s="3">
+        <v>166.0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>161.0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="F14" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="2">
-        <v>166.0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>161.0</v>
-      </c>
-      <c r="D14" s="3" t="s">
+      <c r="B15" s="3">
+        <v>184.0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>179.0</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="2">
-        <v>184.0</v>
-      </c>
-      <c r="C15" s="2">
-        <v>179.0</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>27</v>
+      <c r="E15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F16" s="1" t="s">
+      <c r="B17" s="3">
+        <v>58.0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>53.0</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
+      <c r="F17" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B17" s="2">
-        <v>58.0</v>
-      </c>
-      <c r="C17" s="2">
-        <v>53.0</v>
-      </c>
-      <c r="D17" s="3" t="s">
+      <c r="B18" s="3">
+        <v>76.0</v>
+      </c>
+      <c r="C18" s="3">
+        <v>71.0</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="2">
-        <v>76.0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>71.0</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>27</v>
+      <c r="E18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F19" s="1" t="s">
+      <c r="B20" s="3">
+        <v>94.0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>89.0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
+      <c r="F20" s="2" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2">
-        <v>94.0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>89.0</v>
-      </c>
-      <c r="D20" s="3" t="s">
+      <c r="B21" s="3">
+        <v>112.0</v>
+      </c>
+      <c r="C21" s="3">
+        <v>107.0</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B21" s="2">
-        <v>112.0</v>
-      </c>
-      <c r="C21" s="2">
-        <v>107.0</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>27</v>
+      <c r="E21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1"/>
@@ -4020,50 +4018,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1.0</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>17</v>
+      <c r="B2" s="3" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2">
+      <c r="A3" s="3">
         <v>2.0</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>19</v>
+      <c r="B3" s="3" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3.0</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>21</v>
+      <c r="B4" s="3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2">
+      <c r="A5" s="3">
         <v>4.0</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>22</v>
+      <c r="B5" s="3" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5.0</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>24</v>
+      <c r="B6" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5068,50 +5066,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>34</v>
+      <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>36</v>
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>38</v>
+      <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>40</v>
+      <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>42</v>
+      <c r="A6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6114,503 +6112,503 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>27</v>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>27</v>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3">
+        <v>37.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2">
-        <v>37.0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3">
+        <v>38.0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="2">
-        <v>38.0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3">
+        <v>39.0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="2">
-        <v>39.0</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2">
-        <v>40.0</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>27</v>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="3">
+        <v>41.0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="2">
-        <v>41.0</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>27</v>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="2">
-        <v>42.0</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>27</v>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="3">
+        <v>43.0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="2">
-        <v>43.0</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>27</v>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="3">
+        <v>44.0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="2">
-        <v>44.0</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>27</v>
+      <c r="F20" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="3">
+        <v>45.0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>27</v>
+      <c r="F22" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46.0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="2">
-        <v>46.0</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>27</v>
+      <c r="F24" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="3">
+        <v>47.0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="2">
-        <v>47.0</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>27</v>
+      <c r="F26" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1"/>
@@ -7606,483 +7604,483 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="3">
+        <v>35.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B2" s="2">
-        <v>35.0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>27</v>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B4" s="3">
+        <v>36.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B4" s="2">
-        <v>36.0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>27</v>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6" s="3">
+        <v>37.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B6" s="2">
-        <v>37.0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B8" s="3">
+        <v>38.0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B8" s="2">
-        <v>38.0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3">
+        <v>39.0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B10" s="2">
-        <v>39.0</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B12" s="3">
+        <v>40.0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="2">
-        <v>40.0</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>27</v>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="3">
+        <v>41.0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="2">
-        <v>41.0</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>27</v>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B16" s="3">
+        <v>42.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B16" s="2">
-        <v>42.0</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>27</v>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B18" s="3">
+        <v>43.0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B18" s="2">
-        <v>43.0</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>27</v>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B20" s="3">
+        <v>44.0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="2">
-        <v>44.0</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>27</v>
+      <c r="F20" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B22" s="3">
+        <v>45.0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B22" s="2">
-        <v>45.0</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>27</v>
+      <c r="F22" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B24" s="3">
+        <v>46.0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="2">
-        <v>46.0</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>27</v>
+      <c r="F24" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B26" s="3">
+        <v>47.0</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B26" s="2">
-        <v>47.0</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>27</v>
+      <c r="F26" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -9085,502 +9083,502 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="3">
+        <v>250.0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="2">
-        <v>250.0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>220.0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>27</v>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="3">
+        <v>251.0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>221.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="2">
-        <v>251.0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>221.0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>27</v>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="3">
+        <v>252.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>222.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="2">
-        <v>252.0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>222.0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3">
+        <v>253.0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>223.0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2">
-        <v>253.0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>223.0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3">
+        <v>254.0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>224.0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2">
-        <v>254.0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>224.0</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="3">
+        <v>255.0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>225.0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2">
-        <v>255.0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>225.0</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>27</v>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="3">
+        <v>256.0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>226.0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="2">
-        <v>256.0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>226.0</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>27</v>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="3">
+        <v>257.0</v>
+      </c>
+      <c r="C16" s="3">
+        <v>227.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2">
-        <v>257.0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>227.0</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>27</v>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="3">
+        <v>258.0</v>
+      </c>
+      <c r="C18" s="3">
+        <v>228.0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="2">
-        <v>258.0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>228.0</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>27</v>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="3">
+        <v>259.0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>229.0</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B20" s="2">
-        <v>259.0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>229.0</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>27</v>
+      <c r="F20" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F21" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="3">
+        <v>260.0</v>
+      </c>
+      <c r="C22" s="3">
+        <v>230.0</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E22" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B22" s="2">
-        <v>260.0</v>
-      </c>
-      <c r="C22" s="2">
-        <v>230.0</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>27</v>
+      <c r="F22" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="3">
+        <v>261.0</v>
+      </c>
+      <c r="C24" s="3">
+        <v>231.0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="2">
-        <v>261.0</v>
-      </c>
-      <c r="C24" s="2">
-        <v>231.0</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>27</v>
+      <c r="F24" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1"/>
@@ -10584,382 +10582,382 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="3">
+        <v>250.0</v>
+      </c>
+      <c r="C2" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B2" s="2">
-        <v>250.0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>220.0</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>27</v>
+      <c r="F2" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="3">
+        <v>251.0</v>
+      </c>
+      <c r="C4" s="3">
+        <v>221.0</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B4" s="2">
-        <v>251.0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>221.0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>27</v>
+      <c r="F4" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F5" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="3">
+        <v>252.0</v>
+      </c>
+      <c r="C6" s="3">
+        <v>222.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B6" s="2">
-        <v>252.0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>222.0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>27</v>
+      <c r="F6" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F7" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="3">
+        <v>253.0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>223.0</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B8" s="2">
-        <v>253.0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>223.0</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>27</v>
+      <c r="F8" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F9" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="3">
+        <v>254.0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>224.0</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E10" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="2">
-        <v>254.0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>224.0</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>27</v>
+      <c r="F10" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="3">
+        <v>255.0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>225.0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B12" s="2">
-        <v>255.0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>225.0</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>27</v>
+      <c r="F12" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="3">
+        <v>256.0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>226.0</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B14" s="2">
-        <v>256.0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>226.0</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>27</v>
+      <c r="F14" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F15" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="3">
+        <v>257.0</v>
+      </c>
+      <c r="C16" s="3">
+        <v>227.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E16" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B16" s="2">
-        <v>257.0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>227.0</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>27</v>
+      <c r="F16" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="3">
+        <v>258.0</v>
+      </c>
+      <c r="C18" s="3">
+        <v>228.0</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E18" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B18" s="2">
-        <v>258.0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>228.0</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>27</v>
+      <c r="F18" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -19,33 +19,33 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="50">
   <si>
-    <t>مكان_البانر</t>
+    <t>صورة</t>
   </si>
   <si>
     <t>الاسم</t>
   </si>
   <si>
-    <t>صورة</t>
-  </si>
-  <si>
     <t>القسم_المستهدف</t>
   </si>
   <si>
-    <t>مقسم_يمين</t>
+    <t>مكان_البانر</t>
+  </si>
+  <si>
+    <t>رقم_الصفحة</t>
+  </si>
+  <si>
+    <t>images/slider_ (1).jpg</t>
   </si>
   <si>
     <t>السعر الأساسي</t>
   </si>
   <si>
-    <t>images/slider_1.jpg</t>
-  </si>
-  <si>
     <t>السعر بعد الخصم</t>
   </si>
   <si>
-    <t>images/split1.jpg</t>
+    <t>قسم البقالة</t>
   </si>
   <si>
     <t>الوحدة</t>
@@ -54,73 +54,76 @@
     <t>متوفر</t>
   </si>
   <si>
-    <t>قسم البقالة</t>
+    <t>images/slider_ (2).jpg</t>
+  </si>
+  <si>
+    <t>مقسم_يمين</t>
+  </si>
+  <si>
+    <t>قسم قهوة</t>
+  </si>
+  <si>
+    <t>طماطم بلدي</t>
+  </si>
+  <si>
+    <t>images/split1.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_1.jpg</t>
   </si>
   <si>
     <t>مقسم_يسار</t>
   </si>
   <si>
-    <t>طماطم بلدي</t>
-  </si>
-  <si>
     <t>images/split2.jpg</t>
   </si>
   <si>
-    <t>images/slider_2.jpg</t>
+    <t>images/offer_page_2.jpg</t>
+  </si>
+  <si>
+    <t>images/slider_ (3).jpg</t>
+  </si>
+  <si>
+    <t>كيلو</t>
   </si>
   <si>
     <t>رئيسي_ثابت</t>
   </si>
   <si>
-    <t>قسم المنظفات</t>
+    <t>قسم برتقان</t>
+  </si>
+  <si>
+    <t>images/placeholder.png</t>
+  </si>
+  <si>
+    <t>images/offer_page_3.jpg</t>
   </si>
   <si>
     <t>images/static_banner.jpg</t>
   </si>
   <si>
-    <t>كيلو</t>
-  </si>
-  <si>
-    <t>images/placeholder.png</t>
+    <t>images/slider_ (4).jpg</t>
   </si>
   <si>
     <t>نعم</t>
   </si>
   <si>
-    <t>images/slider_3.jpg</t>
+    <t>قسم تسالي</t>
+  </si>
+  <si>
+    <t>images/offer_page_4.jpg</t>
   </si>
   <si>
     <t>سكر الأسرة</t>
   </si>
   <si>
-    <t>قسم التسالي</t>
+    <t>images/offer_page_5.jpg</t>
+  </si>
+  <si>
+    <t>images/slider_ (5).jpg</t>
   </si>
   <si>
     <t>كيس</t>
-  </si>
-  <si>
-    <t>images/slider_4.jpg</t>
-  </si>
-  <si>
-    <t>قسم الخضاروالفاكهة</t>
-  </si>
-  <si>
-    <t>رقم_الصفحة</t>
-  </si>
-  <si>
-    <t>images/offer_page_1.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_2.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_3.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_4.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_5.jpg</t>
   </si>
   <si>
     <t>الإعداد</t>
@@ -229,10 +232,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -485,62 +488,67 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="17.71"/>
+    <col customWidth="1" min="1" max="1" width="19.57"/>
     <col customWidth="1" min="2" max="2" width="14.43"/>
     <col customWidth="1" min="3" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="A2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>17</v>
+      <c r="B3" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>22</v>
+      <c r="A4" s="2" t="s">
+        <v>20</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>26</v>
+      <c r="A5" s="2" t="s">
+        <v>27</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="7">
-      <c r="B7" s="2"/>
+      <c r="B7" s="3"/>
     </row>
     <row r="8">
-      <c r="B8" s="2"/>
+      <c r="B8" s="3"/>
     </row>
     <row r="9">
-      <c r="B9" s="2"/>
+      <c r="B9" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -1544,34 +1552,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>8</v>
+      <c r="A2" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
+      <c r="A3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>18</v>
+      <c r="A4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2583,7 +2591,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -2592,50 +2600,50 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="4">
         <v>22.0</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>17.0</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="3">
+      <c r="A3" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B3" s="4">
         <v>40.0</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="4">
         <v>35.0</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>21</v>
+      <c r="D3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="4">
@@ -2643,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>7</v>
@@ -2652,50 +2660,50 @@
         <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="4">
         <v>58.0</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="4">
         <v>53.0</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="D5" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="E5" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" s="4">
         <v>76.0</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>71.0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
+      <c r="D6" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -2703,7 +2711,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -2712,50 +2720,50 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="4">
         <v>94.0</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>89.0</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="3">
+      <c r="A9" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="4">
         <v>112.0</v>
       </c>
-      <c r="C9" s="3">
+      <c r="C9" s="4">
         <v>107.0</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>21</v>
+      <c r="D9" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="10">
@@ -2763,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>7</v>
@@ -2772,50 +2780,50 @@
         <v>9</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="3">
+      <c r="A11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="4">
         <v>130.0</v>
       </c>
-      <c r="C11" s="3">
+      <c r="C11" s="4">
         <v>125.0</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="E11" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="4">
         <v>148.0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>143.0</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>21</v>
+      <c r="D12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -2823,7 +2831,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
@@ -2832,50 +2840,50 @@
         <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B14" s="4">
         <v>166.0</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>161.0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B15" s="3">
+      <c r="A15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="4">
         <v>184.0</v>
       </c>
-      <c r="C15" s="3">
+      <c r="C15" s="4">
         <v>179.0</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>21</v>
+      <c r="D15" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="16">
@@ -2883,7 +2891,7 @@
         <v>1</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>7</v>
@@ -2892,50 +2900,50 @@
         <v>9</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="3">
+      <c r="A17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B17" s="4">
         <v>58.0</v>
       </c>
-      <c r="C17" s="3">
+      <c r="C17" s="4">
         <v>53.0</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F17" s="2" t="s">
+      <c r="D17" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="E17" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B18" s="4">
         <v>76.0</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <v>71.0</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>21</v>
+      <c r="D18" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -2943,7 +2951,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
@@ -2952,50 +2960,50 @@
         <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B20" s="4">
         <v>94.0</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>89.0</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>21</v>
       </c>
+      <c r="E20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>28</v>
+      </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="B21" s="3">
+      <c r="A21" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" s="4">
         <v>112.0</v>
       </c>
-      <c r="C21" s="3">
+      <c r="C21" s="4">
         <v>107.0</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>21</v>
+      <c r="D21" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -3003,7 +3011,7 @@
         <v>1</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>7</v>
@@ -3012,7 +3020,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>10</v>
@@ -4018,50 +4026,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>28</v>
+        <v>4</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1.0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>29</v>
+      <c r="B2" s="4" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
+      <c r="A3" s="4">
         <v>2.0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6">
+      <c r="A6" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>32</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5066,50 +5074,50 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="A2" s="3" t="s">
         <v>37</v>
       </c>
+      <c r="B2" s="4" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="A3" s="3" t="s">
         <v>39</v>
       </c>
+      <c r="B3" s="4" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="A4" s="3" t="s">
         <v>41</v>
       </c>
+      <c r="B4" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
+      <c r="B5" s="4" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="A6" s="3" t="s">
         <v>45</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6115,7 +6123,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -6124,27 +6132,27 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4">
         <v>35.0</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -6152,7 +6160,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -6161,27 +6169,27 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="4">
         <v>36.0</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -6189,7 +6197,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -6198,27 +6206,27 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4">
         <v>37.0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -6226,7 +6234,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -6235,27 +6243,27 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="4">
         <v>38.0</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -6263,7 +6271,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
@@ -6272,27 +6280,27 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4">
         <v>39.0</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -6300,7 +6308,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -6309,27 +6317,27 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="4">
         <v>40.0</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -6337,7 +6345,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
@@ -6346,27 +6354,27 @@
         <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4">
         <v>41.0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -6374,7 +6382,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -6383,27 +6391,27 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="A16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="4">
         <v>42.0</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -6411,7 +6419,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
@@ -6420,27 +6428,27 @@
         <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="4">
         <v>43.0</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -6448,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
@@ -6457,27 +6465,27 @@
         <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="4">
         <v>44.0</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -6485,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>7</v>
@@ -6494,27 +6502,27 @@
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="4">
         <v>45.0</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -6522,7 +6530,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>7</v>
@@ -6531,27 +6539,27 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="4">
         <v>46.0</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -6559,7 +6567,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -6568,27 +6576,27 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="3">
+      <c r="A26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="4">
         <v>47.0</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -6596,7 +6604,7 @@
         <v>1</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>7</v>
@@ -6605,7 +6613,7 @@
         <v>9</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F27" s="1" t="s">
         <v>10</v>
@@ -7607,7 +7615,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -7616,27 +7624,27 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B2" s="4">
         <v>35.0</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -7644,7 +7652,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -7653,27 +7661,27 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="4">
         <v>36.0</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="D4" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -7681,7 +7689,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -7690,27 +7698,27 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B6" s="4">
         <v>37.0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
+      <c r="D6" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -7718,7 +7726,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -7727,27 +7735,27 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B8" s="4">
         <v>38.0</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -7755,7 +7763,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
@@ -7764,27 +7772,27 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B10" s="4">
         <v>39.0</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -7792,7 +7800,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -7801,27 +7809,27 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12" s="4">
         <v>40.0</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -7829,7 +7837,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
@@ -7838,27 +7846,27 @@
         <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" s="4">
         <v>41.0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -7866,7 +7874,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -7875,27 +7883,27 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="A16" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B16" s="4">
         <v>42.0</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -7903,7 +7911,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
@@ -7912,27 +7920,27 @@
         <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B18" s="4">
         <v>43.0</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="s">
+      <c r="D18" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -7940,7 +7948,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
@@ -7949,27 +7957,27 @@
         <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B20" s="4">
         <v>44.0</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="D20" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -7977,7 +7985,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>7</v>
@@ -7986,27 +7994,27 @@
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="4">
         <v>45.0</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="2" t="s">
+      <c r="D22" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -8014,7 +8022,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>7</v>
@@ -8023,27 +8031,27 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="A24" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="4">
         <v>46.0</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2" t="s">
+      <c r="D24" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -8051,7 +8059,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -8060,27 +8068,27 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="3">
+      <c r="A26" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B26" s="4">
         <v>47.0</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F26" s="2" t="s">
+      <c r="D26" s="3" t="s">
         <v>21</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1"/>
@@ -9086,7 +9094,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -9095,30 +9103,30 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="4">
         <v>250.0</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>220.0</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -9126,7 +9134,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -9135,30 +9143,30 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="4">
         <v>251.0</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>221.0</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
+      <c r="D4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -9166,7 +9174,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -9175,30 +9183,30 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4">
         <v>252.0</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>222.0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -9206,7 +9214,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -9215,30 +9223,30 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4">
         <v>253.0</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>223.0</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>21</v>
+      <c r="D8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -9246,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
@@ -9255,30 +9263,30 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="4">
         <v>254.0</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>224.0</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>21</v>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -9286,7 +9294,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -9295,30 +9303,30 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="4">
         <v>255.0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>225.0</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>21</v>
+      <c r="D12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -9326,7 +9334,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
@@ -9335,30 +9343,30 @@
         <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="4">
         <v>256.0</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>226.0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>21</v>
+      <c r="D14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -9366,7 +9374,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -9375,30 +9383,30 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="A16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="4">
         <v>257.0</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="4">
         <v>227.0</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>21</v>
+      <c r="D16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -9406,7 +9414,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
@@ -9415,30 +9423,30 @@
         <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="4">
         <v>258.0</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <v>228.0</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>21</v>
+      <c r="D18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -9446,7 +9454,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
@@ -9455,30 +9463,30 @@
         <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B20" s="3">
+      <c r="A20" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B20" s="4">
         <v>259.0</v>
       </c>
-      <c r="C20" s="3">
+      <c r="C20" s="4">
         <v>229.0</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>21</v>
+      <c r="D20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -9486,7 +9494,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>7</v>
@@ -9495,30 +9503,30 @@
         <v>9</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B22" s="3">
+      <c r="A22" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B22" s="4">
         <v>260.0</v>
       </c>
-      <c r="C22" s="3">
+      <c r="C22" s="4">
         <v>230.0</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>21</v>
+      <c r="D22" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -9526,7 +9534,7 @@
         <v>1</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>7</v>
@@ -9535,30 +9543,30 @@
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="3">
+      <c r="A24" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="4">
         <v>261.0</v>
       </c>
-      <c r="C24" s="3">
+      <c r="C24" s="4">
         <v>231.0</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>21</v>
+      <c r="D24" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -9566,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>7</v>
@@ -9575,7 +9583,7 @@
         <v>9</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F25" s="1" t="s">
         <v>10</v>
@@ -10585,7 +10593,7 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>7</v>
@@ -10594,30 +10602,30 @@
         <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B2" s="3">
+      <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B2" s="4">
         <v>250.0</v>
       </c>
-      <c r="C2" s="3">
+      <c r="C2" s="4">
         <v>220.0</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>21</v>
+      <c r="D2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -10625,7 +10633,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>7</v>
@@ -10634,30 +10642,30 @@
         <v>9</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B4" s="3">
+      <c r="A4" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="4">
         <v>251.0</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="4">
         <v>221.0</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>21</v>
+      <c r="D4" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="5">
@@ -10665,7 +10673,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>7</v>
@@ -10674,30 +10682,30 @@
         <v>9</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B6" s="3">
+      <c r="A6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" s="4">
         <v>252.0</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="4">
         <v>222.0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>21</v>
+      <c r="D6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="7">
@@ -10705,7 +10713,7 @@
         <v>1</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>7</v>
@@ -10714,30 +10722,30 @@
         <v>9</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B8" s="3">
+      <c r="A8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="4">
         <v>253.0</v>
       </c>
-      <c r="C8" s="3">
+      <c r="C8" s="4">
         <v>223.0</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>21</v>
+      <c r="D8" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="9">
@@ -10745,7 +10753,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>7</v>
@@ -10754,30 +10762,30 @@
         <v>9</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="3">
+      <c r="A10" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" s="4">
         <v>254.0</v>
       </c>
-      <c r="C10" s="3">
+      <c r="C10" s="4">
         <v>224.0</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>21</v>
+      <c r="D10" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="11">
@@ -10785,7 +10793,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>7</v>
@@ -10794,30 +10802,30 @@
         <v>9</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B12" s="3">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="4">
         <v>255.0</v>
       </c>
-      <c r="C12" s="3">
+      <c r="C12" s="4">
         <v>225.0</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>21</v>
+      <c r="D12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="13">
@@ -10825,7 +10833,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>7</v>
@@ -10834,30 +10842,30 @@
         <v>9</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B14" s="3">
+      <c r="A14" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B14" s="4">
         <v>256.0</v>
       </c>
-      <c r="C14" s="3">
+      <c r="C14" s="4">
         <v>226.0</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>21</v>
+      <c r="D14" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="15">
@@ -10865,7 +10873,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>7</v>
@@ -10874,30 +10882,30 @@
         <v>9</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B16" s="3">
+      <c r="A16" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B16" s="4">
         <v>257.0</v>
       </c>
-      <c r="C16" s="3">
+      <c r="C16" s="4">
         <v>227.0</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>21</v>
+      <c r="D16" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="17">
@@ -10905,7 +10913,7 @@
         <v>1</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>7</v>
@@ -10914,30 +10922,30 @@
         <v>9</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="1" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B18" s="3">
+      <c r="A18" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="4">
         <v>258.0</v>
       </c>
-      <c r="C18" s="3">
+      <c r="C18" s="4">
         <v>228.0</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>21</v>
+      <c r="D18" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="19">
@@ -10945,7 +10953,7 @@
         <v>1</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>7</v>
@@ -10954,7 +10962,7 @@
         <v>9</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>10</v>

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,15 +12,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="عروض اليوم" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="مجلة العروض" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الإعدادات" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفاكهة والخضار" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="اللحوم والدواجن" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الألبان والبيض" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المخبوزات" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="البقالة" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المشروبات" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التسالي والمكسرات" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المنظفات" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="العناية الشخصية" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الفواكه والخضروات" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التسالي والمكسرات" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المشروبات" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="البقالة" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الألبان" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="المخبوزات" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="التوابل والبهارات" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="الحلويات والكاندي" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="منظفات" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -438,7 +438,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B3"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,7 +461,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>البقالة</t>
+          <t>الفواكه والخضروات</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,91 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>المنظفات</t>
+          <t>التسالي والمكسرات</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>images/slider_1.jpg</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>المشروبات</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>images/slider_2.jpg</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>البقالة</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>images/slider_1.jpg</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>الألبان</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>images/slider_2.jpg</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>المخبوزات</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>images/slider_1.jpg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>التوابل والبهارات</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>images/slider_2.jpg</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>الحلويات والكاندي</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>images/slider_1.jpg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>منظفات</t>
         </is>
       </c>
     </row>
@@ -526,15 +610,13 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>أرز</t>
+          <t>لبن كامل الدسم</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>147</v>
-      </c>
-      <c r="C2" t="n">
-        <v>143</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -554,18 +636,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>مكرونة</t>
+          <t>جبنة بيضاء</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41</v>
-      </c>
-      <c r="C3" t="n">
-        <v>35</v>
-      </c>
+        <v>168</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -582,18 +662,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>سكر</t>
+          <t>جبنة رومي</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="C4" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -610,18 +690,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>زيت</t>
+          <t>زبادي</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>38</v>
-      </c>
-      <c r="C5" t="n">
-        <v>30</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -638,18 +716,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>سمنة</t>
+          <t>قشطة</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>160</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>153</v>
+        <v>27</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -666,15 +744,13 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>صلصة</t>
+          <t>زبدة</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73</v>
-      </c>
-      <c r="C7" t="n">
-        <v>70</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -694,16 +770,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>تونة</t>
+          <t>جبنة شيدر</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>173</v>
+        <v>248</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -720,16 +796,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>فول</t>
+          <t>جبنة نستو</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>153</v>
+        <v>129</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -746,18 +822,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>عدس</t>
+          <t>لبن رايب</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>59</v>
+        <v>114</v>
       </c>
       <c r="C10" t="n">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -774,14 +850,14 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>دقيق</t>
+          <t>سمن بلدي</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>66</v>
+        <v>192</v>
       </c>
       <c r="C11" t="n">
-        <v>61</v>
+        <v>186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -802,16 +878,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>أرز (11)</t>
+          <t>لبن كامل الدسم (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49</v>
+        <v>150</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -828,16 +904,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>مكرونة (12)</t>
+          <t>جبنة بيضاء (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>117</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="C13" t="n">
+        <v>144</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -854,11 +932,11 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>سكر (13)</t>
+          <t>جبنة رومي (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>204</v>
+        <v>46</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
@@ -880,11 +958,11 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>زيت (14)</t>
+          <t>زبادي (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>94</v>
+        <v>215</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
@@ -906,18 +984,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>سمنة (15)</t>
+          <t>قشطة (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>237</v>
-      </c>
-      <c r="C16" t="n">
-        <v>227</v>
-      </c>
+        <v>233</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -934,18 +1010,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>صلصة (16)</t>
+          <t>زبدة (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>54</v>
-      </c>
-      <c r="C17" t="n">
-        <v>45</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -962,16 +1036,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>تونة (17)</t>
+          <t>جبنة شيدر (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -988,11 +1062,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>فول (18)</t>
+          <t>جبنة نستو (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>60</v>
+        <v>235</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
@@ -1014,16 +1088,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>عدس (19)</t>
+          <t>لبن رايب (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>169</v>
+        <v>188</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1040,18 +1114,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>دقيق (20)</t>
+          <t>سمن بلدي (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>148</v>
-      </c>
-      <c r="C21" t="n">
-        <v>146</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1068,18 +1140,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>أرز (21)</t>
+          <t>لبن كامل الدسم (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>189</v>
+        <v>81</v>
       </c>
       <c r="C22" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1096,16 +1168,18 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>مكرونة (22)</t>
+          <t>جبنة بيضاء (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>130</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>145</v>
+      </c>
+      <c r="C23" t="n">
+        <v>137</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1122,16 +1196,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>سكر (23)</t>
+          <t>جبنة رومي (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>65</v>
+        <v>208</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1148,18 +1222,18 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>زيت (24)</t>
+          <t>زبادي (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>128</v>
+        <v>204</v>
       </c>
       <c r="C25" t="n">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1176,13 +1250,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>سمنة (25)</t>
+          <t>قشطة (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>152</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>159</v>
+      </c>
+      <c r="C26" t="n">
+        <v>156</v>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -1202,16 +1278,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>صلصة (26)</t>
+          <t>زبدة (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1228,15 +1304,13 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>تونة (27)</t>
+          <t>جبنة شيدر (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>231</v>
-      </c>
-      <c r="C28" t="n">
-        <v>228</v>
-      </c>
+        <v>80</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -1256,16 +1330,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>فول (28)</t>
+          <t>جبنة نستو (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>50</v>
+        <v>129</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1282,16 +1356,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>عدس (29)</t>
+          <t>لبن رايب (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>242</v>
+        <v>109</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1308,18 +1382,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>دقيق (30)</t>
+          <t>سمن بلدي (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>230</v>
+        <v>92</v>
       </c>
       <c r="C31" t="n">
-        <v>221</v>
+        <v>87</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1382,16 +1456,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>شاي</t>
+          <t>عيش فينو</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -1408,16 +1482,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>قهوة</t>
+          <t>عيش بلدي</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>18</v>
+      </c>
+      <c r="C3" t="n">
+        <v>9</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1434,16 +1510,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>نسكافيه</t>
+          <t>باتيه</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>122</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>36</v>
+      </c>
+      <c r="C4" t="n">
+        <v>29</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1460,16 +1538,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>عصير برتقال</t>
+          <t>كرواسون</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1486,18 +1564,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>عصير تفاح</t>
+          <t>بقسماط</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>108</v>
+        <v>64</v>
       </c>
       <c r="C6" t="n">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1514,18 +1592,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>كولا</t>
+          <t>توست أبيض</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>41</v>
+        <v>200</v>
       </c>
       <c r="C7" t="n">
-        <v>35</v>
+        <v>193</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1542,16 +1620,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>مياه معدنية</t>
+          <t>توست أسمر</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>234</v>
+      </c>
+      <c r="C8" t="n">
+        <v>227</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1568,16 +1648,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>مشروب طاقة</t>
+          <t>فطير</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>111</v>
+        <v>91</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1594,13 +1674,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>كاكاو</t>
+          <t>كيك</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>223</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>122</v>
+      </c>
+      <c r="C10" t="n">
+        <v>112</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -1620,11 +1702,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>نعناع</t>
+          <t>بسكويت</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>162</v>
+        <v>62</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
@@ -1646,14 +1728,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>شاي (11)</t>
+          <t>عيش فينو (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>175</v>
+        <v>205</v>
       </c>
       <c r="C12" t="n">
-        <v>173</v>
+        <v>196</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1674,16 +1756,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>قهوة (12)</t>
+          <t>عيش بلدي (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>97</v>
+        <v>192</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1700,16 +1782,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>نسكافيه (13)</t>
+          <t>باتيه (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1726,15 +1808,13 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>عصير برتقال (14)</t>
+          <t>كرواسون (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>239</v>
-      </c>
-      <c r="C15" t="n">
-        <v>237</v>
-      </c>
+        <v>246</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -1754,16 +1834,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>عصير تفاح (15)</t>
+          <t>بقسماط (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>108</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="C16" t="n">
+        <v>25</v>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1780,16 +1862,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>كولا (16)</t>
+          <t>توست أبيض (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>185</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>198</v>
+      </c>
+      <c r="C17" t="n">
+        <v>190</v>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1806,18 +1890,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>مياه معدنية (17)</t>
+          <t>توست أسمر (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>117</v>
-      </c>
-      <c r="C18" t="n">
-        <v>114</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1834,16 +1916,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>مشروب طاقة (18)</t>
+          <t>فطير (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>230</v>
+        <v>178</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1860,18 +1942,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>كاكاو (19)</t>
+          <t>كيك (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29</v>
-      </c>
-      <c r="C20" t="n">
-        <v>23</v>
-      </c>
+        <v>112</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1888,18 +1968,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>نعناع (20)</t>
+          <t>بسكويت (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>204</v>
-      </c>
-      <c r="C21" t="n">
-        <v>195</v>
-      </c>
+        <v>89</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1916,16 +1994,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>شاي (21)</t>
+          <t>عيش فينو (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1942,11 +2020,11 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>قهوة (22)</t>
+          <t>عيش بلدي (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>143</v>
+        <v>82</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
@@ -1968,16 +2046,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>نسكافيه (23)</t>
+          <t>باتيه (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>124</v>
+        <v>73</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1994,11 +2072,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>عصير برتقال (24)</t>
+          <t>كرواسون (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>222</v>
+        <v>100</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
@@ -2020,16 +2098,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>عصير تفاح (25)</t>
+          <t>بقسماط (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>171</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>37</v>
+      </c>
+      <c r="C26" t="n">
+        <v>34</v>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2046,11 +2126,11 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>كولا (26)</t>
+          <t>توست أبيض (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>182</v>
+        <v>132</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
@@ -2072,18 +2152,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>مياه معدنية (27)</t>
+          <t>توست أسمر (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>49</v>
-      </c>
-      <c r="C28" t="n">
-        <v>39</v>
-      </c>
+        <v>217</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2100,15 +2178,13 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>مشروب طاقة (28)</t>
+          <t>فطير (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>181</v>
-      </c>
-      <c r="C29" t="n">
-        <v>173</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -2128,11 +2204,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>كاكاو (29)</t>
+          <t>كيك (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>190</v>
+        <v>249</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
@@ -2154,11 +2230,11 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>نعناع (30)</t>
+          <t>بسكويت (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
@@ -2226,18 +2302,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>لب سوبر</t>
+          <t>كمون</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81</v>
+        <v>136</v>
       </c>
       <c r="C2" t="n">
-        <v>76</v>
+        <v>126</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2254,14 +2330,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>لب سوري</t>
+          <t>فلفل أسود</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>53</v>
+        <v>95</v>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2282,11 +2358,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>سوداني</t>
+          <t>كركم</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>167</v>
+        <v>206</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -2308,18 +2384,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>لوز</t>
+          <t>كزبرة</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>117</v>
-      </c>
-      <c r="C5" t="n">
-        <v>112</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2336,11 +2410,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>عين جمل</t>
+          <t>بهارات مشكلة</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70</v>
+        <v>142</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
@@ -2362,16 +2436,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>كاجو</t>
+          <t>قرفة</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>194</v>
+        <v>114</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2388,16 +2462,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>شيبسي</t>
+          <t>حبهان</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>239</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="C8" t="n">
+        <v>67</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2414,13 +2490,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>فشار</t>
+          <t>ورق لورا</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>224</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>119</v>
+      </c>
+      <c r="C9" t="n">
+        <v>110</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -2440,13 +2518,15 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>مقرمشات</t>
+          <t>بابريكا</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>197</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>205</v>
+      </c>
+      <c r="C10" t="n">
+        <v>198</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -2466,16 +2546,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>فستق</t>
+          <t>قرنفل</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>147</v>
+        <v>212</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2492,16 +2572,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>لب سوبر (11)</t>
+          <t>كمون (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>197</v>
+        <v>163</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -2518,13 +2598,15 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>لب سوري (12)</t>
+          <t>فلفل أسود (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>204</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="C13" t="n">
+        <v>24</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -2544,16 +2626,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>سوداني (13)</t>
+          <t>كركم (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="C14" t="n">
+        <v>139</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -2570,18 +2654,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>لوز (14)</t>
+          <t>كزبرة (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75</v>
-      </c>
-      <c r="C15" t="n">
-        <v>72</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2598,18 +2680,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>عين جمل (15)</t>
+          <t>بهارات مشكلة (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>234</v>
-      </c>
-      <c r="C16" t="n">
-        <v>225</v>
-      </c>
+        <v>160</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2626,11 +2706,11 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>كاجو (16)</t>
+          <t>قرفة (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>35</v>
+        <v>175</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
@@ -2652,16 +2732,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>شيبسي (17)</t>
+          <t>حبهان (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="C18" t="n">
+        <v>161</v>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2678,18 +2760,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>فشار (18)</t>
+          <t>ورق لورا (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>60</v>
+        <v>189</v>
       </c>
       <c r="C19" t="n">
-        <v>52</v>
+        <v>187</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2706,16 +2788,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>مقرمشات (19)</t>
+          <t>بابريكا (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>148</v>
+        <v>74</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2732,11 +2814,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>فستق (20)</t>
+          <t>قرنفل (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>249</v>
+        <v>36</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
@@ -2758,11 +2840,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>لب سوبر (21)</t>
+          <t>كمون (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
@@ -2784,15 +2866,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>لب سوري (22)</t>
+          <t>فلفل أسود (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>236</v>
-      </c>
-      <c r="C23" t="n">
-        <v>230</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -2812,11 +2892,11 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>سوداني (23)</t>
+          <t>كركم (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>235</v>
+        <v>178</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
@@ -2838,18 +2918,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>لوز (24)</t>
+          <t>كزبرة (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>245</v>
-      </c>
-      <c r="C25" t="n">
-        <v>235</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2866,16 +2944,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>عين جمل (25)</t>
+          <t>بهارات مشكلة (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>122</v>
+        <v>149</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2892,16 +2970,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>كاجو (26)</t>
+          <t>قرفة (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2918,13 +2996,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>شيبسي (27)</t>
+          <t>حبهان (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>53</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="C28" t="n">
+        <v>49</v>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -2944,16 +3024,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>فشار (28)</t>
+          <t>ورق لورا (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>183</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
+        <v>127</v>
+      </c>
+      <c r="C29" t="n">
+        <v>122</v>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2970,18 +3052,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>مقرمشات (29)</t>
+          <t>بابريكا (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>57</v>
-      </c>
-      <c r="C30" t="n">
-        <v>51</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2998,18 +3078,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>فستق (30)</t>
+          <t>قرنفل (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>180</v>
-      </c>
-      <c r="C31" t="n">
-        <v>174</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3072,13 +3150,15 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>مسحوق غسيل</t>
+          <t>شوكولاتة</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>116</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>152</v>
+      </c>
+      <c r="C2" t="n">
+        <v>144</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -3098,16 +3178,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>صابون سائل</t>
+          <t>جيلي</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>139</v>
+        <v>50</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3124,11 +3204,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>كلور</t>
+          <t>كريم كراميل</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170</v>
+        <v>230</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -3150,11 +3230,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>معطر جو</t>
+          <t>حلاوة طحينية</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
@@ -3176,16 +3256,16 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ديتول</t>
+          <t>ملبن</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>200</v>
+        <v>148</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -3202,16 +3282,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>صابون وجه</t>
+          <t>بسكويت شيكولاتة</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>116</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>203</v>
+      </c>
+      <c r="C7" t="n">
+        <v>198</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3228,18 +3310,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>شامبو</t>
+          <t>لبان</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>137</v>
+        <v>206</v>
       </c>
       <c r="C8" t="n">
-        <v>130</v>
+        <v>201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3256,11 +3338,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>مناديل</t>
+          <t>مربى</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>67</v>
+        <v>28</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
@@ -3282,11 +3364,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>سلك مواعين</t>
+          <t>عسل نحل</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>169</v>
+        <v>202</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
@@ -3308,11 +3390,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ملمع زجاج</t>
+          <t>كيك شوكولاتة</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
@@ -3334,15 +3416,13 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>مسحوق غسيل (11)</t>
+          <t>شوكولاتة (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>216</v>
-      </c>
-      <c r="C12" t="n">
-        <v>210</v>
-      </c>
+        <v>197</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -3362,16 +3442,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>صابون سائل (12)</t>
+          <t>جيلي (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>141</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="C13" t="n">
+        <v>83</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3388,16 +3470,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>كلور (13)</t>
+          <t>كريم كراميل (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>145</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>85</v>
+      </c>
+      <c r="C14" t="n">
+        <v>77</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3414,16 +3498,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>معطر جو (14)</t>
+          <t>حلاوة طحينية (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>155</v>
+        <v>182</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3440,16 +3524,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ديتول (15)</t>
+          <t>ملبن (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>177</v>
+        <v>118</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3466,16 +3550,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>صابون وجه (16)</t>
+          <t>بسكويت شيكولاتة (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3492,13 +3576,15 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>شامبو (17)</t>
+          <t>لبان (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>179</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="C18" t="n">
+        <v>39</v>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -3518,16 +3604,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>مناديل (18)</t>
+          <t>مربى (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>235</v>
+        <v>39</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3544,18 +3630,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>سلك مواعين (19)</t>
+          <t>عسل نحل (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="C20" t="n">
-        <v>96</v>
+        <v>133</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3572,11 +3658,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ملمع زجاج (20)</t>
+          <t>كيك شوكولاتة (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>89</v>
+        <v>238</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
@@ -3598,11 +3684,11 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>مسحوق غسيل (21)</t>
+          <t>شوكولاتة (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>106</v>
+        <v>54</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
@@ -3624,18 +3710,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>صابون سائل (22)</t>
+          <t>جيلي (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>34</v>
-      </c>
-      <c r="C23" t="n">
-        <v>30</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3652,16 +3736,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>كلور (23)</t>
+          <t>كريم كراميل (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>45</v>
+        <v>89</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -3678,11 +3762,11 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>معطر جو (24)</t>
+          <t>حلاوة طحينية (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>242</v>
+        <v>149</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
@@ -3704,18 +3788,18 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ديتول (25)</t>
+          <t>ملبن (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>143</v>
+        <v>66</v>
       </c>
       <c r="C26" t="n">
-        <v>140</v>
+        <v>56</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -3732,18 +3816,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>صابون وجه (26)</t>
+          <t>بسكويت شيكولاتة (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>166</v>
-      </c>
-      <c r="C27" t="n">
-        <v>159</v>
-      </c>
+        <v>155</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3760,18 +3842,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>شامبو (27)</t>
+          <t>لبان (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>101</v>
-      </c>
-      <c r="C28" t="n">
-        <v>99</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3788,11 +3868,11 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>مناديل (28)</t>
+          <t>مربى (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -3814,18 +3894,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>سلك مواعين (29)</t>
+          <t>عسل نحل (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>164</v>
-      </c>
-      <c r="C30" t="n">
-        <v>156</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3842,18 +3920,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ملمع زجاج (30)</t>
+          <t>كيك شوكولاتة (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>56</v>
-      </c>
-      <c r="C31" t="n">
-        <v>51</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3916,16 +3992,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>معجون أسنان</t>
+          <t>مسحوق غسيل</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>134</v>
+        <v>240</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3942,13 +4018,15 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>فرشاة أسنان</t>
+          <t>صابون سائل</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>189</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>116</v>
+      </c>
+      <c r="C3" t="n">
+        <v>113</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -3968,16 +4046,16 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>شامبو</t>
+          <t>كلور</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>185</v>
+        <v>42</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -3994,13 +4072,15 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>بلسم</t>
+          <t>معطر جو</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>83</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>187</v>
+      </c>
+      <c r="C5" t="n">
+        <v>183</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -4020,16 +4100,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>شاور جل</t>
+          <t>ديتول</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="C6" t="n">
+        <v>39</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4046,16 +4128,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>كريم شعر</t>
+          <t>صابون وجه</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>204</v>
+        <v>180</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4072,18 +4154,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>مزيل عرق</t>
+          <t>شامبو</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>127</v>
-      </c>
-      <c r="C8" t="n">
-        <v>120</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -4100,18 +4180,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ماكينة حلاقة</t>
+          <t>مناديل</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>223</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>216</v>
+        <v>18</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4128,18 +4208,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>غسول وجه</t>
+          <t>سلك مواعين</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181</v>
-      </c>
-      <c r="C10" t="n">
-        <v>174</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4156,16 +4234,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>مرطب</t>
+          <t>ملمع زجاج</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>218</v>
+        <v>50</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4182,11 +4260,11 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>معجون أسنان (11)</t>
+          <t>مسحوق غسيل (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>89</v>
+        <v>217</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
@@ -4208,16 +4286,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>فرشاة أسنان (12)</t>
+          <t>صابون سائل (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>201</v>
+        <v>154</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4234,16 +4312,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>شامبو (13)</t>
+          <t>كلور (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>133</v>
+        <v>85</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4260,18 +4338,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>بلسم (14)</t>
+          <t>معطر جو (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>122</v>
+        <v>75</v>
       </c>
       <c r="C15" t="n">
-        <v>114</v>
+        <v>72</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4288,16 +4366,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>شاور جل (15)</t>
+          <t>ديتول (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>137</v>
+        <v>162</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4314,16 +4392,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>كريم شعر (16)</t>
+          <t>صابون وجه (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>232</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4340,14 +4418,14 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>مزيل عرق (17)</t>
+          <t>شامبو (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>194</v>
+        <v>246</v>
       </c>
       <c r="C18" t="n">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -4368,16 +4446,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ماكينة حلاقة (18)</t>
+          <t>مناديل (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4394,16 +4472,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>غسول وجه (19)</t>
+          <t>سلك مواعين (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4420,11 +4498,11 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>مرطب (20)</t>
+          <t>ملمع زجاج (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>24</v>
+        <v>217</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
@@ -4446,16 +4524,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>معجون أسنان (21)</t>
+          <t>مسحوق غسيل (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4472,15 +4550,13 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>فرشاة أسنان (22)</t>
+          <t>صابون سائل (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>166</v>
-      </c>
-      <c r="C23" t="n">
-        <v>164</v>
-      </c>
+        <v>215</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -4500,16 +4576,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>شامبو (23)</t>
+          <t>كلور (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>34</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>32</v>
+      </c>
+      <c r="C24" t="n">
+        <v>23</v>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -4526,13 +4604,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>بلسم (24)</t>
+          <t>معطر جو (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>146</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="C25" t="n">
+        <v>92</v>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -4552,11 +4632,11 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>شاور جل (25)</t>
+          <t>ديتول (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>193</v>
+        <v>56</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
@@ -4578,16 +4658,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>كريم شعر (26)</t>
+          <t>صابون وجه (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>99</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>42</v>
+      </c>
+      <c r="C27" t="n">
+        <v>34</v>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4604,16 +4686,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>مزيل عرق (27)</t>
+          <t>شامبو (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4630,16 +4712,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ماكينة حلاقة (28)</t>
+          <t>مناديل (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4656,16 +4738,16 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>غسول وجه (29)</t>
+          <t>سلك مواعين (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>53</v>
+        <v>152</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4682,13 +4764,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>مرطب (30)</t>
+          <t>ملمع زجاج (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>135</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>220</v>
+      </c>
+      <c r="C31" t="n">
+        <v>211</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -4828,14 +4912,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>طماطم</t>
+          <t>جزر</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
+        <v>169</v>
       </c>
       <c r="C2" t="n">
-        <v>40</v>
+        <v>167</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4856,18 +4940,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>خيار</t>
+          <t>برتقال</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="C3" t="n">
-        <v>59</v>
+        <v>41</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4884,18 +4968,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>بصل (13)</t>
+          <t>برتقال (18)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>151</v>
+        <v>34</v>
       </c>
       <c r="C4" t="n">
-        <v>145</v>
+        <v>26</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4912,18 +4996,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>جزر (15)</t>
+          <t>بطاطس (22)</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81</v>
+        <v>57</v>
       </c>
       <c r="C5" t="n">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4940,18 +5024,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>موز (17)</t>
+          <t>لوز</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>186</v>
+        <v>155</v>
       </c>
       <c r="C6" t="n">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4968,14 +5052,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>تفاح (26)</t>
+          <t>شيبسي</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -4996,18 +5080,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>فراخ كاملة</t>
+          <t>فشار</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C8" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5024,18 +5108,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>كبدة</t>
+          <t>لب سوبر (11)</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5052,18 +5136,18 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>كفتة</t>
+          <t>فشار (18)</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>148</v>
+        <v>246</v>
       </c>
       <c r="C10" t="n">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5080,18 +5164,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>فراخ كاملة (11)</t>
+          <t>لب سوبر (21)</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>59</v>
+        <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5108,18 +5192,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>لحمة مفرومة (23)</t>
+          <t>مشروب طاقة</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C12" t="n">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5136,18 +5220,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>شيش طاووق (27)</t>
+          <t>عصير برتقال (14)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>223</v>
+        <v>32</v>
       </c>
       <c r="C13" t="n">
-        <v>214</v>
+        <v>25</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5164,14 +5248,14 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>جبنة رومي (13)</t>
+          <t>عصير تفاح (15)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="C14" t="n">
-        <v>149</v>
+        <v>196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -5192,18 +5276,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>بيض أبيض (15)</t>
+          <t>نعناع (20)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>199</v>
+        <v>142</v>
       </c>
       <c r="C15" t="n">
-        <v>194</v>
+        <v>140</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5220,18 +5304,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>جبنة رومي (23)</t>
+          <t>عصير تفاح (25)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>92</v>
+        <v>198</v>
       </c>
       <c r="C16" t="n">
-        <v>86</v>
+        <v>188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5248,18 +5332,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>قشطة (28)</t>
+          <t>أرز</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C17" t="n">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -5276,18 +5360,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>عيش فينو</t>
+          <t>سمنة</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>54</v>
+        <v>79</v>
       </c>
       <c r="C18" t="n">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5304,14 +5388,14 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>كرواسون</t>
+          <t>سكر (13)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="C19" t="n">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -5332,18 +5416,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>فطير</t>
+          <t>فول (28)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>171</v>
+        <v>28</v>
       </c>
       <c r="C20" t="n">
-        <v>169</v>
+        <v>26</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5360,7 +5444,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>كرواسون (24)</t>
+          <t>جبنة رومي</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -5371,7 +5455,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5636,14 +5720,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46</v>
-      </c>
-      <c r="C2" t="n">
-        <v>40</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5664,12 +5746,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>181</v>
+        <v>120</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -5690,12 +5772,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>197</v>
+        <v>184</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5716,14 +5798,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>67</v>
-      </c>
-      <c r="C5" t="n">
-        <v>59</v>
-      </c>
+        <v>137</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5744,12 +5824,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>140</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>169</v>
+      </c>
+      <c r="C6" t="n">
+        <v>167</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5770,7 +5852,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
@@ -5796,12 +5878,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>184</v>
+        <v>57</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5822,12 +5904,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>185</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="C9" t="n">
+        <v>41</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5848,12 +5932,14 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>94</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="C10" t="n">
+        <v>69</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5874,12 +5960,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>87</v>
+        <v>144</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5900,12 +5986,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>139</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5926,12 +6012,12 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>40</v>
+        <v>197</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5952,14 +6038,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>151</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
-        <v>145</v>
+        <v>8</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5980,14 +6066,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>114</v>
-      </c>
-      <c r="C15" t="n">
-        <v>104</v>
-      </c>
+        <v>95</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6008,14 +6092,12 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>81</v>
-      </c>
-      <c r="C16" t="n">
-        <v>76</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6036,14 +6118,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>220</v>
-      </c>
-      <c r="C17" t="n">
-        <v>213</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6064,14 +6144,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>186</v>
-      </c>
-      <c r="C18" t="n">
-        <v>179</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6092,12 +6170,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>75</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="C19" t="n">
+        <v>26</v>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6118,12 +6198,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6144,14 +6224,12 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>234</v>
-      </c>
-      <c r="C21" t="n">
-        <v>228</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6172,12 +6250,12 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>52</v>
+        <v>162</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6198,12 +6276,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>53</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>57</v>
+      </c>
+      <c r="C23" t="n">
+        <v>52</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6224,14 +6304,14 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>46</v>
+        <v>163</v>
       </c>
       <c r="C24" t="n">
-        <v>37</v>
+        <v>159</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -6252,12 +6332,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>77</v>
+        <v>102</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6278,12 +6358,12 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>243</v>
+        <v>61</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6304,14 +6384,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>21</v>
+        <v>65</v>
       </c>
       <c r="C27" t="n">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -6332,12 +6412,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>227</v>
+        <v>130</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -6358,12 +6438,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>135</v>
+        <v>51</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -6384,12 +6464,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>119</v>
+        <v>96</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6410,12 +6490,14 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>247</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>167</v>
+      </c>
+      <c r="C31" t="n">
+        <v>160</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -6478,18 +6560,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>فراخ كاملة</t>
+          <t>لب سوبر</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>100</v>
-      </c>
-      <c r="C2" t="n">
-        <v>92</v>
-      </c>
+        <v>177</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -6506,18 +6586,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>بانيه</t>
+          <t>لب سوري</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>118</v>
-      </c>
-      <c r="C3" t="n">
-        <v>108</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6534,13 +6612,15 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>لحمة مفرومة</t>
+          <t>سوداني</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>212</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="C4" t="n">
+        <v>240</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -6560,18 +6640,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>كبدة</t>
+          <t>لوز</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>48</v>
+        <v>155</v>
       </c>
       <c r="C5" t="n">
-        <v>40</v>
+        <v>149</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -6588,18 +6668,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>سجق</t>
+          <t>عين جمل</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73</v>
+        <v>171</v>
       </c>
       <c r="C6" t="n">
-        <v>69</v>
+        <v>164</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6616,11 +6696,11 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>لحم مكعبات</t>
+          <t>كاجو</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>81</v>
+        <v>23</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
@@ -6642,18 +6722,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>شيش طاووق</t>
+          <t>شيبسي</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>225</v>
+        <v>43</v>
       </c>
       <c r="C8" t="n">
-        <v>218</v>
+        <v>39</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6670,18 +6750,18 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>دبابيس</t>
+          <t>فشار</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="C9" t="n">
-        <v>69</v>
+        <v>91</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6698,16 +6778,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>برجر</t>
+          <t>مقرمشات</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>143</v>
+        <v>232</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -6724,18 +6804,16 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>كفتة</t>
+          <t>فستق</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>148</v>
-      </c>
-      <c r="C11" t="n">
-        <v>146</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6752,18 +6830,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>فراخ كاملة (11)</t>
+          <t>لب سوبر (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>59</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6780,16 +6858,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>بانيه (12)</t>
+          <t>لب سوري (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6806,18 +6884,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>لحمة مفرومة (13)</t>
+          <t>سوداني (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>232</v>
-      </c>
-      <c r="C14" t="n">
-        <v>224</v>
-      </c>
+        <v>206</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6834,16 +6910,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>كبدة (14)</t>
+          <t>لوز (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>120</v>
+        <v>81</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6860,16 +6936,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>سجق (15)</t>
+          <t>عين جمل (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6886,15 +6962,13 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>لحم مكعبات (16)</t>
+          <t>كاجو (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>194</v>
-      </c>
-      <c r="C17" t="n">
-        <v>189</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -6914,16 +6988,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>شيش طاووق (17)</t>
+          <t>شيبسي (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>158</v>
+        <v>175</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6940,18 +7014,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>دبابيس (18)</t>
+          <t>فشار (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>31</v>
+        <v>246</v>
       </c>
       <c r="C19" t="n">
-        <v>23</v>
+        <v>237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -6968,16 +7042,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>برجر (19)</t>
+          <t>مقرمشات (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>53</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>74</v>
+      </c>
+      <c r="C20" t="n">
+        <v>70</v>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6994,18 +7070,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>كفتة (20)</t>
+          <t>فستق (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>63</v>
-      </c>
-      <c r="C21" t="n">
-        <v>55</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -7022,13 +7096,15 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>فراخ كاملة (21)</t>
+          <t>لب سوبر (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>124</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="C22" t="n">
+        <v>27</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -7048,13 +7124,15 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>بانيه (22)</t>
+          <t>لب سوري (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>45</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>244</v>
+      </c>
+      <c r="C23" t="n">
+        <v>234</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -7074,18 +7152,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>لحمة مفرومة (23)</t>
+          <t>سوداني (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>193</v>
-      </c>
-      <c r="C24" t="n">
-        <v>186</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -7102,16 +7178,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>كبدة (24)</t>
+          <t>لوز (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>36</v>
+        <v>150</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7128,16 +7204,16 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>سجق (25)</t>
+          <t>عين جمل (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>195</v>
+        <v>17</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -7154,18 +7230,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>لحم مكعبات (26)</t>
+          <t>كاجو (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>96</v>
-      </c>
-      <c r="C27" t="n">
-        <v>93</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7182,18 +7256,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>شيش طاووق (27)</t>
+          <t>شيبسي (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>223</v>
-      </c>
-      <c r="C28" t="n">
-        <v>214</v>
-      </c>
+        <v>249</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -7210,16 +7282,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>دبابيس (28)</t>
+          <t>فشار (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7236,13 +7308,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>برجر (29)</t>
+          <t>مقرمشات (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>148</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="C30" t="n">
+        <v>127</v>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -7262,16 +7336,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>كفتة (30)</t>
+          <t>فستق (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7334,18 +7408,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>لبن كامل الدسم</t>
+          <t>شاي</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>59</v>
-      </c>
-      <c r="C2" t="n">
-        <v>55</v>
-      </c>
+        <v>43</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7362,16 +7434,16 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>جبنة بيضاء</t>
+          <t>قهوة</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -7388,11 +7460,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>جبنة رومي</t>
+          <t>نسكافيه</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>160</v>
+        <v>235</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -7414,11 +7486,11 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>زبادي</t>
+          <t>عصير برتقال</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>224</v>
+        <v>43</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
@@ -7440,11 +7512,11 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>بيض أبيض</t>
+          <t>عصير تفاح</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>136</v>
+        <v>32</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
@@ -7466,16 +7538,16 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>بيض أحمر</t>
+          <t>كولا</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>126</v>
+        <v>120</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -7492,16 +7564,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>زبدة</t>
+          <t>مياه معدنية</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7518,13 +7590,15 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>قشطة</t>
+          <t>مشروب طاقة</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>183</v>
+      </c>
+      <c r="C9" t="n">
+        <v>178</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -7544,18 +7618,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>جبنة شيدر</t>
+          <t>كاكاو</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>173</v>
-      </c>
-      <c r="C10" t="n">
-        <v>171</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -7572,15 +7644,13 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>جبنة نستو</t>
+          <t>نعناع</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>44</v>
-      </c>
-      <c r="C11" t="n">
-        <v>36</v>
-      </c>
+        <v>212</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -7600,16 +7670,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>لبن كامل الدسم (11)</t>
+          <t>شاي (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>131</v>
+        <v>116</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7626,16 +7696,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>جبنة بيضاء (12)</t>
+          <t>قهوة (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>162</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>55</v>
+      </c>
+      <c r="C13" t="n">
+        <v>47</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -7652,15 +7724,13 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>جبنة رومي (13)</t>
+          <t>نسكافيه (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>159</v>
-      </c>
-      <c r="C14" t="n">
-        <v>149</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -7680,18 +7750,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>زبادي (14)</t>
+          <t>عصير برتقال (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>115</v>
+        <v>32</v>
       </c>
       <c r="C15" t="n">
-        <v>111</v>
+        <v>25</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7708,18 +7778,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>بيض أبيض (15)</t>
+          <t>عصير تفاح (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C16" t="n">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7736,18 +7806,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>بيض أحمر (16)</t>
+          <t>كولا (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56</v>
-      </c>
-      <c r="C17" t="n">
-        <v>53</v>
-      </c>
+        <v>84</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7764,16 +7832,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>زبدة (17)</t>
+          <t>مياه معدنية (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>239</v>
+        <v>119</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7790,16 +7858,16 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>قشطة (18)</t>
+          <t>مشروب طاقة (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26</v>
+        <v>51</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7816,16 +7884,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>جبنة شيدر (19)</t>
+          <t>كاكاو (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>63</v>
+        <v>205</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -7842,16 +7910,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>جبنة نستو (20)</t>
+          <t>نعناع (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>124</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>142</v>
+      </c>
+      <c r="C21" t="n">
+        <v>140</v>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -7868,15 +7938,13 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>لبن كامل الدسم (21)</t>
+          <t>شاي (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>120</v>
-      </c>
-      <c r="C22" t="n">
-        <v>116</v>
-      </c>
+        <v>126</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -7896,16 +7964,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>جبنة بيضاء (22)</t>
+          <t>قهوة (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -7922,18 +7990,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>جبنة رومي (23)</t>
+          <t>نسكافيه (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92</v>
-      </c>
-      <c r="C24" t="n">
-        <v>86</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -7950,16 +8016,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>زبادي (24)</t>
+          <t>عصير برتقال (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7976,13 +8042,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>بيض أبيض (25)</t>
+          <t>عصير تفاح (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>157</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>198</v>
+      </c>
+      <c r="C26" t="n">
+        <v>188</v>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -8002,16 +8070,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>بيض أحمر (26)</t>
+          <t>كولا (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>61</v>
+        <v>41</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -8028,16 +8096,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>زبدة (27)</t>
+          <t>مياه معدنية (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>238</v>
+        <v>159</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8054,18 +8122,16 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>قشطة (28)</t>
+          <t>مشروب طاقة (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82</v>
-      </c>
-      <c r="C29" t="n">
-        <v>78</v>
-      </c>
+        <v>236</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -8082,11 +8148,11 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>جبنة شيدر (29)</t>
+          <t>كاكاو (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64</v>
+        <v>104</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
@@ -8108,16 +8174,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>جبنة نستو (30)</t>
+          <t>نعناع (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>102</v>
+        <v>202</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -8180,18 +8246,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>عيش فينو</t>
+          <t>أرز</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>54</v>
+        <v>64</v>
       </c>
       <c r="C2" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8208,11 +8274,11 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>عيش بلدي</t>
+          <t>مكرونة</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>146</v>
+        <v>127</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
@@ -8234,11 +8300,11 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>باتيه</t>
+          <t>سكر</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>155</v>
+        <v>214</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -8260,18 +8326,16 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>كرواسون</t>
+          <t>زيت</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
-      </c>
-      <c r="C5" t="n">
-        <v>113</v>
-      </c>
+        <v>202</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8288,16 +8352,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>بقسماط</t>
+          <t>سمنة</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>143</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
+        <v>79</v>
+      </c>
+      <c r="C6" t="n">
+        <v>76</v>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -8314,16 +8380,18 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>توست أبيض</t>
+          <t>صلصة</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>193</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="C7" t="n">
+        <v>127</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8340,16 +8408,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>توست أسمر</t>
+          <t>تونة</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>229</v>
+        <v>164</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8366,18 +8434,16 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>فطير</t>
+          <t>فول</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>171</v>
-      </c>
-      <c r="C9" t="n">
-        <v>169</v>
-      </c>
+        <v>58</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8394,16 +8460,16 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>كيك</t>
+          <t>عدس</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>107</v>
+        <v>16</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8420,15 +8486,13 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>بسكويت</t>
+          <t>دقيق</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>150</v>
-      </c>
-      <c r="C11" t="n">
-        <v>148</v>
-      </c>
+        <v>222</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -8448,16 +8512,18 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>عيش فينو (11)</t>
+          <t>أرز (11)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>103</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>168</v>
+      </c>
+      <c r="C12" t="n">
+        <v>163</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8474,15 +8540,13 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>عيش بلدي (12)</t>
+          <t>مكرونة (12)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>130</v>
-      </c>
-      <c r="C13" t="n">
-        <v>128</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -8502,16 +8566,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>باتيه (13)</t>
+          <t>سكر (13)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>34</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>135</v>
+      </c>
+      <c r="C14" t="n">
+        <v>133</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8528,16 +8594,16 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>كرواسون (14)</t>
+          <t>زيت (14)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95</v>
+        <v>128</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8554,16 +8620,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>بقسماط (15)</t>
+          <t>سمنة (15)</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>184</v>
+        <v>108</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8580,16 +8646,16 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>توست أبيض (16)</t>
+          <t>صلصة (16)</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>158</v>
+        <v>99</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8606,16 +8672,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>توست أسمر (17)</t>
+          <t>تونة (17)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>173</v>
+        <v>203</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -8632,11 +8698,11 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>فطير (18)</t>
+          <t>فول (18)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
@@ -8658,16 +8724,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>كيك (19)</t>
+          <t>عدس (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>61</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="C20" t="n">
+        <v>132</v>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8684,16 +8752,16 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>بسكويت (20)</t>
+          <t>دقيق (20)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>234</v>
+        <v>17</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -8710,15 +8778,13 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>عيش فينو (21)</t>
+          <t>أرز (21)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>72</v>
-      </c>
-      <c r="C22" t="n">
-        <v>64</v>
-      </c>
+        <v>133</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -8738,16 +8804,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>عيش بلدي (22)</t>
+          <t>مكرونة (22)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
+        <v>144</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -8764,16 +8830,18 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>باتيه (23)</t>
+          <t>سكر (23)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>165</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="C24" t="n">
+        <v>132</v>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8790,18 +8858,16 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>كرواسون (24)</t>
+          <t>زيت (24)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>87</v>
-      </c>
-      <c r="C25" t="n">
-        <v>79</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -8818,15 +8884,13 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>بقسماط (25)</t>
+          <t>سمنة (25)</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>86</v>
-      </c>
-      <c r="C26" t="n">
-        <v>76</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -8846,13 +8910,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>توست أبيض (26)</t>
+          <t>صلصة (26)</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>181</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>95</v>
+      </c>
+      <c r="C27" t="n">
+        <v>86</v>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -8872,16 +8938,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>توست أسمر (27)</t>
+          <t>تونة (27)</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>128</v>
+        <v>249</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8898,16 +8964,18 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>فطير (28)</t>
+          <t>فول (28)</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>142</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="C29" t="n">
+        <v>26</v>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -8924,16 +8992,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>كيك (29)</t>
+          <t>عدس (29)</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>231</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>123</v>
+      </c>
+      <c r="C30" t="n">
+        <v>120</v>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -8950,16 +9020,16 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>بسكويت (30)</t>
+          <t>دقيق (30)</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -614,12 +614,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>197</v>
+        <v>243</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -640,7 +640,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>168</v>
+        <v>228</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
@@ -666,11 +666,9 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>87</v>
-      </c>
-      <c r="C4" t="n">
-        <v>79</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -694,12 +692,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>224</v>
+        <v>199</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -720,14 +718,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>31</v>
-      </c>
-      <c r="C6" t="n">
-        <v>27</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -748,12 +744,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -774,12 +770,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>248</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="C8" t="n">
+        <v>39</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -800,12 +798,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>137</v>
+      </c>
+      <c r="C9" t="n">
+        <v>135</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -826,14 +826,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>114</v>
-      </c>
-      <c r="C10" t="n">
-        <v>110</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -854,11 +852,9 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>192</v>
-      </c>
-      <c r="C11" t="n">
-        <v>186</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -882,12 +878,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>150</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>134</v>
+      </c>
+      <c r="C12" t="n">
+        <v>124</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -908,10 +906,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>149</v>
+        <v>126</v>
       </c>
       <c r="C13" t="n">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -936,12 +934,12 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -962,12 +960,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>215</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>148</v>
+      </c>
+      <c r="C15" t="n">
+        <v>141</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -988,12 +988,12 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1014,12 +1014,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>98</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>196</v>
+      </c>
+      <c r="C17" t="n">
+        <v>194</v>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1040,12 +1042,14 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>200</v>
-      </c>
-      <c r="C18" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="C18" t="n">
+        <v>66</v>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1066,12 +1070,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>235</v>
+        <v>53</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1092,12 +1096,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1118,12 +1122,12 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>89</v>
+        <v>65</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1144,14 +1148,12 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>81</v>
-      </c>
-      <c r="C22" t="n">
-        <v>72</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1172,10 +1174,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>145</v>
+        <v>29</v>
       </c>
       <c r="C23" t="n">
-        <v>137</v>
+        <v>25</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1200,12 +1202,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>208</v>
+        <v>165</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1226,14 +1228,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>204</v>
+        <v>118</v>
       </c>
       <c r="C25" t="n">
-        <v>202</v>
+        <v>114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1254,14 +1256,14 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>159</v>
+        <v>210</v>
       </c>
       <c r="C26" t="n">
-        <v>156</v>
+        <v>202</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1282,7 +1284,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>174</v>
+        <v>24</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
@@ -1308,12 +1310,14 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>191</v>
+      </c>
+      <c r="C28" t="n">
+        <v>187</v>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1334,12 +1338,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>129</v>
+        <v>172</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1360,12 +1364,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1386,14 +1390,12 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>92</v>
-      </c>
-      <c r="C31" t="n">
-        <v>87</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1460,7 +1462,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
@@ -1486,11 +1488,9 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
-      </c>
-      <c r="C3" t="n">
-        <v>9</v>
-      </c>
+        <v>191</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -1514,11 +1514,9 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>36</v>
-      </c>
-      <c r="C4" t="n">
-        <v>29</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -1542,7 +1540,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>84</v>
+        <v>66</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
@@ -1568,11 +1566,9 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>64</v>
-      </c>
-      <c r="C6" t="n">
-        <v>55</v>
-      </c>
+        <v>51</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -1596,14 +1592,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C7" t="n">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1624,14 +1620,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>234</v>
+        <v>32</v>
       </c>
       <c r="C8" t="n">
-        <v>227</v>
+        <v>24</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1652,12 +1648,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>91</v>
-      </c>
-      <c r="C9" t="inlineStr"/>
+        <v>189</v>
+      </c>
+      <c r="C9" t="n">
+        <v>181</v>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1678,14 +1676,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>122</v>
-      </c>
-      <c r="C10" t="n">
-        <v>112</v>
-      </c>
+        <v>101</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1706,12 +1702,14 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>62</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>124</v>
+      </c>
+      <c r="C11" t="n">
+        <v>118</v>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1732,14 +1730,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>205</v>
-      </c>
-      <c r="C12" t="n">
-        <v>196</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1760,12 +1756,14 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>192</v>
-      </c>
-      <c r="C13" t="inlineStr"/>
+        <v>69</v>
+      </c>
+      <c r="C13" t="n">
+        <v>60</v>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1786,12 +1784,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>69</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="C14" t="n">
+        <v>131</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1812,12 +1812,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>246</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>216</v>
+      </c>
+      <c r="C15" t="n">
+        <v>209</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1838,11 +1840,9 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29</v>
-      </c>
-      <c r="C16" t="n">
-        <v>25</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -1866,14 +1866,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>198</v>
-      </c>
-      <c r="C17" t="n">
-        <v>190</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1894,7 +1892,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
@@ -1920,12 +1918,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>178</v>
+        <v>246</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1946,12 +1944,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>112</v>
+        <v>151</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1972,7 +1970,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
@@ -1998,12 +1996,12 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>225</v>
+        <v>54</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2024,12 +2022,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>29</v>
+      </c>
+      <c r="C23" t="n">
+        <v>21</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2050,12 +2050,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>73</v>
+        <v>135</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2076,12 +2076,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>100</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>76</v>
+      </c>
+      <c r="C25" t="n">
+        <v>73</v>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2102,14 +2104,12 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>37</v>
-      </c>
-      <c r="C26" t="n">
-        <v>34</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2130,12 +2130,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>132</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C27" t="n">
+        <v>54</v>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2156,12 +2158,14 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>217</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>16</v>
+      </c>
+      <c r="C28" t="n">
+        <v>7</v>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2182,7 +2186,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>52</v>
+        <v>87</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -2208,12 +2212,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>249</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>77</v>
+      </c>
+      <c r="C30" t="n">
+        <v>74</v>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2234,12 +2240,14 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>35</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>98</v>
+      </c>
+      <c r="C31" t="n">
+        <v>91</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2306,14 +2314,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>136</v>
+        <v>214</v>
       </c>
       <c r="C2" t="n">
-        <v>126</v>
+        <v>207</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -2334,10 +2342,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>95</v>
+        <v>65</v>
       </c>
       <c r="C3" t="n">
-        <v>85</v>
+        <v>58</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -2362,12 +2370,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>206</v>
+        <v>101</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -2388,12 +2396,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2414,12 +2422,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>142</v>
+        <v>56</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2440,12 +2448,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>114</v>
-      </c>
-      <c r="C7" t="inlineStr"/>
+        <v>46</v>
+      </c>
+      <c r="C7" t="n">
+        <v>41</v>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2466,14 +2476,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74</v>
+        <v>211</v>
       </c>
       <c r="C8" t="n">
-        <v>67</v>
+        <v>204</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -2494,14 +2504,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>119</v>
-      </c>
-      <c r="C9" t="n">
-        <v>110</v>
-      </c>
+        <v>174</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -2522,11 +2530,9 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>205</v>
-      </c>
-      <c r="C10" t="n">
-        <v>198</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -2550,12 +2556,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -2576,7 +2582,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>163</v>
+        <v>98</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
@@ -2602,14 +2608,14 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>101</v>
       </c>
       <c r="C13" t="n">
-        <v>24</v>
+        <v>99</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -2630,10 +2636,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>144</v>
+        <v>34</v>
       </c>
       <c r="C14" t="n">
-        <v>139</v>
+        <v>25</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2658,12 +2664,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -2684,12 +2690,12 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2710,12 +2716,14 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>175</v>
-      </c>
-      <c r="C17" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="C17" t="n">
+        <v>138</v>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2736,14 +2744,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>164</v>
-      </c>
-      <c r="C18" t="n">
-        <v>161</v>
-      </c>
+        <v>104</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2764,10 +2770,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="C19" t="n">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2792,12 +2798,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>74</v>
+        <v>205</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2818,12 +2824,14 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>36</v>
-      </c>
-      <c r="C21" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="C21" t="n">
+        <v>51</v>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2844,7 +2852,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>120</v>
+        <v>172</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
@@ -2870,12 +2878,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>101</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>93</v>
+      </c>
+      <c r="C23" t="n">
+        <v>88</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -2896,12 +2906,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -2922,12 +2932,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>220</v>
+        <v>126</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -2948,9 +2958,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>149</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>250</v>
+      </c>
+      <c r="C26" t="n">
+        <v>247</v>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -2974,12 +2986,14 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>124</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>118</v>
+      </c>
+      <c r="C27" t="n">
+        <v>108</v>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3000,14 +3014,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>54</v>
-      </c>
-      <c r="C28" t="n">
-        <v>49</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3028,14 +3040,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>127</v>
-      </c>
-      <c r="C29" t="n">
-        <v>122</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3056,12 +3066,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>145</v>
+        <v>18</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3082,12 +3092,12 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>237</v>
+        <v>197</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3154,14 +3164,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>152</v>
-      </c>
-      <c r="C2" t="n">
-        <v>144</v>
-      </c>
+        <v>119</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -3182,12 +3190,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>50</v>
+        <v>144</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3208,9 +3216,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>230</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>244</v>
+      </c>
+      <c r="C4" t="n">
+        <v>234</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -3234,12 +3244,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>233</v>
+        <v>28</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3260,7 +3270,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>148</v>
+        <v>206</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
@@ -3286,14 +3296,14 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>203</v>
+        <v>223</v>
       </c>
       <c r="C7" t="n">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3314,14 +3324,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>206</v>
+        <v>234</v>
       </c>
       <c r="C8" t="n">
-        <v>201</v>
+        <v>230</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3342,12 +3352,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>28</v>
+        <v>87</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3368,12 +3378,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>202</v>
+        <v>147</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -3394,7 +3404,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>232</v>
+        <v>141</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
@@ -3420,12 +3430,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>197</v>
+        <v>152</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3446,14 +3456,12 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>93</v>
-      </c>
-      <c r="C13" t="n">
-        <v>83</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -3474,14 +3482,12 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>85</v>
-      </c>
-      <c r="C14" t="n">
-        <v>77</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -3502,12 +3508,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>182</v>
+        <v>213</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -3528,12 +3534,14 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>118</v>
-      </c>
-      <c r="C16" t="inlineStr"/>
+        <v>167</v>
+      </c>
+      <c r="C16" t="n">
+        <v>161</v>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -3554,12 +3562,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3580,10 +3588,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>47</v>
+        <v>243</v>
       </c>
       <c r="C18" t="n">
-        <v>39</v>
+        <v>241</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3608,12 +3616,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>39</v>
+        <v>166</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -3634,14 +3642,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>138</v>
-      </c>
-      <c r="C20" t="n">
-        <v>133</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -3662,12 +3668,12 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -3688,12 +3694,12 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>54</v>
+        <v>224</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -3714,12 +3720,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>226</v>
+        <v>160</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -3740,7 +3746,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>89</v>
+        <v>233</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
@@ -3766,12 +3772,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -3792,11 +3798,9 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>66</v>
-      </c>
-      <c r="C26" t="n">
-        <v>56</v>
-      </c>
+        <v>195</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -3820,9 +3824,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>155</v>
-      </c>
-      <c r="C27" t="inlineStr"/>
+        <v>194</v>
+      </c>
+      <c r="C27" t="n">
+        <v>191</v>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -3846,12 +3852,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3872,12 +3878,14 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27</v>
-      </c>
-      <c r="C29" t="inlineStr"/>
+        <v>237</v>
+      </c>
+      <c r="C29" t="n">
+        <v>228</v>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -3898,12 +3906,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>51</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>234</v>
+      </c>
+      <c r="C30" t="n">
+        <v>228</v>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3924,9 +3934,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>170</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>210</v>
+      </c>
+      <c r="C31" t="n">
+        <v>201</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -3996,9 +4008,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>240</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>103</v>
+      </c>
+      <c r="C2" t="n">
+        <v>101</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -4022,14 +4036,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>116</v>
-      </c>
-      <c r="C3" t="n">
-        <v>113</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4050,12 +4062,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>54</v>
+      </c>
+      <c r="C4" t="n">
+        <v>44</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -4076,14 +4090,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>187</v>
-      </c>
-      <c r="C5" t="n">
-        <v>183</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4104,14 +4116,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42</v>
-      </c>
-      <c r="C6" t="n">
-        <v>39</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -4132,12 +4142,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>180</v>
+        <v>116</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -4158,7 +4168,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>202</v>
+        <v>227</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
@@ -4184,14 +4194,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>199</v>
       </c>
       <c r="C9" t="n">
-        <v>18</v>
+        <v>189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4212,12 +4222,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4238,9 +4248,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50</v>
-      </c>
-      <c r="C11" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="C11" t="n">
+        <v>157</v>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -4264,12 +4276,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>217</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="C12" t="n">
+        <v>55</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -4290,12 +4304,12 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>154</v>
+        <v>54</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -4316,12 +4330,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>85</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>28</v>
+      </c>
+      <c r="C14" t="n">
+        <v>19</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -4342,14 +4358,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>75</v>
-      </c>
-      <c r="C15" t="n">
-        <v>72</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -4370,12 +4384,12 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>162</v>
+        <v>243</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -4396,12 +4410,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>232</v>
+        <v>38</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -4422,11 +4436,9 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>246</v>
-      </c>
-      <c r="C18" t="n">
-        <v>241</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -4450,12 +4462,14 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>135</v>
-      </c>
-      <c r="C19" t="inlineStr"/>
+        <v>71</v>
+      </c>
+      <c r="C19" t="n">
+        <v>61</v>
+      </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -4476,12 +4490,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>66</v>
+        <v>240</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -4502,12 +4516,12 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>217</v>
+        <v>195</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -4528,12 +4542,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>200</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>58</v>
+      </c>
+      <c r="C22" t="n">
+        <v>49</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -4554,12 +4570,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>215</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>140</v>
+      </c>
+      <c r="C23" t="n">
+        <v>130</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -4580,11 +4598,9 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>32</v>
-      </c>
-      <c r="C24" t="n">
-        <v>23</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -4608,14 +4624,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>95</v>
-      </c>
-      <c r="C25" t="n">
-        <v>92</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -4636,12 +4650,12 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -4662,14 +4676,12 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>42</v>
-      </c>
-      <c r="C27" t="n">
-        <v>34</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -4690,12 +4702,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>73</v>
+        <v>139</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -4716,12 +4728,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>186</v>
+        <v>57</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -4742,12 +4754,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>152</v>
+        <v>224</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -4768,11 +4780,9 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>220</v>
-      </c>
-      <c r="C31" t="n">
-        <v>211</v>
-      </c>
+        <v>91</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -4912,14 +4922,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>جزر</t>
+          <t>خيار</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>169</v>
+        <v>84</v>
       </c>
       <c r="C2" t="n">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -4940,18 +4950,18 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>برتقال</t>
+          <t>موز</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -4968,18 +4978,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>برتقال (18)</t>
+          <t>خيار (14)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>34</v>
+        <v>136</v>
       </c>
       <c r="C4" t="n">
-        <v>26</v>
+        <v>131</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -5000,14 +5010,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5024,18 +5034,18 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>لوز</t>
+          <t>بصل (23)</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>155</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5052,14 +5062,14 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>شيبسي</t>
+          <t>موز (27)</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="C7" t="n">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -5080,18 +5090,18 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>فشار</t>
+          <t>عنب (29)</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>95</v>
+        <v>129</v>
       </c>
       <c r="C8" t="n">
-        <v>91</v>
+        <v>123</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5108,14 +5118,14 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>لب سوبر (11)</t>
+          <t>لب سوبر</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5136,14 +5146,14 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>فشار (18)</t>
+          <t>شيبسي</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>246</v>
+        <v>103</v>
       </c>
       <c r="C10" t="n">
-        <v>237</v>
+        <v>98</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -5164,18 +5174,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>لب سوبر (21)</t>
+          <t>مقرمشات</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>33</v>
       </c>
       <c r="C11" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5192,14 +5202,14 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>مشروب طاقة</t>
+          <t>سوداني (13)</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>183</v>
+        <v>221</v>
       </c>
       <c r="C12" t="n">
-        <v>178</v>
+        <v>214</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -5220,18 +5230,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>عصير برتقال (14)</t>
+          <t>سوداني (23)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>32</v>
+        <v>149</v>
       </c>
       <c r="C13" t="n">
-        <v>25</v>
+        <v>145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5248,18 +5258,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>عصير تفاح (15)</t>
+          <t>لوز (24)</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="C14" t="n">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -5276,18 +5286,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>نعناع (20)</t>
+          <t>مقرمشات (29)</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>142</v>
+        <v>173</v>
       </c>
       <c r="C15" t="n">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -5304,18 +5314,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>عصير تفاح (25)</t>
+          <t>قهوة</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>198</v>
+        <v>89</v>
       </c>
       <c r="C16" t="n">
-        <v>188</v>
+        <v>86</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -5332,14 +5342,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>أرز</t>
+          <t>مشروب طاقة</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>64</v>
+        <v>159</v>
       </c>
       <c r="C17" t="n">
-        <v>58</v>
+        <v>154</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -5360,18 +5370,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>سمنة</t>
+          <t>عصير برتقال (14)</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>79</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>76</v>
+        <v>17</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -5388,18 +5398,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>سكر (13)</t>
+          <t>عصير تفاح (15)</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="C19" t="n">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -5416,18 +5426,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>فول (28)</t>
+          <t>كاكاو (19)</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="C20" t="n">
-        <v>26</v>
+        <v>145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -5444,18 +5454,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>جبنة رومي</t>
+          <t>شاي (21)</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>87</v>
+        <v>183</v>
       </c>
       <c r="C21" t="n">
-        <v>79</v>
+        <v>175</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -5556,7 +5566,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5664,6 +5674,18 @@
       <c r="B9" t="inlineStr">
         <is>
           <t>https://instagram.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>صورة صفحة حول</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>images/about_icon.jpg</t>
         </is>
       </c>
     </row>
@@ -5720,12 +5742,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>219</v>
+        <v>53</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -5746,9 +5768,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>120</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>92</v>
+      </c>
+      <c r="C3" t="n">
+        <v>87</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -5772,7 +5796,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
@@ -5798,12 +5822,14 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>137</v>
-      </c>
-      <c r="C5" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="C5" t="n">
+        <v>77</v>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -5824,14 +5850,14 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>169</v>
+        <v>249</v>
       </c>
       <c r="C6" t="n">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -5852,7 +5878,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
@@ -5878,12 +5904,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>57</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
+        <v>49</v>
+      </c>
+      <c r="C8" t="n">
+        <v>40</v>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -5904,14 +5932,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>46</v>
-      </c>
-      <c r="C9" t="n">
-        <v>41</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -5932,14 +5958,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>77</v>
-      </c>
-      <c r="C10" t="n">
-        <v>69</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -5960,12 +5984,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5986,12 +6010,14 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>139</v>
-      </c>
-      <c r="C12" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="C12" t="n">
+        <v>24</v>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6012,7 +6038,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>197</v>
+        <v>250</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
@@ -6038,11 +6064,9 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
-      </c>
-      <c r="C14" t="n">
-        <v>8</v>
-      </c>
+        <v>242</v>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -6066,12 +6090,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>95</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>136</v>
+      </c>
+      <c r="C15" t="n">
+        <v>131</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6092,7 +6118,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
@@ -6118,12 +6144,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58</v>
+        <v>184</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6144,12 +6170,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>188</v>
+        <v>23</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -6170,11 +6196,9 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>34</v>
-      </c>
-      <c r="C19" t="n">
-        <v>26</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -6198,12 +6222,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>70</v>
+        <v>151</v>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -6224,12 +6248,12 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -6250,12 +6274,12 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>162</v>
+        <v>144</v>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -6276,14 +6300,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>57</v>
+        <v>171</v>
       </c>
       <c r="C23" t="n">
-        <v>52</v>
+        <v>161</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -6304,10 +6328,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>163</v>
+        <v>31</v>
       </c>
       <c r="C24" t="n">
-        <v>159</v>
+        <v>23</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -6332,12 +6356,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>102</v>
+        <v>41</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -6358,12 +6382,12 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>61</v>
+        <v>170</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -6384,11 +6408,9 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>65</v>
-      </c>
-      <c r="C27" t="n">
-        <v>59</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -6412,9 +6434,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>130</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>66</v>
+      </c>
+      <c r="C28" t="n">
+        <v>60</v>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -6438,7 +6462,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>51</v>
+        <v>208</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -6464,12 +6488,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>96</v>
-      </c>
-      <c r="C30" t="inlineStr"/>
+        <v>129</v>
+      </c>
+      <c r="C30" t="n">
+        <v>123</v>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -6490,11 +6516,9 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>167</v>
-      </c>
-      <c r="C31" t="n">
-        <v>160</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -6564,9 +6588,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>177</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="C2" t="n">
+        <v>39</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>عبوة</t>
@@ -6590,12 +6616,12 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>245</v>
+        <v>151</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -6616,14 +6642,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>250</v>
-      </c>
-      <c r="C4" t="n">
-        <v>240</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -6644,11 +6668,9 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>155</v>
-      </c>
-      <c r="C5" t="n">
-        <v>149</v>
-      </c>
+        <v>175</v>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -6672,14 +6694,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>171</v>
-      </c>
-      <c r="C6" t="n">
-        <v>164</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -6700,7 +6720,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>215</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
@@ -6726,14 +6746,14 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>43</v>
+        <v>103</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>98</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -6754,14 +6774,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>95</v>
-      </c>
-      <c r="C9" t="n">
-        <v>91</v>
-      </c>
+        <v>72</v>
+      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -6782,9 +6800,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>232</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
+        <v>33</v>
+      </c>
+      <c r="C10" t="n">
+        <v>31</v>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -6808,12 +6828,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>206</v>
+        <v>187</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -6834,14 +6854,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
-      </c>
-      <c r="C12" t="n">
-        <v>10</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -6862,12 +6880,12 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -6888,12 +6906,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>206</v>
-      </c>
-      <c r="C14" t="inlineStr"/>
+        <v>221</v>
+      </c>
+      <c r="C14" t="n">
+        <v>214</v>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6914,12 +6934,12 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>81</v>
+        <v>231</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6940,12 +6960,12 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6966,12 +6986,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67</v>
+        <v>162</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -6992,12 +7012,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>175</v>
+        <v>42</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7018,14 +7038,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>246</v>
-      </c>
-      <c r="C19" t="n">
-        <v>237</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7046,11 +7064,9 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>74</v>
-      </c>
-      <c r="C20" t="n">
-        <v>70</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -7074,12 +7090,12 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>237</v>
+        <v>110</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -7100,10 +7116,10 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="C22" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -7128,14 +7144,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>244</v>
-      </c>
-      <c r="C23" t="n">
-        <v>234</v>
-      </c>
+        <v>199</v>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -7156,9 +7170,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>91</v>
-      </c>
-      <c r="C24" t="inlineStr"/>
+        <v>149</v>
+      </c>
+      <c r="C24" t="n">
+        <v>145</v>
+      </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -7182,12 +7198,14 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>150</v>
-      </c>
-      <c r="C25" t="inlineStr"/>
+        <v>197</v>
+      </c>
+      <c r="C25" t="n">
+        <v>187</v>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -7208,12 +7226,14 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>17</v>
-      </c>
-      <c r="C26" t="inlineStr"/>
+        <v>84</v>
+      </c>
+      <c r="C26" t="n">
+        <v>76</v>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -7234,12 +7254,12 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>190</v>
+        <v>119</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -7260,12 +7280,12 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>249</v>
+        <v>110</v>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -7286,12 +7306,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>182</v>
+        <v>212</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -7312,14 +7332,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="C30" t="n">
-        <v>127</v>
+        <v>164</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -7340,12 +7360,12 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>74</v>
+        <v>147</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -7412,12 +7432,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43</v>
-      </c>
-      <c r="C2" t="inlineStr"/>
+        <v>189</v>
+      </c>
+      <c r="C2" t="n">
+        <v>179</v>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -7438,9 +7460,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>138</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>89</v>
+      </c>
+      <c r="C3" t="n">
+        <v>86</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>كيلو</t>
@@ -7464,12 +7488,12 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>235</v>
+        <v>105</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -7490,7 +7514,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
@@ -7516,12 +7540,12 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -7542,7 +7566,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>120</v>
+        <v>47</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
@@ -7568,12 +7592,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>63</v>
+        <v>164</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -7594,14 +7618,14 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>183</v>
+        <v>159</v>
       </c>
       <c r="C9" t="n">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -7622,7 +7646,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>224</v>
+        <v>124</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
@@ -7648,12 +7672,12 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>212</v>
+        <v>66</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -7674,12 +7698,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>116</v>
+        <v>38</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -7700,14 +7724,12 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>55</v>
-      </c>
-      <c r="C13" t="n">
-        <v>47</v>
-      </c>
+        <v>116</v>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -7728,7 +7750,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>161</v>
+        <v>73</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
@@ -7754,14 +7776,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -7782,14 +7804,14 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="C16" t="n">
-        <v>196</v>
+        <v>37</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7810,12 +7832,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84</v>
+        <v>98</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7836,12 +7858,12 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>119</v>
+        <v>40</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7862,12 +7884,12 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -7888,12 +7910,14 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>205</v>
-      </c>
-      <c r="C20" t="inlineStr"/>
+        <v>153</v>
+      </c>
+      <c r="C20" t="n">
+        <v>145</v>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -7914,14 +7938,12 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>142</v>
-      </c>
-      <c r="C21" t="n">
-        <v>140</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -7942,12 +7964,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>126</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>183</v>
+      </c>
+      <c r="C22" t="n">
+        <v>175</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -7968,12 +7992,14 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>35</v>
-      </c>
-      <c r="C23" t="inlineStr"/>
+        <v>38</v>
+      </c>
+      <c r="C23" t="n">
+        <v>33</v>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -7994,12 +8020,12 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -8020,7 +8046,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>39</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
@@ -8046,14 +8072,12 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>198</v>
-      </c>
-      <c r="C26" t="n">
-        <v>188</v>
-      </c>
+        <v>130</v>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -8074,12 +8098,12 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>41</v>
+        <v>145</v>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -8100,12 +8124,14 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>159</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>75</v>
+      </c>
+      <c r="C28" t="n">
+        <v>68</v>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8126,7 +8152,7 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
@@ -8152,12 +8178,12 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -8178,9 +8204,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>202</v>
-      </c>
-      <c r="C31" t="inlineStr"/>
+        <v>34</v>
+      </c>
+      <c r="C31" t="n">
+        <v>25</v>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
           <t>لتر</t>
@@ -8250,14 +8278,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>64</v>
-      </c>
-      <c r="C2" t="n">
-        <v>58</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -8278,12 +8304,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>127</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="C3" t="n">
+        <v>52</v>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -8304,12 +8332,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>214</v>
-      </c>
-      <c r="C4" t="inlineStr"/>
+        <v>164</v>
+      </c>
+      <c r="C4" t="n">
+        <v>155</v>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -8330,12 +8360,12 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>202</v>
+        <v>91</v>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -8356,11 +8386,9 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>79</v>
-      </c>
-      <c r="C6" t="n">
-        <v>76</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
           <t>قطعة</t>
@@ -8384,14 +8412,12 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>134</v>
-      </c>
-      <c r="C7" t="n">
-        <v>127</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -8412,12 +8438,12 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>164</v>
+        <v>68</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -8438,12 +8464,12 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>58</v>
+        <v>40</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -8464,12 +8490,12 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>137</v>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -8490,7 +8516,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>222</v>
+        <v>51</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
@@ -8516,14 +8542,12 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>168</v>
-      </c>
-      <c r="C12" t="n">
-        <v>163</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -8544,12 +8568,12 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -8570,14 +8594,14 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>135</v>
+        <v>69</v>
       </c>
       <c r="C14" t="n">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -8598,12 +8622,14 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>128</v>
-      </c>
-      <c r="C15" t="inlineStr"/>
+        <v>78</v>
+      </c>
+      <c r="C15" t="n">
+        <v>69</v>
+      </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -8624,12 +8650,12 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>108</v>
+        <v>231</v>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -8650,12 +8676,12 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>99</v>
+        <v>155</v>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -8676,7 +8702,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
@@ -8707,7 +8733,7 @@
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8728,14 +8754,12 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>134</v>
-      </c>
-      <c r="C20" t="n">
-        <v>132</v>
-      </c>
+        <v>70</v>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8756,7 +8780,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>17</v>
+        <v>136</v>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
@@ -8782,12 +8806,14 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>133</v>
-      </c>
-      <c r="C22" t="inlineStr"/>
+        <v>125</v>
+      </c>
+      <c r="C22" t="n">
+        <v>119</v>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -8808,12 +8834,12 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>عبوة</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -8834,10 +8860,10 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>134</v>
+        <v>250</v>
       </c>
       <c r="C24" t="n">
-        <v>132</v>
+        <v>244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -8862,12 +8888,12 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -8888,12 +8914,12 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>كيلو</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -8914,14 +8940,12 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>95</v>
-      </c>
-      <c r="C27" t="n">
-        <v>86</v>
-      </c>
+        <v>240</v>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -8942,12 +8966,14 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>249</v>
-      </c>
-      <c r="C28" t="inlineStr"/>
+        <v>174</v>
+      </c>
+      <c r="C28" t="n">
+        <v>165</v>
+      </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>قطعة</t>
+          <t>لتر</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -8968,14 +8994,12 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28</v>
-      </c>
-      <c r="C29" t="n">
-        <v>26</v>
-      </c>
+        <v>152</v>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>لتر</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -8996,14 +9020,14 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>123</v>
+        <v>162</v>
       </c>
       <c r="C30" t="n">
-        <v>120</v>
+        <v>152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>قطعة</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -9024,12 +9048,12 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>132</v>
+        <v>189</v>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>عبوة</t>
+          <t>كيلو</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -26,19 +26,199 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="329">
   <si>
+    <t>الاسم</t>
+  </si>
+  <si>
     <t>صورة</t>
   </si>
   <si>
+    <t>السعر الأساسي</t>
+  </si>
+  <si>
+    <t>القسم_المستهدف</t>
+  </si>
+  <si>
+    <t>السعر بعد الخصم</t>
+  </si>
+  <si>
+    <t>images/slider_1.jpg</t>
+  </si>
+  <si>
+    <t>الوحدة</t>
+  </si>
+  <si>
+    <t>متوفر</t>
+  </si>
+  <si>
+    <t>الفواكه والخضروات</t>
+  </si>
+  <si>
+    <t>خيار</t>
+  </si>
+  <si>
+    <t>images/slider_2.jpg</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات</t>
+  </si>
+  <si>
+    <t>لتر</t>
+  </si>
+  <si>
+    <t>images/placeholder.png</t>
+  </si>
+  <si>
+    <t>المشروبات</t>
+  </si>
+  <si>
+    <t>نعم</t>
+  </si>
+  <si>
+    <t>موز</t>
+  </si>
+  <si>
+    <t>البقالة</t>
+  </si>
+  <si>
+    <t>كيلو</t>
+  </si>
+  <si>
+    <t>الألبان</t>
+  </si>
+  <si>
+    <t>المخبوزات</t>
+  </si>
+  <si>
+    <t>خيار (14)</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي</t>
+  </si>
+  <si>
+    <t>بطاطس (22)</t>
+  </si>
+  <si>
+    <t>منظفات</t>
+  </si>
+  <si>
+    <t>بصل (23)</t>
+  </si>
+  <si>
+    <t>قطعة</t>
+  </si>
+  <si>
+    <t>موز (27)</t>
+  </si>
+  <si>
+    <t>عنب (29)</t>
+  </si>
+  <si>
+    <t>لب سوبر</t>
+  </si>
+  <si>
+    <t>عبوة</t>
+  </si>
+  <si>
+    <t>شيبسي</t>
+  </si>
+  <si>
+    <t>مقرمشات</t>
+  </si>
+  <si>
+    <t>سوداني (13)</t>
+  </si>
+  <si>
+    <t>سوداني (23)</t>
+  </si>
+  <si>
+    <t>لوز (24)</t>
+  </si>
+  <si>
+    <t>مقرمشات (29)</t>
+  </si>
+  <si>
+    <t>قهوة</t>
+  </si>
+  <si>
+    <t>مشروب طاقة</t>
+  </si>
+  <si>
+    <t>عصير برتقال (14)</t>
+  </si>
+  <si>
+    <t>عصير تفاح (15)</t>
+  </si>
+  <si>
+    <t>كاكاو (19)</t>
+  </si>
+  <si>
+    <t>شاي (21)</t>
+  </si>
+  <si>
+    <t>رقم_الصفحة</t>
+  </si>
+  <si>
+    <t>images/offer_page_1.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_2.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_3.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_4.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_5.jpg</t>
+  </si>
+  <si>
+    <t>الإعداد</t>
+  </si>
+  <si>
+    <t>القيمة</t>
+  </si>
+  <si>
+    <t>أيقونة الموقع</t>
+  </si>
+  <si>
+    <t>images/favicon.jpg</t>
+  </si>
+  <si>
+    <t>رقم الواتساب</t>
+  </si>
+  <si>
+    <t>01063883209</t>
+  </si>
+  <si>
     <t>مكان_البانر</t>
   </si>
   <si>
-    <t>القسم_المستهدف</t>
-  </si>
-  <si>
-    <t>images/slider_1.jpg</t>
-  </si>
-  <si>
-    <t>الفواكه والخضروات</t>
+    <t>رابط الواتساب</t>
+  </si>
+  <si>
+    <t>https://wa.me/201063883209</t>
+  </si>
+  <si>
+    <t>صورة كيو آر الواتساب</t>
+  </si>
+  <si>
+    <t>images/qr_wa.jpg</t>
+  </si>
+  <si>
+    <t>رابط الموقع</t>
+  </si>
+  <si>
+    <t>https://abdelazim17.github.io/trolley-market</t>
+  </si>
+  <si>
+    <t>صورة كيو آر الموقع</t>
+  </si>
+  <si>
+    <t>images/qr_site.jpg</t>
   </si>
   <si>
     <t>رئيسي_علوي</t>
@@ -47,25 +227,31 @@
     <t>images/top_banner.jpg</t>
   </si>
   <si>
-    <t>images/slider_2.jpg</t>
+    <t>رابط فيسبوك</t>
+  </si>
+  <si>
+    <t>https://facebook.com</t>
   </si>
   <si>
     <t>مقسم_يمين</t>
   </si>
   <si>
-    <t>التسالي والمكسرات</t>
+    <t>رابط إنستجرام</t>
+  </si>
+  <si>
+    <t>https://instagram.com</t>
   </si>
   <si>
     <t>images/split1.jpg</t>
   </si>
   <si>
-    <t>المشروبات</t>
+    <t>صورة صفحة حول</t>
   </si>
   <si>
     <t>مقسم_يسار</t>
   </si>
   <si>
-    <t>البقالة</t>
+    <t>images/about_icon.jpg</t>
   </si>
   <si>
     <t>images/split2.jpg</t>
@@ -74,495 +260,309 @@
     <t>رئيسي_ثابت</t>
   </si>
   <si>
-    <t>الألبان</t>
-  </si>
-  <si>
-    <t>الاسم</t>
-  </si>
-  <si>
-    <t>رقم_الصفحة</t>
-  </si>
-  <si>
-    <t>المخبوزات</t>
-  </si>
-  <si>
     <t>images/static_banner.jpg</t>
   </si>
   <si>
-    <t>التوابل والبهارات</t>
-  </si>
-  <si>
-    <t>الحلويات والكاندي</t>
-  </si>
-  <si>
-    <t>السعر الأساسي</t>
-  </si>
-  <si>
-    <t>منظفات</t>
-  </si>
-  <si>
-    <t>السعر بعد الخصم</t>
-  </si>
-  <si>
-    <t>images/offer_page_1.jpg</t>
-  </si>
-  <si>
-    <t>الوحدة</t>
-  </si>
-  <si>
-    <t>images/offer_page_2.jpg</t>
-  </si>
-  <si>
-    <t>متوفر</t>
-  </si>
-  <si>
-    <t>images/offer_page_3.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_4.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_5.jpg</t>
-  </si>
-  <si>
-    <t>خيار</t>
-  </si>
-  <si>
-    <t>لتر</t>
-  </si>
-  <si>
-    <t>images/placeholder.png</t>
-  </si>
-  <si>
-    <t>نعم</t>
-  </si>
-  <si>
-    <t>موز</t>
-  </si>
-  <si>
-    <t>كيلو</t>
-  </si>
-  <si>
-    <t>خيار (14)</t>
-  </si>
-  <si>
-    <t>بطاطس (22)</t>
-  </si>
-  <si>
-    <t>بصل (23)</t>
-  </si>
-  <si>
-    <t>قطعة</t>
-  </si>
-  <si>
-    <t>موز (27)</t>
-  </si>
-  <si>
-    <t>عنب (29)</t>
-  </si>
-  <si>
-    <t>لب سوبر</t>
-  </si>
-  <si>
-    <t>عبوة</t>
-  </si>
-  <si>
-    <t>شيبسي</t>
-  </si>
-  <si>
-    <t>مقرمشات</t>
-  </si>
-  <si>
-    <t>سوداني (13)</t>
-  </si>
-  <si>
-    <t>سوداني (23)</t>
-  </si>
-  <si>
-    <t>لوز (24)</t>
-  </si>
-  <si>
-    <t>مقرمشات (29)</t>
-  </si>
-  <si>
-    <t>قهوة</t>
-  </si>
-  <si>
-    <t>مشروب طاقة</t>
-  </si>
-  <si>
-    <t>عصير برتقال (14)</t>
-  </si>
-  <si>
-    <t>عصير تفاح (15)</t>
-  </si>
-  <si>
-    <t>كاكاو (19)</t>
-  </si>
-  <si>
-    <t>شاي (21)</t>
-  </si>
-  <si>
-    <t>الإعداد</t>
-  </si>
-  <si>
-    <t>القيمة</t>
-  </si>
-  <si>
-    <t>أيقونة الموقع</t>
-  </si>
-  <si>
-    <t>images/favicon.jpg</t>
-  </si>
-  <si>
-    <t>رقم الواتساب</t>
-  </si>
-  <si>
-    <t>01063883209</t>
-  </si>
-  <si>
-    <t>رابط الواتساب</t>
-  </si>
-  <si>
-    <t>https://wa.me/201063883209</t>
-  </si>
-  <si>
-    <t>صورة كيو آر الواتساب</t>
-  </si>
-  <si>
-    <t>images/qr_wa.jpg</t>
-  </si>
-  <si>
-    <t>رابط الموقع</t>
-  </si>
-  <si>
-    <t>https://abdelazim17.github.io/trolley-market</t>
-  </si>
-  <si>
-    <t>صورة كيو آر الموقع</t>
-  </si>
-  <si>
-    <t>images/qr_site.jpg</t>
-  </si>
-  <si>
-    <t>رابط فيسبوك</t>
-  </si>
-  <si>
-    <t>https://facebook.com</t>
-  </si>
-  <si>
-    <t>رابط إنستجرام</t>
-  </si>
-  <si>
-    <t>https://instagram.com</t>
-  </si>
-  <si>
-    <t>صورة صفحة حول</t>
-  </si>
-  <si>
-    <t>images/about_icon.jpg</t>
-  </si>
-  <si>
     <t>طماطم</t>
   </si>
   <si>
+    <t>لب سوري</t>
+  </si>
+  <si>
+    <t>سوداني</t>
+  </si>
+  <si>
+    <t>لوز</t>
+  </si>
+  <si>
+    <t>عين جمل</t>
+  </si>
+  <si>
+    <t>كاجو</t>
+  </si>
+  <si>
+    <t>فشار</t>
+  </si>
+  <si>
+    <t>فستق</t>
+  </si>
+  <si>
+    <t>لب سوبر (11)</t>
+  </si>
+  <si>
+    <t>لب سوري (12)</t>
+  </si>
+  <si>
+    <t>لوز (14)</t>
+  </si>
+  <si>
+    <t>عين جمل (15)</t>
+  </si>
+  <si>
+    <t>كاجو (16)</t>
+  </si>
+  <si>
+    <t>شيبسي (17)</t>
+  </si>
+  <si>
+    <t>شاي</t>
+  </si>
+  <si>
+    <t>فشار (18)</t>
+  </si>
+  <si>
+    <t>مقرمشات (19)</t>
+  </si>
+  <si>
+    <t>فستق (20)</t>
+  </si>
+  <si>
+    <t>لب سوبر (21)</t>
+  </si>
+  <si>
+    <t>أرز</t>
+  </si>
+  <si>
+    <t>لب سوري (22)</t>
+  </si>
+  <si>
+    <t>مكرونة</t>
+  </si>
+  <si>
+    <t>سكر</t>
+  </si>
+  <si>
+    <t>زيت</t>
+  </si>
+  <si>
+    <t>نسكافيه</t>
+  </si>
+  <si>
+    <t>سمنة</t>
+  </si>
+  <si>
+    <t>عين جمل (25)</t>
+  </si>
+  <si>
     <t>بطاطس</t>
   </si>
   <si>
+    <t>صلصة</t>
+  </si>
+  <si>
+    <t>عصير برتقال</t>
+  </si>
+  <si>
+    <t>كاجو (26)</t>
+  </si>
+  <si>
+    <t>تونة</t>
+  </si>
+  <si>
+    <t>عصير تفاح</t>
+  </si>
+  <si>
+    <t>فول</t>
+  </si>
+  <si>
+    <t>شيبسي (27)</t>
+  </si>
+  <si>
+    <t>كولا</t>
+  </si>
+  <si>
     <t>بصل</t>
   </si>
   <si>
+    <t>عدس</t>
+  </si>
+  <si>
+    <t>فشار (28)</t>
+  </si>
+  <si>
+    <t>مياه معدنية</t>
+  </si>
+  <si>
+    <t>دقيق</t>
+  </si>
+  <si>
+    <t>أرز (11)</t>
+  </si>
+  <si>
+    <t>مكرونة (12)</t>
+  </si>
+  <si>
     <t>جزر</t>
   </si>
   <si>
+    <t>كاكاو</t>
+  </si>
+  <si>
+    <t>فستق (30)</t>
+  </si>
+  <si>
+    <t>سكر (13)</t>
+  </si>
+  <si>
+    <t>نعناع</t>
+  </si>
+  <si>
     <t>تفاح</t>
   </si>
   <si>
+    <t>زيت (14)</t>
+  </si>
+  <si>
+    <t>شاي (11)</t>
+  </si>
+  <si>
+    <t>سمنة (15)</t>
+  </si>
+  <si>
+    <t>قهوة (12)</t>
+  </si>
+  <si>
+    <t>صلصة (16)</t>
+  </si>
+  <si>
+    <t>نسكافيه (13)</t>
+  </si>
+  <si>
     <t>برتقال</t>
   </si>
   <si>
+    <t>تونة (17)</t>
+  </si>
+  <si>
+    <t>فول (18)</t>
+  </si>
+  <si>
     <t>عنب</t>
   </si>
   <si>
+    <t>عدس (19)</t>
+  </si>
+  <si>
+    <t>كولا (16)</t>
+  </si>
+  <si>
     <t>مانجو</t>
   </si>
   <si>
+    <t>دقيق (20)</t>
+  </si>
+  <si>
+    <t>مياه معدنية (17)</t>
+  </si>
+  <si>
+    <t>أرز (21)</t>
+  </si>
+  <si>
+    <t>مكرونة (22)</t>
+  </si>
+  <si>
     <t>طماطم (11)</t>
   </si>
   <si>
+    <t>مشروب طاقة (18)</t>
+  </si>
+  <si>
+    <t>سكر (23)</t>
+  </si>
+  <si>
     <t>بطاطس (12)</t>
   </si>
   <si>
+    <t>زيت (24)</t>
+  </si>
+  <si>
     <t>بصل (13)</t>
   </si>
   <si>
+    <t>نعناع (20)</t>
+  </si>
+  <si>
+    <t>سمنة (25)</t>
+  </si>
+  <si>
+    <t>صلصة (26)</t>
+  </si>
+  <si>
+    <t>قهوة (22)</t>
+  </si>
+  <si>
+    <t>تونة (27)</t>
+  </si>
+  <si>
     <t>جزر (15)</t>
   </si>
   <si>
+    <t>نسكافيه (23)</t>
+  </si>
+  <si>
+    <t>فول (28)</t>
+  </si>
+  <si>
+    <t>عصير برتقال (24)</t>
+  </si>
+  <si>
     <t>تفاح (16)</t>
   </si>
   <si>
+    <t>عدس (29)</t>
+  </si>
+  <si>
+    <t>عصير تفاح (25)</t>
+  </si>
+  <si>
     <t>موز (17)</t>
   </si>
   <si>
+    <t>دقيق (30)</t>
+  </si>
+  <si>
+    <t>كولا (26)</t>
+  </si>
+  <si>
+    <t>مياه معدنية (27)</t>
+  </si>
+  <si>
     <t>برتقال (18)</t>
   </si>
   <si>
+    <t>مشروب طاقة (28)</t>
+  </si>
+  <si>
     <t>عنب (19)</t>
   </si>
   <si>
-    <t>لب سوري</t>
+    <t>كاكاو (29)</t>
+  </si>
+  <si>
+    <t>نعناع (30)</t>
   </si>
   <si>
     <t>مانجو (20)</t>
   </si>
   <si>
-    <t>سوداني</t>
-  </si>
-  <si>
     <t>طماطم (21)</t>
   </si>
   <si>
-    <t>لوز</t>
-  </si>
-  <si>
-    <t>عين جمل</t>
-  </si>
-  <si>
-    <t>كاجو</t>
-  </si>
-  <si>
     <t>خيار (24)</t>
   </si>
   <si>
     <t>جزر (25)</t>
   </si>
   <si>
-    <t>فشار</t>
-  </si>
-  <si>
     <t>تفاح (26)</t>
   </si>
   <si>
-    <t>فستق</t>
-  </si>
-  <si>
     <t>برتقال (28)</t>
   </si>
   <si>
-    <t>لب سوبر (11)</t>
-  </si>
-  <si>
-    <t>لب سوري (12)</t>
-  </si>
-  <si>
     <t>مانجو (30)</t>
   </si>
   <si>
-    <t>لوز (14)</t>
-  </si>
-  <si>
-    <t>شاي</t>
-  </si>
-  <si>
-    <t>عين جمل (15)</t>
-  </si>
-  <si>
-    <t>كاجو (16)</t>
-  </si>
-  <si>
-    <t>شيبسي (17)</t>
-  </si>
-  <si>
-    <t>فشار (18)</t>
-  </si>
-  <si>
-    <t>مقرمشات (19)</t>
-  </si>
-  <si>
-    <t>فستق (20)</t>
-  </si>
-  <si>
-    <t>لب سوبر (21)</t>
-  </si>
-  <si>
-    <t>نسكافيه</t>
-  </si>
-  <si>
-    <t>لب سوري (22)</t>
-  </si>
-  <si>
-    <t>عصير برتقال</t>
-  </si>
-  <si>
-    <t>عصير تفاح</t>
-  </si>
-  <si>
-    <t>كولا</t>
-  </si>
-  <si>
-    <t>مياه معدنية</t>
-  </si>
-  <si>
-    <t>عين جمل (25)</t>
-  </si>
-  <si>
-    <t>كاجو (26)</t>
-  </si>
-  <si>
-    <t>كاكاو</t>
-  </si>
-  <si>
-    <t>شيبسي (27)</t>
-  </si>
-  <si>
-    <t>نعناع</t>
-  </si>
-  <si>
-    <t>شاي (11)</t>
-  </si>
-  <si>
-    <t>فشار (28)</t>
-  </si>
-  <si>
-    <t>قهوة (12)</t>
-  </si>
-  <si>
-    <t>نسكافيه (13)</t>
-  </si>
-  <si>
-    <t>فستق (30)</t>
-  </si>
-  <si>
-    <t>كولا (16)</t>
-  </si>
-  <si>
-    <t>مياه معدنية (17)</t>
-  </si>
-  <si>
-    <t>مشروب طاقة (18)</t>
-  </si>
-  <si>
-    <t>نعناع (20)</t>
-  </si>
-  <si>
-    <t>قهوة (22)</t>
-  </si>
-  <si>
-    <t>نسكافيه (23)</t>
-  </si>
-  <si>
-    <t>عصير برتقال (24)</t>
-  </si>
-  <si>
-    <t>عصير تفاح (25)</t>
-  </si>
-  <si>
-    <t>كولا (26)</t>
-  </si>
-  <si>
-    <t>مياه معدنية (27)</t>
-  </si>
-  <si>
-    <t>مشروب طاقة (28)</t>
-  </si>
-  <si>
-    <t>كاكاو (29)</t>
-  </si>
-  <si>
-    <t>نعناع (30)</t>
-  </si>
-  <si>
-    <t>أرز</t>
-  </si>
-  <si>
-    <t>مكرونة</t>
-  </si>
-  <si>
-    <t>سكر</t>
-  </si>
-  <si>
-    <t>زيت</t>
-  </si>
-  <si>
-    <t>سمنة</t>
-  </si>
-  <si>
-    <t>صلصة</t>
-  </si>
-  <si>
-    <t>تونة</t>
-  </si>
-  <si>
-    <t>فول</t>
-  </si>
-  <si>
-    <t>عدس</t>
-  </si>
-  <si>
-    <t>دقيق</t>
-  </si>
-  <si>
-    <t>أرز (11)</t>
-  </si>
-  <si>
-    <t>مكرونة (12)</t>
-  </si>
-  <si>
-    <t>سكر (13)</t>
-  </si>
-  <si>
-    <t>زيت (14)</t>
-  </si>
-  <si>
-    <t>سمنة (15)</t>
-  </si>
-  <si>
-    <t>صلصة (16)</t>
-  </si>
-  <si>
-    <t>تونة (17)</t>
-  </si>
-  <si>
-    <t>فول (18)</t>
-  </si>
-  <si>
-    <t>عدس (19)</t>
-  </si>
-  <si>
-    <t>دقيق (20)</t>
-  </si>
-  <si>
-    <t>أرز (21)</t>
-  </si>
-  <si>
-    <t>مكرونة (22)</t>
-  </si>
-  <si>
-    <t>سكر (23)</t>
-  </si>
-  <si>
-    <t>زيت (24)</t>
-  </si>
-  <si>
-    <t>سمنة (25)</t>
-  </si>
-  <si>
-    <t>صلصة (26)</t>
-  </si>
-  <si>
-    <t>تونة (27)</t>
-  </si>
-  <si>
-    <t>فول (28)</t>
-  </si>
-  <si>
-    <t>عدس (29)</t>
-  </si>
-  <si>
-    <t>دقيق (30)</t>
-  </si>
-  <si>
     <t>لبن كامل الدسم</t>
   </si>
   <si>
@@ -608,90 +608,90 @@
     <t>قشطة (15)</t>
   </si>
   <si>
+    <t>عيش فينو</t>
+  </si>
+  <si>
     <t>زبدة (16)</t>
   </si>
   <si>
-    <t>عيش فينو</t>
+    <t>عيش بلدي</t>
   </si>
   <si>
     <t>جبنة شيدر (17)</t>
   </si>
   <si>
-    <t>عيش بلدي</t>
+    <t>باتيه</t>
+  </si>
+  <si>
+    <t>كرواسون</t>
   </si>
   <si>
     <t>جبنة نستو (18)</t>
   </si>
   <si>
-    <t>باتيه</t>
-  </si>
-  <si>
-    <t>كرواسون</t>
+    <t>بقسماط</t>
   </si>
   <si>
     <t>لبن رايب (19)</t>
   </si>
   <si>
+    <t>توست أبيض</t>
+  </si>
+  <si>
     <t>سمن بلدي (20)</t>
   </si>
   <si>
     <t>لبن كامل الدسم (21)</t>
   </si>
   <si>
+    <t>توست أسمر</t>
+  </si>
+  <si>
     <t>جبنة بيضاء (22)</t>
   </si>
   <si>
-    <t>بقسماط</t>
+    <t>فطير</t>
   </si>
   <si>
     <t>جبنة رومي (23)</t>
   </si>
   <si>
-    <t>توست أبيض</t>
+    <t>كيك</t>
   </si>
   <si>
     <t>زبادي (24)</t>
   </si>
   <si>
-    <t>توست أسمر</t>
+    <t>بسكويت</t>
   </si>
   <si>
     <t>قشطة (25)</t>
   </si>
   <si>
-    <t>فطير</t>
-  </si>
-  <si>
-    <t>كيك</t>
+    <t>عيش فينو (11)</t>
   </si>
   <si>
     <t>زبدة (26)</t>
   </si>
   <si>
-    <t>بسكويت</t>
+    <t>عيش بلدي (12)</t>
   </si>
   <si>
     <t>جبنة شيدر (27)</t>
   </si>
   <si>
-    <t>عيش فينو (11)</t>
+    <t>باتيه (13)</t>
   </si>
   <si>
     <t>جبنة نستو (28)</t>
   </si>
   <si>
-    <t>عيش بلدي (12)</t>
-  </si>
-  <si>
-    <t>باتيه (13)</t>
+    <t>كرواسون (14)</t>
   </si>
   <si>
     <t>لبن رايب (29)</t>
   </si>
   <si>
-    <t>كرواسون (14)</t>
-  </si>
-  <si>
     <t>سمن بلدي (30)</t>
   </si>
   <si>
@@ -707,310 +707,310 @@
     <t>فطير (18)</t>
   </si>
   <si>
+    <t>كيك (19)</t>
+  </si>
+  <si>
+    <t>بسكويت (20)</t>
+  </si>
+  <si>
+    <t>عيش فينو (21)</t>
+  </si>
+  <si>
+    <t>عيش بلدي (22)</t>
+  </si>
+  <si>
+    <t>باتيه (23)</t>
+  </si>
+  <si>
+    <t>كرواسون (24)</t>
+  </si>
+  <si>
+    <t>بقسماط (25)</t>
+  </si>
+  <si>
+    <t>توست أبيض (26)</t>
+  </si>
+  <si>
+    <t>توست أسمر (27)</t>
+  </si>
+  <si>
+    <t>فطير (28)</t>
+  </si>
+  <si>
+    <t>كيك (29)</t>
+  </si>
+  <si>
+    <t>بسكويت (30)</t>
+  </si>
+  <si>
     <t>كمون</t>
   </si>
   <si>
-    <t>كيك (19)</t>
-  </si>
-  <si>
-    <t>بسكويت (20)</t>
-  </si>
-  <si>
     <t>فلفل أسود</t>
   </si>
   <si>
     <t>كركم</t>
   </si>
   <si>
-    <t>عيش فينو (21)</t>
-  </si>
-  <si>
     <t>كزبرة</t>
   </si>
   <si>
-    <t>عيش بلدي (22)</t>
-  </si>
-  <si>
     <t>بهارات مشكلة</t>
   </si>
   <si>
-    <t>باتيه (23)</t>
-  </si>
-  <si>
     <t>قرفة</t>
   </si>
   <si>
-    <t>كرواسون (24)</t>
-  </si>
-  <si>
     <t>حبهان</t>
   </si>
   <si>
-    <t>بقسماط (25)</t>
-  </si>
-  <si>
     <t>ورق لورا</t>
   </si>
   <si>
-    <t>توست أبيض (26)</t>
-  </si>
-  <si>
     <t>بابريكا</t>
   </si>
   <si>
-    <t>توست أسمر (27)</t>
+    <t>شوكولاتة</t>
+  </si>
+  <si>
+    <t>جيلي</t>
+  </si>
+  <si>
+    <t>كريم كراميل</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية</t>
+  </si>
+  <si>
+    <t>ملبن</t>
   </si>
   <si>
     <t>قرنفل</t>
   </si>
   <si>
-    <t>فطير (28)</t>
-  </si>
-  <si>
-    <t>كيك (29)</t>
+    <t>بسكويت شيكولاتة</t>
   </si>
   <si>
     <t>كمون (11)</t>
   </si>
   <si>
-    <t>بسكويت (30)</t>
+    <t>لبان</t>
   </si>
   <si>
     <t>فلفل أسود (12)</t>
   </si>
   <si>
+    <t>مربى</t>
+  </si>
+  <si>
     <t>كركم (13)</t>
   </si>
   <si>
+    <t>عسل نحل</t>
+  </si>
+  <si>
+    <t>كيك شوكولاتة</t>
+  </si>
+  <si>
     <t>كزبرة (14)</t>
   </si>
   <si>
+    <t>مسحوق غسيل</t>
+  </si>
+  <si>
+    <t>شوكولاتة (11)</t>
+  </si>
+  <si>
     <t>بهارات مشكلة (15)</t>
   </si>
   <si>
+    <t>صابون سائل</t>
+  </si>
+  <si>
     <t>قرفة (16)</t>
   </si>
   <si>
+    <t>جيلي (12)</t>
+  </si>
+  <si>
+    <t>كلور</t>
+  </si>
+  <si>
     <t>حبهان (17)</t>
   </si>
   <si>
+    <t>كريم كراميل (13)</t>
+  </si>
+  <si>
+    <t>معطر جو</t>
+  </si>
+  <si>
     <t>ورق لورا (18)</t>
   </si>
   <si>
+    <t>حلاوة طحينية (14)</t>
+  </si>
+  <si>
+    <t>ديتول</t>
+  </si>
+  <si>
+    <t>صابون وجه</t>
+  </si>
+  <si>
+    <t>ملبن (15)</t>
+  </si>
+  <si>
     <t>بابريكا (19)</t>
   </si>
   <si>
+    <t>شامبو</t>
+  </si>
+  <si>
+    <t>بسكويت شيكولاتة (16)</t>
+  </si>
+  <si>
     <t>قرنفل (20)</t>
   </si>
   <si>
+    <t>مناديل</t>
+  </si>
+  <si>
+    <t>لبان (17)</t>
+  </si>
+  <si>
     <t>كمون (21)</t>
   </si>
   <si>
+    <t>سلك مواعين</t>
+  </si>
+  <si>
+    <t>ملمع زجاج</t>
+  </si>
+  <si>
+    <t>مربى (18)</t>
+  </si>
+  <si>
     <t>فلفل أسود (22)</t>
   </si>
   <si>
+    <t>مسحوق غسيل (11)</t>
+  </si>
+  <si>
+    <t>عسل نحل (19)</t>
+  </si>
+  <si>
     <t>كركم (23)</t>
   </si>
   <si>
+    <t>صابون سائل (12)</t>
+  </si>
+  <si>
+    <t>كيك شوكولاتة (20)</t>
+  </si>
+  <si>
+    <t>كلور (13)</t>
+  </si>
+  <si>
+    <t>معطر جو (14)</t>
+  </si>
+  <si>
+    <t>شوكولاتة (21)</t>
+  </si>
+  <si>
+    <t>ديتول (15)</t>
+  </si>
+  <si>
+    <t>جيلي (22)</t>
+  </si>
+  <si>
+    <t>صابون وجه (16)</t>
+  </si>
+  <si>
+    <t>شامبو (17)</t>
+  </si>
+  <si>
+    <t>كريم كراميل (23)</t>
+  </si>
+  <si>
+    <t>مناديل (18)</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية (24)</t>
+  </si>
+  <si>
+    <t>سلك مواعين (19)</t>
+  </si>
+  <si>
+    <t>ملبن (25)</t>
+  </si>
+  <si>
+    <t>بسكويت شيكولاتة (26)</t>
+  </si>
+  <si>
+    <t>ملمع زجاج (20)</t>
+  </si>
+  <si>
+    <t>مسحوق غسيل (21)</t>
+  </si>
+  <si>
+    <t>لبان (27)</t>
+  </si>
+  <si>
+    <t>صابون سائل (22)</t>
+  </si>
+  <si>
+    <t>مربى (28)</t>
+  </si>
+  <si>
     <t>كزبرة (24)</t>
   </si>
   <si>
+    <t>عسل نحل (29)</t>
+  </si>
+  <si>
+    <t>كلور (23)</t>
+  </si>
+  <si>
+    <t>كيك شوكولاتة (30)</t>
+  </si>
+  <si>
     <t>بهارات مشكلة (25)</t>
   </si>
   <si>
+    <t>معطر جو (24)</t>
+  </si>
+  <si>
     <t>قرفة (26)</t>
   </si>
   <si>
+    <t>ديتول (25)</t>
+  </si>
+  <si>
     <t>حبهان (27)</t>
   </si>
   <si>
+    <t>صابون وجه (26)</t>
+  </si>
+  <si>
     <t>ورق لورا (28)</t>
   </si>
   <si>
+    <t>شامبو (27)</t>
+  </si>
+  <si>
     <t>بابريكا (29)</t>
   </si>
   <si>
+    <t>مناديل (28)</t>
+  </si>
+  <si>
     <t>قرنفل (30)</t>
   </si>
   <si>
-    <t>شوكولاتة</t>
-  </si>
-  <si>
-    <t>جيلي</t>
-  </si>
-  <si>
-    <t>كريم كراميل</t>
-  </si>
-  <si>
-    <t>حلاوة طحينية</t>
-  </si>
-  <si>
-    <t>ملبن</t>
-  </si>
-  <si>
-    <t>بسكويت شيكولاتة</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل</t>
-  </si>
-  <si>
-    <t>لبان</t>
-  </si>
-  <si>
-    <t>صابون سائل</t>
-  </si>
-  <si>
-    <t>مربى</t>
-  </si>
-  <si>
-    <t>كلور</t>
-  </si>
-  <si>
-    <t>عسل نحل</t>
-  </si>
-  <si>
-    <t>معطر جو</t>
-  </si>
-  <si>
-    <t>ديتول</t>
-  </si>
-  <si>
-    <t>كيك شوكولاتة</t>
-  </si>
-  <si>
-    <t>صابون وجه</t>
-  </si>
-  <si>
-    <t>شوكولاتة (11)</t>
-  </si>
-  <si>
-    <t>شامبو</t>
-  </si>
-  <si>
-    <t>مناديل</t>
-  </si>
-  <si>
-    <t>جيلي (12)</t>
-  </si>
-  <si>
-    <t>سلك مواعين</t>
-  </si>
-  <si>
-    <t>كريم كراميل (13)</t>
-  </si>
-  <si>
-    <t>ملمع زجاج</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل (11)</t>
-  </si>
-  <si>
-    <t>حلاوة طحينية (14)</t>
-  </si>
-  <si>
-    <t>صابون سائل (12)</t>
-  </si>
-  <si>
-    <t>ملبن (15)</t>
-  </si>
-  <si>
-    <t>كلور (13)</t>
-  </si>
-  <si>
-    <t>بسكويت شيكولاتة (16)</t>
-  </si>
-  <si>
-    <t>معطر جو (14)</t>
-  </si>
-  <si>
-    <t>ديتول (15)</t>
-  </si>
-  <si>
-    <t>لبان (17)</t>
-  </si>
-  <si>
-    <t>صابون وجه (16)</t>
-  </si>
-  <si>
-    <t>مربى (18)</t>
-  </si>
-  <si>
-    <t>شامبو (17)</t>
-  </si>
-  <si>
-    <t>مناديل (18)</t>
-  </si>
-  <si>
-    <t>عسل نحل (19)</t>
-  </si>
-  <si>
-    <t>سلك مواعين (19)</t>
-  </si>
-  <si>
-    <t>كيك شوكولاتة (20)</t>
-  </si>
-  <si>
-    <t>ملمع زجاج (20)</t>
-  </si>
-  <si>
-    <t>شوكولاتة (21)</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل (21)</t>
-  </si>
-  <si>
-    <t>جيلي (22)</t>
-  </si>
-  <si>
-    <t>صابون سائل (22)</t>
-  </si>
-  <si>
-    <t>كلور (23)</t>
-  </si>
-  <si>
-    <t>كريم كراميل (23)</t>
-  </si>
-  <si>
-    <t>معطر جو (24)</t>
-  </si>
-  <si>
-    <t>حلاوة طحينية (24)</t>
-  </si>
-  <si>
-    <t>ديتول (25)</t>
-  </si>
-  <si>
-    <t>ملبن (25)</t>
-  </si>
-  <si>
-    <t>صابون وجه (26)</t>
-  </si>
-  <si>
-    <t>شامبو (27)</t>
-  </si>
-  <si>
-    <t>بسكويت شيكولاتة (26)</t>
-  </si>
-  <si>
-    <t>مناديل (28)</t>
-  </si>
-  <si>
-    <t>لبان (27)</t>
-  </si>
-  <si>
     <t>سلك مواعين (29)</t>
   </si>
   <si>
-    <t>مربى (28)</t>
-  </si>
-  <si>
     <t>ملمع زجاج (30)</t>
-  </si>
-  <si>
-    <t>عسل نحل (29)</t>
-  </si>
-  <si>
-    <t>كيك شوكولاتة (30)</t>
   </si>
 </sst>
 </file>
@@ -1351,82 +1351,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2429,22 +2429,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
@@ -2455,13 +2455,13 @@
         <v>243.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
@@ -2472,13 +2472,13 @@
         <v>228.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
@@ -2489,13 +2489,13 @@
         <v>30.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -2506,13 +2506,13 @@
         <v>199.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -2523,13 +2523,13 @@
         <v>121.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
@@ -2540,13 +2540,13 @@
         <v>232.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
@@ -2560,13 +2560,13 @@
         <v>39.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -2580,13 +2580,13 @@
         <v>135.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
@@ -2597,13 +2597,13 @@
         <v>214.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
@@ -2614,13 +2614,13 @@
         <v>67.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -2634,13 +2634,13 @@
         <v>124.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
@@ -2654,13 +2654,13 @@
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
@@ -2671,13 +2671,13 @@
         <v>21.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
@@ -2691,13 +2691,13 @@
         <v>141.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -2708,18 +2708,18 @@
         <v>222.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B17" s="2">
         <v>196.0</v>
@@ -2728,18 +2728,18 @@
         <v>194.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" s="2">
         <v>71.0</v>
@@ -2748,86 +2748,86 @@
         <v>66.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B19" s="2">
         <v>53.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B20" s="2">
         <v>202.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B21" s="2">
         <v>65.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B22" s="2">
         <v>35.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="B23" s="2">
         <v>29.0</v>
@@ -2836,35 +2836,35 @@
         <v>25.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B24" s="2">
         <v>165.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="B25" s="2">
         <v>118.0</v>
@@ -2873,18 +2873,18 @@
         <v>114.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="B26" s="2">
         <v>210.0</v>
@@ -2893,35 +2893,35 @@
         <v>202.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="B27" s="2">
         <v>24.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B28" s="2">
         <v>191.0</v>
@@ -2930,47 +2930,47 @@
         <v>187.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B29" s="2">
         <v>172.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B30" s="2">
         <v>104.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -2981,13 +2981,13 @@
         <v>59.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -3979,112 +3979,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B2" s="2">
         <v>79.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B3" s="2">
         <v>191.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B4" s="2">
         <v>91.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B5" s="2">
         <v>66.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="B6" s="2">
         <v>51.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="B7" s="2">
         <v>198.0</v>
@@ -4093,18 +4093,18 @@
         <v>192.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="B8" s="2">
         <v>32.0</v>
@@ -4113,18 +4113,18 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B9" s="2">
         <v>189.0</v>
@@ -4133,35 +4133,35 @@
         <v>181.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B10" s="2">
         <v>101.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B11" s="2">
         <v>124.0</v>
@@ -4170,35 +4170,35 @@
         <v>118.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B12" s="2">
         <v>30.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="B13" s="2">
         <v>69.0</v>
@@ -4207,18 +4207,18 @@
         <v>60.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B14" s="2">
         <v>140.0</v>
@@ -4227,18 +4227,18 @@
         <v>131.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B15" s="2">
         <v>216.0</v>
@@ -4247,13 +4247,13 @@
         <v>209.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -4264,13 +4264,13 @@
         <v>214.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
@@ -4281,13 +4281,13 @@
         <v>108.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
@@ -4298,13 +4298,13 @@
         <v>158.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
@@ -4315,69 +4315,69 @@
         <v>246.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="B21" s="2">
         <v>99.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="B22" s="2">
         <v>54.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B23" s="2">
         <v>29.0</v>
@@ -4386,35 +4386,35 @@
         <v>21.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="B24" s="2">
         <v>135.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="B25" s="2">
         <v>76.0</v>
@@ -4423,35 +4423,35 @@
         <v>73.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="B26" s="2">
         <v>181.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="B27" s="2">
         <v>58.0</v>
@@ -4460,18 +4460,18 @@
         <v>54.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="B28" s="2">
         <v>16.0</v>
@@ -4480,35 +4480,35 @@
         <v>7.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B29" s="2">
         <v>87.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B30" s="2">
         <v>77.0</v>
@@ -4517,18 +4517,18 @@
         <v>74.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="B31" s="2">
         <v>98.0</v>
@@ -4537,13 +4537,13 @@
         <v>91.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -5535,27 +5535,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="B2" s="2">
         <v>214.0</v>
@@ -5564,18 +5564,18 @@
         <v>207.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B3" s="2">
         <v>65.0</v>
@@ -5584,69 +5584,69 @@
         <v>58.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="B4" s="2">
         <v>101.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="B5" s="2">
         <v>204.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B6" s="2">
         <v>56.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="B7" s="2">
         <v>46.0</v>
@@ -5655,18 +5655,18 @@
         <v>41.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B8" s="2">
         <v>211.0</v>
@@ -5675,86 +5675,86 @@
         <v>204.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="B9" s="2">
         <v>174.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B10" s="2">
         <v>136.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B11" s="2">
         <v>230.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="B12" s="2">
         <v>98.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="B13" s="2">
         <v>101.0</v>
@@ -5763,18 +5763,18 @@
         <v>99.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B14" s="2">
         <v>34.0</v>
@@ -5783,52 +5783,52 @@
         <v>25.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="B15" s="2">
         <v>58.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>253</v>
+        <v>265</v>
       </c>
       <c r="B16" s="2">
         <v>100.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B17" s="2">
         <v>144.0</v>
@@ -5837,35 +5837,35 @@
         <v>138.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
       <c r="B18" s="2">
         <v>104.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="B19" s="2">
         <v>152.0</v>
@@ -5874,35 +5874,35 @@
         <v>144.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="B20" s="2">
         <v>205.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="B21" s="2">
         <v>60.0</v>
@@ -5911,35 +5911,35 @@
         <v>51.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>259</v>
+        <v>284</v>
       </c>
       <c r="B22" s="2">
         <v>172.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>260</v>
+        <v>288</v>
       </c>
       <c r="B23" s="2">
         <v>93.0</v>
@@ -5948,52 +5948,52 @@
         <v>88.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>261</v>
+        <v>291</v>
       </c>
       <c r="B24" s="2">
         <v>167.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>262</v>
+        <v>312</v>
       </c>
       <c r="B25" s="2">
         <v>126.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="B26" s="2">
         <v>250.0</v>
@@ -6002,18 +6002,18 @@
         <v>247.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>264</v>
+        <v>318</v>
       </c>
       <c r="B27" s="2">
         <v>118.0</v>
@@ -6022,81 +6022,81 @@
         <v>108.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>265</v>
+        <v>320</v>
       </c>
       <c r="B28" s="2">
         <v>62.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>266</v>
+        <v>322</v>
       </c>
       <c r="B29" s="2">
         <v>88.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>267</v>
+        <v>324</v>
       </c>
       <c r="B30" s="2">
         <v>18.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>268</v>
+        <v>326</v>
       </c>
       <c r="B31" s="2">
         <v>197.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -7088,61 +7088,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>269</v>
+        <v>248</v>
       </c>
       <c r="B2" s="2">
         <v>119.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>270</v>
+        <v>249</v>
       </c>
       <c r="B3" s="2">
         <v>144.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>271</v>
+        <v>250</v>
       </c>
       <c r="B4" s="2">
         <v>244.0</v>
@@ -7151,52 +7151,52 @@
         <v>234.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>272</v>
+        <v>251</v>
       </c>
       <c r="B5" s="2">
         <v>28.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>252</v>
       </c>
       <c r="B6" s="2">
         <v>206.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>274</v>
+        <v>254</v>
       </c>
       <c r="B7" s="2">
         <v>223.0</v>
@@ -7205,18 +7205,18 @@
         <v>220.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>256</v>
       </c>
       <c r="B8" s="2">
         <v>234.0</v>
@@ -7225,137 +7225,137 @@
         <v>230.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>278</v>
+        <v>258</v>
       </c>
       <c r="B9" s="2">
         <v>87.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="B10" s="2">
         <v>147.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>283</v>
+        <v>261</v>
       </c>
       <c r="B11" s="2">
         <v>141.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>285</v>
+        <v>264</v>
       </c>
       <c r="B12" s="2">
         <v>152.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>288</v>
+        <v>268</v>
       </c>
       <c r="B13" s="2">
         <v>124.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>290</v>
+        <v>271</v>
       </c>
       <c r="B14" s="2">
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>293</v>
+        <v>274</v>
       </c>
       <c r="B15" s="2">
         <v>213.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>295</v>
+        <v>277</v>
       </c>
       <c r="B16" s="2">
         <v>167.0</v>
@@ -7364,35 +7364,35 @@
         <v>161.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B17" s="2">
         <v>138.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>300</v>
+        <v>283</v>
       </c>
       <c r="B18" s="2">
         <v>243.0</v>
@@ -7401,154 +7401,154 @@
         <v>241.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="B19" s="2">
         <v>166.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="B20" s="2">
         <v>31.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>307</v>
+        <v>293</v>
       </c>
       <c r="B21" s="2">
         <v>243.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>309</v>
+        <v>296</v>
       </c>
       <c r="B22" s="2">
         <v>224.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="B23" s="2">
         <v>160.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="B24" s="2">
         <v>233.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="B25" s="2">
         <v>148.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>318</v>
+        <v>305</v>
       </c>
       <c r="B26" s="2">
         <v>195.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="B27" s="2">
         <v>194.0</v>
@@ -7557,35 +7557,35 @@
         <v>191.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>323</v>
+        <v>309</v>
       </c>
       <c r="B28" s="2">
         <v>48.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>325</v>
+        <v>311</v>
       </c>
       <c r="B29" s="2">
         <v>237.0</v>
@@ -7594,18 +7594,18 @@
         <v>228.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>327</v>
+        <v>313</v>
       </c>
       <c r="B30" s="2">
         <v>234.0</v>
@@ -7614,18 +7614,18 @@
         <v>228.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>328</v>
+        <v>315</v>
       </c>
       <c r="B31" s="2">
         <v>210.0</v>
@@ -7634,13 +7634,13 @@
         <v>201.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -8632,27 +8632,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="B2" s="2">
         <v>103.0</v>
@@ -8661,35 +8661,35 @@
         <v>101.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="B3" s="2">
         <v>46.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="B4" s="2">
         <v>54.0</v>
@@ -8698,86 +8698,86 @@
         <v>44.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="B6" s="2">
         <v>68.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="B7" s="2">
         <v>116.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="B8" s="2">
         <v>227.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="B9" s="2">
         <v>199.0</v>
@@ -8786,35 +8786,35 @@
         <v>189.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B10" s="2">
         <v>179.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B11" s="2">
         <v>164.0</v>
@@ -8823,18 +8823,18 @@
         <v>157.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="B12" s="2">
         <v>60.0</v>
@@ -8843,35 +8843,35 @@
         <v>55.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="B13" s="2">
         <v>54.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B14" s="2">
         <v>28.0</v>
@@ -8880,86 +8880,86 @@
         <v>19.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="B15" s="2">
         <v>208.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B16" s="2">
         <v>243.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B17" s="2">
         <v>38.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="B18" s="2">
         <v>181.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="B19" s="2">
         <v>71.0</v>
@@ -8968,52 +8968,52 @@
         <v>61.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B20" s="2">
         <v>240.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B21" s="2">
         <v>195.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="B22" s="2">
         <v>58.0</v>
@@ -9022,18 +9022,18 @@
         <v>49.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B23" s="2">
         <v>140.0</v>
@@ -9042,149 +9042,149 @@
         <v>130.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B24" s="2">
         <v>214.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B25" s="2">
         <v>199.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B26" s="2">
         <v>84.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B27" s="2">
         <v>188.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B28" s="2">
         <v>139.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B29" s="2">
         <v>57.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B30" s="2">
         <v>224.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B31" s="2">
         <v>91.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -10178,42 +10178,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>6</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>10</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>12</v>
+        <v>74</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>14</v>
+        <v>76</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>20</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -11222,27 +11222,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>84.0</v>
@@ -11251,18 +11251,18 @@
         <v>77.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2">
         <v>49.0</v>
@@ -11271,18 +11271,18 @@
         <v>40.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B4" s="2">
         <v>136.0</v>
@@ -11291,18 +11291,18 @@
         <v>131.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B5" s="2">
         <v>171.0</v>
@@ -11311,18 +11311,18 @@
         <v>161.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B6" s="2">
         <v>31.0</v>
@@ -11331,18 +11331,18 @@
         <v>23.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B7" s="2">
         <v>66.0</v>
@@ -11351,18 +11351,18 @@
         <v>60.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B8" s="2">
         <v>129.0</v>
@@ -11371,18 +11371,18 @@
         <v>123.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B9" s="2">
         <v>47.0</v>
@@ -11391,18 +11391,18 @@
         <v>39.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B10" s="2">
         <v>103.0</v>
@@ -11411,18 +11411,18 @@
         <v>98.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2">
         <v>33.0</v>
@@ -11431,18 +11431,18 @@
         <v>31.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2">
         <v>221.0</v>
@@ -11451,18 +11451,18 @@
         <v>214.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2">
         <v>149.0</v>
@@ -11471,18 +11471,18 @@
         <v>145.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B14" s="2">
         <v>197.0</v>
@@ -11491,18 +11491,18 @@
         <v>187.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B15" s="2">
         <v>173.0</v>
@@ -11511,18 +11511,18 @@
         <v>164.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B16" s="2">
         <v>89.0</v>
@@ -11531,18 +11531,18 @@
         <v>86.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B17" s="2">
         <v>159.0</v>
@@ -11551,18 +11551,18 @@
         <v>154.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B18" s="2">
         <v>21.0</v>
@@ -11571,18 +11571,18 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B19" s="2">
         <v>41.0</v>
@@ -11591,18 +11591,18 @@
         <v>37.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2">
         <v>153.0</v>
@@ -11611,18 +11611,18 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2">
         <v>183.0</v>
@@ -11631,13 +11631,13 @@
         <v>175.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -12641,10 +12641,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -12652,7 +12652,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3">
@@ -12660,7 +12660,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>28</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4">
@@ -12668,7 +12668,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
     </row>
     <row r="5">
@@ -12676,7 +12676,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6">
@@ -12684,7 +12684,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>32</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -13689,82 +13689,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>64</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -14773,22 +14773,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
@@ -14799,19 +14799,19 @@
         <v>53.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E2" s="2" t="str">
         <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; (ROW(A1)  &amp; ").png")</f>
         <v>images/proudect (1).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>106</v>
       </c>
       <c r="B3" s="2">
         <v>92.0</v>
@@ -14820,37 +14820,37 @@
         <v>87.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (2).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>115</v>
       </c>
       <c r="B4" s="2">
         <v>198.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (3).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>84.0</v>
@@ -14859,19 +14859,19 @@
         <v>77.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (4).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="B6" s="2">
         <v>249.0</v>
@@ -14880,37 +14880,37 @@
         <v>245.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (5).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="B7" s="2">
         <v>181.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (6).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2">
         <v>49.0</v>
@@ -14919,73 +14919,73 @@
         <v>40.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (7).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>134</v>
       </c>
       <c r="B9" s="2">
         <v>240.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (8).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="B10" s="2">
         <v>203.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (9).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>86</v>
+        <v>140</v>
       </c>
       <c r="B11" s="2">
         <v>109.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (10).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>87</v>
+        <v>145</v>
       </c>
       <c r="B12" s="2">
         <v>31.0</v>
@@ -14994,55 +14994,55 @@
         <v>24.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (11).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>148</v>
       </c>
       <c r="B13" s="2">
         <v>250.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (12).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>89</v>
+        <v>150</v>
       </c>
       <c r="B14" s="2">
         <v>242.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (13).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>21</v>
       </c>
       <c r="B15" s="2">
         <v>136.0</v>
@@ -15051,145 +15051,145 @@
         <v>131.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (14).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>156</v>
       </c>
       <c r="B16" s="2">
         <v>85.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (15).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>91</v>
+        <v>160</v>
       </c>
       <c r="B17" s="2">
         <v>184.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (16).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>92</v>
+        <v>163</v>
       </c>
       <c r="B18" s="2">
         <v>23.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (17).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>93</v>
+        <v>167</v>
       </c>
       <c r="B19" s="2">
         <v>52.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (18).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>94</v>
+        <v>169</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (19).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>96</v>
+        <v>172</v>
       </c>
       <c r="B21" s="2">
         <v>32.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (20).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>98</v>
+        <v>173</v>
       </c>
       <c r="B22" s="2">
         <v>144.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (21).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>24</v>
       </c>
       <c r="B23" s="2">
         <v>171.0</v>
@@ -15198,19 +15198,19 @@
         <v>161.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (22).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="B24" s="2">
         <v>31.0</v>
@@ -15219,73 +15219,73 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (23).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>102</v>
+        <v>174</v>
       </c>
       <c r="B25" s="2">
         <v>41.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (24).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>103</v>
+        <v>175</v>
       </c>
       <c r="B26" s="2">
         <v>170.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (25).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>105</v>
+        <v>176</v>
       </c>
       <c r="B27" s="2">
         <v>199.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (26).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="B28" s="2">
         <v>66.0</v>
@@ -15294,37 +15294,37 @@
         <v>60.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (27).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>107</v>
+        <v>177</v>
       </c>
       <c r="B29" s="2">
         <v>208.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (28).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="B30" s="2">
         <v>129.0</v>
@@ -15333,32 +15333,32 @@
         <v>123.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (29).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>110</v>
+        <v>178</v>
       </c>
       <c r="B31" s="2">
         <v>96.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect (30).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -16356,27 +16356,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2">
         <v>47.0</v>
@@ -16385,109 +16385,109 @@
         <v>39.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect  (" &amp; (ROW(A1) + 30) &amp; ").png"</f>
-        <v>images/proudect  (31).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; (ROW(A1) + 30) &amp; ").png"</f>
+        <v>images/proudect (31).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>151.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (32).png</v>
+        <v>images/proudect (32).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B4" s="2">
         <v>17.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (33).png</v>
+        <v>images/proudect (33).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="B5" s="2">
         <v>175.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (34).png</v>
+        <v>images/proudect (34).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2">
         <v>32.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (35).png</v>
+        <v>images/proudect (35).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>101</v>
+        <v>84</v>
       </c>
       <c r="B7" s="2">
         <v>215.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (36).png</v>
+        <v>images/proudect (36).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2">
         <v>103.0</v>
@@ -16496,37 +16496,37 @@
         <v>98.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (37).png</v>
+        <v>images/proudect (37).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B9" s="2">
         <v>72.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (38).png</v>
+        <v>images/proudect (38).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2">
         <v>33.0</v>
@@ -16535,73 +16535,73 @@
         <v>31.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (39).png</v>
+        <v>images/proudect (39).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2">
         <v>187.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (40).png</v>
+        <v>images/proudect (40).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>108</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2">
         <v>125.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (41).png</v>
+        <v>images/proudect (41).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>109</v>
+        <v>88</v>
       </c>
       <c r="B13" s="2">
         <v>80.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (42).png</v>
+        <v>images/proudect (42).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2">
         <v>221.0</v>
@@ -16610,145 +16610,145 @@
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (43).png</v>
+        <v>images/proudect (43).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2">
         <v>231.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (44).png</v>
+        <v>images/proudect (44).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="B16" s="2">
         <v>201.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (45).png</v>
+        <v>images/proudect (45).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>91</v>
       </c>
       <c r="B17" s="2">
         <v>162.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (46).png</v>
+        <v>images/proudect (46).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>115</v>
+        <v>92</v>
       </c>
       <c r="B18" s="2">
         <v>42.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (47).png</v>
+        <v>images/proudect (47).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>116</v>
+        <v>94</v>
       </c>
       <c r="B19" s="2">
         <v>33.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (48).png</v>
+        <v>images/proudect (48).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="B20" s="2">
         <v>87.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (49).png</v>
+        <v>images/proudect (49).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>118</v>
+        <v>96</v>
       </c>
       <c r="B21" s="2">
         <v>110.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (50).png</v>
+        <v>images/proudect (50).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>119</v>
+        <v>97</v>
       </c>
       <c r="B22" s="2">
         <v>69.0</v>
@@ -16757,37 +16757,37 @@
         <v>62.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (51).png</v>
+        <v>images/proudect (51).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>99</v>
       </c>
       <c r="B23" s="2">
         <v>199.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (52).png</v>
+        <v>images/proudect (52).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2">
         <v>149.0</v>
@@ -16796,19 +16796,19 @@
         <v>145.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (53).png</v>
+        <v>images/proudect (53).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>51</v>
+        <v>36</v>
       </c>
       <c r="B25" s="2">
         <v>197.0</v>
@@ -16817,19 +16817,19 @@
         <v>187.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (54).png</v>
+        <v>images/proudect (54).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B26" s="2">
         <v>84.0</v>
@@ -16838,73 +16838,73 @@
         <v>76.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (55).png</v>
+        <v>images/proudect (55).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>109</v>
       </c>
       <c r="B27" s="2">
         <v>119.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (56).png</v>
+        <v>images/proudect (56).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B28" s="2">
         <v>110.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (57).png</v>
+        <v>images/proudect (57).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>132</v>
+        <v>117</v>
       </c>
       <c r="B29" s="2">
         <v>212.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (58).png</v>
+        <v>images/proudect (58).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B30" s="2">
         <v>173.0</v>
@@ -16913,32 +16913,32 @@
         <v>164.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (59).png</v>
+        <v>images/proudect (59).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B31" s="2">
         <v>147.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (60).png</v>
+        <v>images/proudect (60).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -17936,27 +17936,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="B2" s="2">
         <v>189.0</v>
@@ -17965,19 +17965,19 @@
         <v>179.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect  (" &amp; (ROW(A1) + 60) &amp; ").png"</f>
-        <v>images/proudect  (61).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; (ROW(A1) + 60) &amp; ").png"</f>
+        <v>images/proudect (61).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B3" s="2">
         <v>89.0</v>
@@ -17986,109 +17986,109 @@
         <v>86.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (62).png</v>
+        <v>images/proudect (62).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2">
         <v>105.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (63).png</v>
+        <v>images/proudect (63).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>108</v>
       </c>
       <c r="B5" s="2">
         <v>25.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (64).png</v>
+        <v>images/proudect (64).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="B6" s="2">
         <v>49.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (65).png</v>
+        <v>images/proudect (65).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B7" s="2">
         <v>47.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (66).png</v>
+        <v>images/proudect (66).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>118</v>
       </c>
       <c r="B8" s="2">
         <v>164.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (67).png</v>
+        <v>images/proudect (67).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="B9" s="2">
         <v>159.0</v>
@@ -18097,109 +18097,109 @@
         <v>154.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (68).png</v>
+        <v>images/proudect (68).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B10" s="2">
         <v>124.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (69).png</v>
+        <v>images/proudect (69).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="B11" s="2">
         <v>66.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (70).png</v>
+        <v>images/proudect (70).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="B12" s="2">
         <v>38.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (71).png</v>
+        <v>images/proudect (71).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B13" s="2">
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (72).png</v>
+        <v>images/proudect (72).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B14" s="2">
         <v>73.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (73).png</v>
+        <v>images/proudect (73).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B15" s="2">
         <v>21.0</v>
@@ -18208,19 +18208,19 @@
         <v>17.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (74).png</v>
+        <v>images/proudect (74).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="B16" s="2">
         <v>41.0</v>
@@ -18229,73 +18229,73 @@
         <v>37.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (75).png</v>
+        <v>images/proudect (75).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B17" s="2">
         <v>98.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (76).png</v>
+        <v>images/proudect (76).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="B18" s="2">
         <v>40.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (77).png</v>
+        <v>images/proudect (77).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="B19" s="2">
         <v>53.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (78).png</v>
+        <v>images/proudect (78).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2">
         <v>153.0</v>
@@ -18304,37 +18304,37 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (79).png</v>
+        <v>images/proudect (79).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="B21" s="2">
         <v>157.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (80).png</v>
+        <v>images/proudect (80).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>58</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2">
         <v>183.0</v>
@@ -18343,19 +18343,19 @@
         <v>175.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (81).png</v>
+        <v>images/proudect (81).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="B23" s="2">
         <v>38.0</v>
@@ -18364,91 +18364,91 @@
         <v>33.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (82).png</v>
+        <v>images/proudect (82).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="B24" s="2">
         <v>206.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (83).png</v>
+        <v>images/proudect (83).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B25" s="2">
         <v>39.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (84).png</v>
+        <v>images/proudect (84).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>162</v>
       </c>
       <c r="B26" s="2">
         <v>130.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (85).png</v>
+        <v>images/proudect (85).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>144</v>
+        <v>165</v>
       </c>
       <c r="B27" s="2">
         <v>145.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (86).png</v>
+        <v>images/proudect (86).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B28" s="2">
         <v>75.0</v>
@@ -18457,55 +18457,55 @@
         <v>68.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (87).png</v>
+        <v>images/proudect (87).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>146</v>
+        <v>168</v>
       </c>
       <c r="B29" s="2">
         <v>221.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (88).png</v>
+        <v>images/proudect (88).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>170</v>
       </c>
       <c r="B30" s="2">
         <v>122.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (89).png</v>
+        <v>images/proudect (89).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>148</v>
+        <v>171</v>
       </c>
       <c r="B31" s="2">
         <v>34.0</v>
@@ -18514,14 +18514,14 @@
         <v>25.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect  (90).png</v>
+        <v>images/proudect (90).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -19513,44 +19513,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>23</v>
+        <v>2</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>6</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>149</v>
+        <v>98</v>
       </c>
       <c r="B2" s="2">
         <v>161.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="B3" s="2">
         <v>62.0</v>
@@ -19559,18 +19559,18 @@
         <v>52.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>151</v>
+        <v>101</v>
       </c>
       <c r="B4" s="2">
         <v>164.0</v>
@@ -19579,171 +19579,171 @@
         <v>155.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>152</v>
+        <v>102</v>
       </c>
       <c r="B5" s="2">
         <v>91.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>153</v>
+        <v>104</v>
       </c>
       <c r="B6" s="2">
         <v>120.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>154</v>
+        <v>107</v>
       </c>
       <c r="B7" s="2">
         <v>240.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="B8" s="2">
         <v>68.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>156</v>
+        <v>112</v>
       </c>
       <c r="B9" s="2">
         <v>40.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>157</v>
+        <v>116</v>
       </c>
       <c r="B10" s="2">
         <v>137.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>158</v>
+        <v>119</v>
       </c>
       <c r="B11" s="2">
         <v>51.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>159</v>
+        <v>120</v>
       </c>
       <c r="B12" s="2">
         <v>211.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>160</v>
+        <v>121</v>
       </c>
       <c r="B13" s="2">
         <v>236.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="B14" s="2">
         <v>69.0</v>
@@ -19752,18 +19752,18 @@
         <v>64.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>162</v>
+        <v>128</v>
       </c>
       <c r="B15" s="2">
         <v>78.0</v>
@@ -19772,120 +19772,120 @@
         <v>69.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>163</v>
+        <v>130</v>
       </c>
       <c r="B16" s="2">
         <v>231.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>164</v>
+        <v>132</v>
       </c>
       <c r="B17" s="2">
         <v>155.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="B18" s="2">
         <v>156.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="B19" s="2">
         <v>168.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="B20" s="2">
         <v>70.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>168</v>
+        <v>141</v>
       </c>
       <c r="B21" s="2">
         <v>136.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>169</v>
+        <v>143</v>
       </c>
       <c r="B22" s="2">
         <v>125.0</v>
@@ -19894,35 +19894,35 @@
         <v>119.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>170</v>
+        <v>144</v>
       </c>
       <c r="B23" s="2">
         <v>135.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>171</v>
+        <v>147</v>
       </c>
       <c r="B24" s="2">
         <v>250.0</v>
@@ -19931,69 +19931,69 @@
         <v>244.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>172</v>
+        <v>149</v>
       </c>
       <c r="B25" s="2">
         <v>83.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="B26" s="2">
         <v>117.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="B27" s="2">
         <v>240.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>175</v>
+        <v>155</v>
       </c>
       <c r="B28" s="2">
         <v>174.0</v>
@@ -20002,35 +20002,35 @@
         <v>165.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>176</v>
+        <v>158</v>
       </c>
       <c r="B29" s="2">
         <v>152.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>177</v>
+        <v>161</v>
       </c>
       <c r="B30" s="2">
         <v>162.0</v>
@@ -20039,30 +20039,30 @@
         <v>152.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="B31" s="2">
         <v>189.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -26,66 +26,111 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="329">
   <si>
+    <t>رقم_الصفحة</t>
+  </si>
+  <si>
+    <t>صورة</t>
+  </si>
+  <si>
+    <t>مكان_البانر</t>
+  </si>
+  <si>
     <t>الاسم</t>
   </si>
   <si>
-    <t>صورة</t>
-  </si>
-  <si>
     <t>السعر الأساسي</t>
   </si>
   <si>
+    <t>رئيسي_علوي</t>
+  </si>
+  <si>
     <t>القسم_المستهدف</t>
   </si>
   <si>
     <t>السعر بعد الخصم</t>
   </si>
   <si>
+    <t>images/offer_page_1.jpg</t>
+  </si>
+  <si>
+    <t>الوحدة</t>
+  </si>
+  <si>
     <t>images/slider_1.jpg</t>
   </si>
   <si>
-    <t>الوحدة</t>
+    <t>images/offer_page_2.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_3.jpg</t>
+  </si>
+  <si>
+    <t>الفواكه والخضروات</t>
   </si>
   <si>
     <t>متوفر</t>
   </si>
   <si>
-    <t>الفواكه والخضروات</t>
+    <t>images/offer_page_4.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_5.jpg</t>
+  </si>
+  <si>
+    <t>images/top_banner.jpg</t>
+  </si>
+  <si>
+    <t>images/slider_2.jpg</t>
   </si>
   <si>
     <t>خيار</t>
   </si>
   <si>
-    <t>images/slider_2.jpg</t>
+    <t>مقسم_يمين</t>
   </si>
   <si>
     <t>التسالي والمكسرات</t>
   </si>
   <si>
+    <t>images/split1.jpg</t>
+  </si>
+  <si>
+    <t>مقسم_يسار</t>
+  </si>
+  <si>
     <t>لتر</t>
   </si>
   <si>
+    <t>المشروبات</t>
+  </si>
+  <si>
     <t>images/placeholder.png</t>
   </si>
   <si>
-    <t>المشروبات</t>
+    <t>images/split2.jpg</t>
   </si>
   <si>
     <t>نعم</t>
   </si>
   <si>
+    <t>البقالة</t>
+  </si>
+  <si>
+    <t>رئيسي_ثابت</t>
+  </si>
+  <si>
+    <t>images/static_banner.jpg</t>
+  </si>
+  <si>
     <t>موز</t>
   </si>
   <si>
-    <t>البقالة</t>
+    <t>الألبان</t>
   </si>
   <si>
     <t>كيلو</t>
   </si>
   <si>
-    <t>الألبان</t>
-  </si>
-  <si>
     <t>المخبوزات</t>
   </si>
   <si>
@@ -101,12 +146,12 @@
     <t>بطاطس (22)</t>
   </si>
   <si>
+    <t>بصل (23)</t>
+  </si>
+  <si>
     <t>منظفات</t>
   </si>
   <si>
-    <t>بصل (23)</t>
-  </si>
-  <si>
     <t>قطعة</t>
   </si>
   <si>
@@ -158,24 +203,6 @@
     <t>شاي (21)</t>
   </si>
   <si>
-    <t>رقم_الصفحة</t>
-  </si>
-  <si>
-    <t>images/offer_page_1.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_2.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_3.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_4.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_5.jpg</t>
-  </si>
-  <si>
     <t>الإعداد</t>
   </si>
   <si>
@@ -194,9 +221,6 @@
     <t>01063883209</t>
   </si>
   <si>
-    <t>مكان_البانر</t>
-  </si>
-  <si>
     <t>رابط الواتساب</t>
   </si>
   <si>
@@ -221,51 +245,57 @@
     <t>images/qr_site.jpg</t>
   </si>
   <si>
-    <t>رئيسي_علوي</t>
-  </si>
-  <si>
-    <t>images/top_banner.jpg</t>
-  </si>
-  <si>
     <t>رابط فيسبوك</t>
   </si>
   <si>
     <t>https://facebook.com</t>
   </si>
   <si>
-    <t>مقسم_يمين</t>
-  </si>
-  <si>
     <t>رابط إنستجرام</t>
   </si>
   <si>
     <t>https://instagram.com</t>
   </si>
   <si>
-    <t>images/split1.jpg</t>
-  </si>
-  <si>
     <t>صورة صفحة حول</t>
   </si>
   <si>
-    <t>مقسم_يسار</t>
-  </si>
-  <si>
     <t>images/about_icon.jpg</t>
   </si>
   <si>
-    <t>images/split2.jpg</t>
-  </si>
-  <si>
-    <t>رئيسي_ثابت</t>
-  </si>
-  <si>
-    <t>images/static_banner.jpg</t>
-  </si>
-  <si>
     <t>طماطم</t>
   </si>
   <si>
+    <t>بطاطس</t>
+  </si>
+  <si>
+    <t>بصل</t>
+  </si>
+  <si>
+    <t>جزر</t>
+  </si>
+  <si>
+    <t>تفاح</t>
+  </si>
+  <si>
+    <t>برتقال</t>
+  </si>
+  <si>
+    <t>عنب</t>
+  </si>
+  <si>
+    <t>مانجو</t>
+  </si>
+  <si>
+    <t>طماطم (11)</t>
+  </si>
+  <si>
+    <t>بطاطس (12)</t>
+  </si>
+  <si>
+    <t>بصل (13)</t>
+  </si>
+  <si>
     <t>لب سوري</t>
   </si>
   <si>
@@ -275,12 +305,21 @@
     <t>لوز</t>
   </si>
   <si>
+    <t>جزر (15)</t>
+  </si>
+  <si>
     <t>عين جمل</t>
   </si>
   <si>
+    <t>تفاح (16)</t>
+  </si>
+  <si>
     <t>كاجو</t>
   </si>
   <si>
+    <t>موز (17)</t>
+  </si>
+  <si>
     <t>فشار</t>
   </si>
   <si>
@@ -290,24 +329,36 @@
     <t>لب سوبر (11)</t>
   </si>
   <si>
+    <t>برتقال (18)</t>
+  </si>
+  <si>
+    <t>شاي</t>
+  </si>
+  <si>
     <t>لب سوري (12)</t>
   </si>
   <si>
+    <t>عنب (19)</t>
+  </si>
+  <si>
     <t>لوز (14)</t>
   </si>
   <si>
+    <t>مانجو (20)</t>
+  </si>
+  <si>
     <t>عين جمل (15)</t>
   </si>
   <si>
+    <t>طماطم (21)</t>
+  </si>
+  <si>
     <t>كاجو (16)</t>
   </si>
   <si>
     <t>شيبسي (17)</t>
   </si>
   <si>
-    <t>شاي</t>
-  </si>
-  <si>
     <t>فشار (18)</t>
   </si>
   <si>
@@ -317,13 +368,85 @@
     <t>فستق (20)</t>
   </si>
   <si>
+    <t>خيار (24)</t>
+  </si>
+  <si>
     <t>لب سوبر (21)</t>
   </si>
   <si>
+    <t>لب سوري (22)</t>
+  </si>
+  <si>
+    <t>جزر (25)</t>
+  </si>
+  <si>
+    <t>تفاح (26)</t>
+  </si>
+  <si>
+    <t>نسكافيه</t>
+  </si>
+  <si>
+    <t>عين جمل (25)</t>
+  </si>
+  <si>
+    <t>عصير برتقال</t>
+  </si>
+  <si>
+    <t>كاجو (26)</t>
+  </si>
+  <si>
+    <t>برتقال (28)</t>
+  </si>
+  <si>
+    <t>عصير تفاح</t>
+  </si>
+  <si>
+    <t>شيبسي (27)</t>
+  </si>
+  <si>
+    <t>كولا</t>
+  </si>
+  <si>
+    <t>فشار (28)</t>
+  </si>
+  <si>
+    <t>مياه معدنية</t>
+  </si>
+  <si>
+    <t>مانجو (30)</t>
+  </si>
+  <si>
+    <t>فستق (30)</t>
+  </si>
+  <si>
+    <t>كاكاو</t>
+  </si>
+  <si>
+    <t>نعناع</t>
+  </si>
+  <si>
+    <t>شاي (11)</t>
+  </si>
+  <si>
+    <t>قهوة (12)</t>
+  </si>
+  <si>
+    <t>نسكافيه (13)</t>
+  </si>
+  <si>
+    <t>كولا (16)</t>
+  </si>
+  <si>
+    <t>مياه معدنية (17)</t>
+  </si>
+  <si>
+    <t>مشروب طاقة (18)</t>
+  </si>
+  <si>
     <t>أرز</t>
   </si>
   <si>
-    <t>لب سوري (22)</t>
+    <t>نعناع (20)</t>
   </si>
   <si>
     <t>مكرونة</t>
@@ -332,679 +455,556 @@
     <t>سكر</t>
   </si>
   <si>
+    <t>قهوة (22)</t>
+  </si>
+  <si>
     <t>زيت</t>
   </si>
   <si>
-    <t>نسكافيه</t>
+    <t>نسكافيه (23)</t>
   </si>
   <si>
     <t>سمنة</t>
   </si>
   <si>
-    <t>عين جمل (25)</t>
-  </si>
-  <si>
-    <t>بطاطس</t>
+    <t>عصير برتقال (24)</t>
   </si>
   <si>
     <t>صلصة</t>
   </si>
   <si>
-    <t>عصير برتقال</t>
-  </si>
-  <si>
-    <t>كاجو (26)</t>
+    <t>عصير تفاح (25)</t>
   </si>
   <si>
     <t>تونة</t>
   </si>
   <si>
-    <t>عصير تفاح</t>
+    <t>كولا (26)</t>
   </si>
   <si>
     <t>فول</t>
   </si>
   <si>
-    <t>شيبسي (27)</t>
-  </si>
-  <si>
-    <t>كولا</t>
-  </si>
-  <si>
-    <t>بصل</t>
+    <t>مياه معدنية (27)</t>
   </si>
   <si>
     <t>عدس</t>
   </si>
   <si>
-    <t>فشار (28)</t>
-  </si>
-  <si>
-    <t>مياه معدنية</t>
+    <t>مشروب طاقة (28)</t>
   </si>
   <si>
     <t>دقيق</t>
   </si>
   <si>
+    <t>كاكاو (29)</t>
+  </si>
+  <si>
     <t>أرز (11)</t>
   </si>
   <si>
+    <t>نعناع (30)</t>
+  </si>
+  <si>
     <t>مكرونة (12)</t>
   </si>
   <si>
-    <t>جزر</t>
-  </si>
-  <si>
-    <t>كاكاو</t>
-  </si>
-  <si>
-    <t>فستق (30)</t>
-  </si>
-  <si>
     <t>سكر (13)</t>
   </si>
   <si>
-    <t>نعناع</t>
-  </si>
-  <si>
-    <t>تفاح</t>
-  </si>
-  <si>
     <t>زيت (14)</t>
   </si>
   <si>
-    <t>شاي (11)</t>
-  </si>
-  <si>
     <t>سمنة (15)</t>
   </si>
   <si>
-    <t>قهوة (12)</t>
-  </si>
-  <si>
     <t>صلصة (16)</t>
   </si>
   <si>
-    <t>نسكافيه (13)</t>
-  </si>
-  <si>
-    <t>برتقال</t>
-  </si>
-  <si>
     <t>تونة (17)</t>
   </si>
   <si>
     <t>فول (18)</t>
   </si>
   <si>
-    <t>عنب</t>
-  </si>
-  <si>
     <t>عدس (19)</t>
   </si>
   <si>
-    <t>كولا (16)</t>
-  </si>
-  <si>
-    <t>مانجو</t>
-  </si>
-  <si>
     <t>دقيق (20)</t>
   </si>
   <si>
-    <t>مياه معدنية (17)</t>
-  </si>
-  <si>
     <t>أرز (21)</t>
   </si>
   <si>
     <t>مكرونة (22)</t>
   </si>
   <si>
-    <t>طماطم (11)</t>
-  </si>
-  <si>
-    <t>مشروب طاقة (18)</t>
-  </si>
-  <si>
     <t>سكر (23)</t>
   </si>
   <si>
-    <t>بطاطس (12)</t>
-  </si>
-  <si>
     <t>زيت (24)</t>
   </si>
   <si>
-    <t>بصل (13)</t>
-  </si>
-  <si>
-    <t>نعناع (20)</t>
-  </si>
-  <si>
     <t>سمنة (25)</t>
   </si>
   <si>
     <t>صلصة (26)</t>
   </si>
   <si>
-    <t>قهوة (22)</t>
-  </si>
-  <si>
     <t>تونة (27)</t>
   </si>
   <si>
-    <t>جزر (15)</t>
-  </si>
-  <si>
-    <t>نسكافيه (23)</t>
-  </si>
-  <si>
     <t>فول (28)</t>
   </si>
   <si>
-    <t>عصير برتقال (24)</t>
-  </si>
-  <si>
-    <t>تفاح (16)</t>
-  </si>
-  <si>
     <t>عدس (29)</t>
   </si>
   <si>
-    <t>عصير تفاح (25)</t>
-  </si>
-  <si>
-    <t>موز (17)</t>
-  </si>
-  <si>
     <t>دقيق (30)</t>
   </si>
   <si>
-    <t>كولا (26)</t>
-  </si>
-  <si>
-    <t>مياه معدنية (27)</t>
-  </si>
-  <si>
-    <t>برتقال (18)</t>
-  </si>
-  <si>
-    <t>مشروب طاقة (28)</t>
-  </si>
-  <si>
-    <t>عنب (19)</t>
-  </si>
-  <si>
-    <t>كاكاو (29)</t>
-  </si>
-  <si>
-    <t>نعناع (30)</t>
-  </si>
-  <si>
-    <t>مانجو (20)</t>
-  </si>
-  <si>
-    <t>طماطم (21)</t>
-  </si>
-  <si>
-    <t>خيار (24)</t>
-  </si>
-  <si>
-    <t>جزر (25)</t>
-  </si>
-  <si>
-    <t>تفاح (26)</t>
-  </si>
-  <si>
-    <t>برتقال (28)</t>
-  </si>
-  <si>
-    <t>مانجو (30)</t>
+    <t>عيش فينو</t>
   </si>
   <si>
     <t>لبن كامل الدسم</t>
   </si>
   <si>
+    <t>عيش بلدي</t>
+  </si>
+  <si>
     <t>جبنة بيضاء</t>
   </si>
   <si>
+    <t>باتيه</t>
+  </si>
+  <si>
     <t>جبنة رومي</t>
   </si>
   <si>
+    <t>كرواسون</t>
+  </si>
+  <si>
     <t>زبادي</t>
   </si>
   <si>
+    <t>بقسماط</t>
+  </si>
+  <si>
     <t>قشطة</t>
   </si>
   <si>
+    <t>توست أبيض</t>
+  </si>
+  <si>
     <t>زبدة</t>
   </si>
   <si>
+    <t>توست أسمر</t>
+  </si>
+  <si>
+    <t>فطير</t>
+  </si>
+  <si>
     <t>جبنة شيدر</t>
   </si>
   <si>
+    <t>كيك</t>
+  </si>
+  <si>
+    <t>بسكويت</t>
+  </si>
+  <si>
     <t>جبنة نستو</t>
   </si>
   <si>
+    <t>عيش فينو (11)</t>
+  </si>
+  <si>
     <t>لبن رايب</t>
   </si>
   <si>
+    <t>عيش بلدي (12)</t>
+  </si>
+  <si>
     <t>سمن بلدي</t>
   </si>
   <si>
+    <t>باتيه (13)</t>
+  </si>
+  <si>
+    <t>كرواسون (14)</t>
+  </si>
+  <si>
+    <t>كمون</t>
+  </si>
+  <si>
     <t>لبن كامل الدسم (11)</t>
   </si>
   <si>
+    <t>بقسماط (15)</t>
+  </si>
+  <si>
+    <t>فلفل أسود</t>
+  </si>
+  <si>
+    <t>توست أبيض (16)</t>
+  </si>
+  <si>
     <t>جبنة بيضاء (12)</t>
   </si>
   <si>
+    <t>توست أسمر (17)</t>
+  </si>
+  <si>
     <t>جبنة رومي (13)</t>
   </si>
   <si>
+    <t>فطير (18)</t>
+  </si>
+  <si>
+    <t>كركم</t>
+  </si>
+  <si>
+    <t>كيك (19)</t>
+  </si>
+  <si>
     <t>زبادي (14)</t>
   </si>
   <si>
+    <t>بسكويت (20)</t>
+  </si>
+  <si>
+    <t>كزبرة</t>
+  </si>
+  <si>
     <t>قشطة (15)</t>
   </si>
   <si>
-    <t>عيش فينو</t>
+    <t>عيش فينو (21)</t>
   </si>
   <si>
     <t>زبدة (16)</t>
   </si>
   <si>
-    <t>عيش بلدي</t>
+    <t>بهارات مشكلة</t>
+  </si>
+  <si>
+    <t>عيش بلدي (22)</t>
   </si>
   <si>
     <t>جبنة شيدر (17)</t>
   </si>
   <si>
-    <t>باتيه</t>
-  </si>
-  <si>
-    <t>كرواسون</t>
+    <t>باتيه (23)</t>
+  </si>
+  <si>
+    <t>قرفة</t>
+  </si>
+  <si>
+    <t>كرواسون (24)</t>
   </si>
   <si>
     <t>جبنة نستو (18)</t>
   </si>
   <si>
-    <t>بقسماط</t>
+    <t>حبهان</t>
+  </si>
+  <si>
+    <t>بقسماط (25)</t>
   </si>
   <si>
     <t>لبن رايب (19)</t>
   </si>
   <si>
-    <t>توست أبيض</t>
+    <t>شوكولاتة</t>
+  </si>
+  <si>
+    <t>توست أبيض (26)</t>
   </si>
   <si>
     <t>سمن بلدي (20)</t>
   </si>
   <si>
+    <t>ورق لورا</t>
+  </si>
+  <si>
+    <t>جيلي</t>
+  </si>
+  <si>
+    <t>توست أسمر (27)</t>
+  </si>
+  <si>
+    <t>بابريكا</t>
+  </si>
+  <si>
     <t>لبن كامل الدسم (21)</t>
   </si>
   <si>
-    <t>توست أسمر</t>
+    <t>كريم كراميل</t>
+  </si>
+  <si>
+    <t>فطير (28)</t>
   </si>
   <si>
     <t>جبنة بيضاء (22)</t>
   </si>
   <si>
-    <t>فطير</t>
+    <t>قرنفل</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية</t>
+  </si>
+  <si>
+    <t>كيك (29)</t>
+  </si>
+  <si>
+    <t>ملبن</t>
+  </si>
+  <si>
+    <t>كمون (11)</t>
   </si>
   <si>
     <t>جبنة رومي (23)</t>
   </si>
   <si>
-    <t>كيك</t>
+    <t>بسكويت شيكولاتة</t>
+  </si>
+  <si>
+    <t>بسكويت (30)</t>
+  </si>
+  <si>
+    <t>فلفل أسود (12)</t>
   </si>
   <si>
     <t>زبادي (24)</t>
   </si>
   <si>
-    <t>بسكويت</t>
+    <t>لبان</t>
+  </si>
+  <si>
+    <t>كركم (13)</t>
   </si>
   <si>
     <t>قشطة (25)</t>
   </si>
   <si>
-    <t>عيش فينو (11)</t>
+    <t>مربى</t>
+  </si>
+  <si>
+    <t>كزبرة (14)</t>
+  </si>
+  <si>
+    <t>عسل نحل</t>
   </si>
   <si>
     <t>زبدة (26)</t>
   </si>
   <si>
-    <t>عيش بلدي (12)</t>
+    <t>كيك شوكولاتة</t>
   </si>
   <si>
     <t>جبنة شيدر (27)</t>
   </si>
   <si>
-    <t>باتيه (13)</t>
+    <t>شوكولاتة (11)</t>
   </si>
   <si>
     <t>جبنة نستو (28)</t>
   </si>
   <si>
-    <t>كرواسون (14)</t>
+    <t>جيلي (12)</t>
   </si>
   <si>
     <t>لبن رايب (29)</t>
   </si>
   <si>
+    <t>كريم كراميل (13)</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية (14)</t>
+  </si>
+  <si>
     <t>سمن بلدي (30)</t>
   </si>
   <si>
-    <t>بقسماط (15)</t>
-  </si>
-  <si>
-    <t>توست أبيض (16)</t>
-  </si>
-  <si>
-    <t>توست أسمر (17)</t>
-  </si>
-  <si>
-    <t>فطير (18)</t>
-  </si>
-  <si>
-    <t>كيك (19)</t>
-  </si>
-  <si>
-    <t>بسكويت (20)</t>
-  </si>
-  <si>
-    <t>عيش فينو (21)</t>
-  </si>
-  <si>
-    <t>عيش بلدي (22)</t>
-  </si>
-  <si>
-    <t>باتيه (23)</t>
-  </si>
-  <si>
-    <t>كرواسون (24)</t>
-  </si>
-  <si>
-    <t>بقسماط (25)</t>
-  </si>
-  <si>
-    <t>توست أبيض (26)</t>
-  </si>
-  <si>
-    <t>توست أسمر (27)</t>
-  </si>
-  <si>
-    <t>فطير (28)</t>
-  </si>
-  <si>
-    <t>كيك (29)</t>
-  </si>
-  <si>
-    <t>بسكويت (30)</t>
-  </si>
-  <si>
-    <t>كمون</t>
-  </si>
-  <si>
-    <t>فلفل أسود</t>
-  </si>
-  <si>
-    <t>كركم</t>
-  </si>
-  <si>
-    <t>كزبرة</t>
-  </si>
-  <si>
-    <t>بهارات مشكلة</t>
-  </si>
-  <si>
-    <t>قرفة</t>
-  </si>
-  <si>
-    <t>حبهان</t>
-  </si>
-  <si>
-    <t>ورق لورا</t>
-  </si>
-  <si>
-    <t>بابريكا</t>
-  </si>
-  <si>
-    <t>شوكولاتة</t>
-  </si>
-  <si>
-    <t>جيلي</t>
-  </si>
-  <si>
-    <t>كريم كراميل</t>
-  </si>
-  <si>
-    <t>حلاوة طحينية</t>
-  </si>
-  <si>
-    <t>ملبن</t>
-  </si>
-  <si>
-    <t>قرنفل</t>
-  </si>
-  <si>
-    <t>بسكويت شيكولاتة</t>
-  </si>
-  <si>
-    <t>كمون (11)</t>
-  </si>
-  <si>
-    <t>لبان</t>
-  </si>
-  <si>
-    <t>فلفل أسود (12)</t>
-  </si>
-  <si>
-    <t>مربى</t>
-  </si>
-  <si>
-    <t>كركم (13)</t>
-  </si>
-  <si>
-    <t>عسل نحل</t>
-  </si>
-  <si>
-    <t>كيك شوكولاتة</t>
-  </si>
-  <si>
-    <t>كزبرة (14)</t>
+    <t>ملبن (15)</t>
+  </si>
+  <si>
+    <t>بسكويت شيكولاتة (16)</t>
+  </si>
+  <si>
+    <t>لبان (17)</t>
+  </si>
+  <si>
+    <t>بهارات مشكلة (15)</t>
+  </si>
+  <si>
+    <t>مربى (18)</t>
+  </si>
+  <si>
+    <t>قرفة (16)</t>
+  </si>
+  <si>
+    <t>عسل نحل (19)</t>
+  </si>
+  <si>
+    <t>حبهان (17)</t>
+  </si>
+  <si>
+    <t>كيك شوكولاتة (20)</t>
+  </si>
+  <si>
+    <t>شوكولاتة (21)</t>
+  </si>
+  <si>
+    <t>ورق لورا (18)</t>
+  </si>
+  <si>
+    <t>جيلي (22)</t>
+  </si>
+  <si>
+    <t>بابريكا (19)</t>
+  </si>
+  <si>
+    <t>كريم كراميل (23)</t>
+  </si>
+  <si>
+    <t>قرنفل (20)</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية (24)</t>
+  </si>
+  <si>
+    <t>كمون (21)</t>
+  </si>
+  <si>
+    <t>ملبن (25)</t>
+  </si>
+  <si>
+    <t>فلفل أسود (22)</t>
+  </si>
+  <si>
+    <t>بسكويت شيكولاتة (26)</t>
+  </si>
+  <si>
+    <t>لبان (27)</t>
+  </si>
+  <si>
+    <t>كركم (23)</t>
+  </si>
+  <si>
+    <t>مربى (28)</t>
+  </si>
+  <si>
+    <t>كزبرة (24)</t>
+  </si>
+  <si>
+    <t>عسل نحل (29)</t>
+  </si>
+  <si>
+    <t>بهارات مشكلة (25)</t>
+  </si>
+  <si>
+    <t>كيك شوكولاتة (30)</t>
+  </si>
+  <si>
+    <t>قرفة (26)</t>
+  </si>
+  <si>
+    <t>حبهان (27)</t>
+  </si>
+  <si>
+    <t>ورق لورا (28)</t>
+  </si>
+  <si>
+    <t>بابريكا (29)</t>
+  </si>
+  <si>
+    <t>قرنفل (30)</t>
   </si>
   <si>
     <t>مسحوق غسيل</t>
   </si>
   <si>
-    <t>شوكولاتة (11)</t>
-  </si>
-  <si>
-    <t>بهارات مشكلة (15)</t>
-  </si>
-  <si>
     <t>صابون سائل</t>
   </si>
   <si>
-    <t>قرفة (16)</t>
-  </si>
-  <si>
-    <t>جيلي (12)</t>
-  </si>
-  <si>
     <t>كلور</t>
   </si>
   <si>
-    <t>حبهان (17)</t>
-  </si>
-  <si>
-    <t>كريم كراميل (13)</t>
-  </si>
-  <si>
     <t>معطر جو</t>
   </si>
   <si>
-    <t>ورق لورا (18)</t>
-  </si>
-  <si>
-    <t>حلاوة طحينية (14)</t>
-  </si>
-  <si>
     <t>ديتول</t>
   </si>
   <si>
     <t>صابون وجه</t>
   </si>
   <si>
-    <t>ملبن (15)</t>
-  </si>
-  <si>
-    <t>بابريكا (19)</t>
-  </si>
-  <si>
     <t>شامبو</t>
   </si>
   <si>
-    <t>بسكويت شيكولاتة (16)</t>
-  </si>
-  <si>
-    <t>قرنفل (20)</t>
-  </si>
-  <si>
     <t>مناديل</t>
   </si>
   <si>
-    <t>لبان (17)</t>
-  </si>
-  <si>
-    <t>كمون (21)</t>
-  </si>
-  <si>
     <t>سلك مواعين</t>
   </si>
   <si>
     <t>ملمع زجاج</t>
   </si>
   <si>
-    <t>مربى (18)</t>
-  </si>
-  <si>
-    <t>فلفل أسود (22)</t>
-  </si>
-  <si>
     <t>مسحوق غسيل (11)</t>
   </si>
   <si>
-    <t>عسل نحل (19)</t>
-  </si>
-  <si>
-    <t>كركم (23)</t>
-  </si>
-  <si>
     <t>صابون سائل (12)</t>
   </si>
   <si>
-    <t>كيك شوكولاتة (20)</t>
-  </si>
-  <si>
     <t>كلور (13)</t>
   </si>
   <si>
     <t>معطر جو (14)</t>
   </si>
   <si>
-    <t>شوكولاتة (21)</t>
-  </si>
-  <si>
     <t>ديتول (15)</t>
   </si>
   <si>
-    <t>جيلي (22)</t>
-  </si>
-  <si>
     <t>صابون وجه (16)</t>
   </si>
   <si>
     <t>شامبو (17)</t>
   </si>
   <si>
-    <t>كريم كراميل (23)</t>
-  </si>
-  <si>
     <t>مناديل (18)</t>
   </si>
   <si>
-    <t>حلاوة طحينية (24)</t>
-  </si>
-  <si>
     <t>سلك مواعين (19)</t>
   </si>
   <si>
-    <t>ملبن (25)</t>
-  </si>
-  <si>
-    <t>بسكويت شيكولاتة (26)</t>
-  </si>
-  <si>
     <t>ملمع زجاج (20)</t>
   </si>
   <si>
     <t>مسحوق غسيل (21)</t>
   </si>
   <si>
-    <t>لبان (27)</t>
-  </si>
-  <si>
     <t>صابون سائل (22)</t>
   </si>
   <si>
-    <t>مربى (28)</t>
-  </si>
-  <si>
-    <t>كزبرة (24)</t>
-  </si>
-  <si>
-    <t>عسل نحل (29)</t>
-  </si>
-  <si>
     <t>كلور (23)</t>
   </si>
   <si>
-    <t>كيك شوكولاتة (30)</t>
-  </si>
-  <si>
-    <t>بهارات مشكلة (25)</t>
-  </si>
-  <si>
     <t>معطر جو (24)</t>
   </si>
   <si>
-    <t>قرفة (26)</t>
-  </si>
-  <si>
     <t>ديتول (25)</t>
   </si>
   <si>
-    <t>حبهان (27)</t>
-  </si>
-  <si>
     <t>صابون وجه (26)</t>
   </si>
   <si>
-    <t>ورق لورا (28)</t>
-  </si>
-  <si>
     <t>شامبو (27)</t>
   </si>
   <si>
-    <t>بابريكا (29)</t>
-  </si>
-  <si>
     <t>مناديل (28)</t>
-  </si>
-  <si>
-    <t>قرنفل (30)</t>
   </si>
   <si>
     <t>سلك مواعين (29)</t>
@@ -1354,79 +1354,79 @@
         <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>11</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>17</v>
+        <v>29</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>20</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>23</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2429,129 +2429,129 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B2" s="2">
         <v>243.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B3" s="2">
         <v>228.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="B4" s="2">
         <v>30.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B5" s="2">
         <v>199.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="B6" s="2">
         <v>121.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B7" s="2">
         <v>232.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="B8" s="2">
         <v>49.0</v>
@@ -2560,18 +2560,18 @@
         <v>39.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B9" s="2">
         <v>137.0</v>
@@ -2580,52 +2580,52 @@
         <v>135.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="B10" s="2">
         <v>214.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B11" s="2">
         <v>67.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="B12" s="2">
         <v>134.0</v>
@@ -2634,18 +2634,18 @@
         <v>124.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B13" s="2">
         <v>126.0</v>
@@ -2654,35 +2654,35 @@
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>191</v>
+        <v>210</v>
       </c>
       <c r="B14" s="2">
         <v>21.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="B15" s="2">
         <v>148.0</v>
@@ -2691,35 +2691,35 @@
         <v>141.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="B16" s="2">
         <v>222.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>195</v>
+        <v>219</v>
       </c>
       <c r="B17" s="2">
         <v>196.0</v>
@@ -2728,18 +2728,18 @@
         <v>194.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="B18" s="2">
         <v>71.0</v>
@@ -2748,86 +2748,86 @@
         <v>66.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>200</v>
+        <v>226</v>
       </c>
       <c r="B19" s="2">
         <v>53.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>202</v>
+        <v>229</v>
       </c>
       <c r="B20" s="2">
         <v>202.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>204</v>
+        <v>232</v>
       </c>
       <c r="B21" s="2">
         <v>65.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>205</v>
+        <v>237</v>
       </c>
       <c r="B22" s="2">
         <v>35.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>207</v>
+        <v>240</v>
       </c>
       <c r="B23" s="2">
         <v>29.0</v>
@@ -2836,35 +2836,35 @@
         <v>25.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="B24" s="2">
         <v>165.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>211</v>
+        <v>250</v>
       </c>
       <c r="B25" s="2">
         <v>118.0</v>
@@ -2873,18 +2873,18 @@
         <v>114.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>213</v>
+        <v>253</v>
       </c>
       <c r="B26" s="2">
         <v>210.0</v>
@@ -2893,35 +2893,35 @@
         <v>202.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>215</v>
+        <v>257</v>
       </c>
       <c r="B27" s="2">
         <v>24.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>217</v>
+        <v>259</v>
       </c>
       <c r="B28" s="2">
         <v>191.0</v>
@@ -2930,64 +2930,64 @@
         <v>187.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="B29" s="2">
         <v>172.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>221</v>
+        <v>263</v>
       </c>
       <c r="B30" s="2">
         <v>104.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>222</v>
+        <v>266</v>
       </c>
       <c r="B31" s="2">
         <v>59.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -3979,112 +3979,112 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2">
         <v>79.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="B3" s="2">
         <v>191.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="B4" s="2">
         <v>91.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>199</v>
+        <v>185</v>
       </c>
       <c r="B5" s="2">
         <v>66.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>201</v>
+        <v>187</v>
       </c>
       <c r="B6" s="2">
         <v>51.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>203</v>
+        <v>189</v>
       </c>
       <c r="B7" s="2">
         <v>198.0</v>
@@ -4093,18 +4093,18 @@
         <v>192.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="B8" s="2">
         <v>32.0</v>
@@ -4113,18 +4113,18 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>192</v>
       </c>
       <c r="B9" s="2">
         <v>189.0</v>
@@ -4133,35 +4133,35 @@
         <v>181.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="B10" s="2">
         <v>101.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="B11" s="2">
         <v>124.0</v>
@@ -4170,35 +4170,35 @@
         <v>118.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="B12" s="2">
         <v>30.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="B13" s="2">
         <v>69.0</v>
@@ -4207,18 +4207,18 @@
         <v>60.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="B14" s="2">
         <v>140.0</v>
@@ -4227,18 +4227,18 @@
         <v>131.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>220</v>
+        <v>202</v>
       </c>
       <c r="B15" s="2">
         <v>216.0</v>
@@ -4247,137 +4247,137 @@
         <v>209.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>223</v>
+        <v>205</v>
       </c>
       <c r="B16" s="2">
         <v>214.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="B17" s="2">
         <v>108.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>225</v>
+        <v>209</v>
       </c>
       <c r="B18" s="2">
         <v>158.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="B19" s="2">
         <v>246.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="B21" s="2">
         <v>99.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="B22" s="2">
         <v>54.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="B23" s="2">
         <v>29.0</v>
@@ -4386,35 +4386,35 @@
         <v>21.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="B24" s="2">
         <v>135.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="B25" s="2">
         <v>76.0</v>
@@ -4423,35 +4423,35 @@
         <v>73.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="B26" s="2">
         <v>181.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="B27" s="2">
         <v>58.0</v>
@@ -4460,13 +4460,13 @@
         <v>54.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -4480,35 +4480,35 @@
         <v>7.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B29" s="2">
         <v>87.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B30" s="2">
         <v>77.0</v>
@@ -4517,18 +4517,18 @@
         <v>74.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B31" s="2">
         <v>98.0</v>
@@ -4537,13 +4537,13 @@
         <v>91.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -5535,27 +5535,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>239</v>
+        <v>203</v>
       </c>
       <c r="B2" s="2">
         <v>214.0</v>
@@ -5564,18 +5564,18 @@
         <v>207.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>240</v>
+        <v>206</v>
       </c>
       <c r="B3" s="2">
         <v>65.0</v>
@@ -5584,69 +5584,69 @@
         <v>58.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="B4" s="2">
         <v>101.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>242</v>
+        <v>216</v>
       </c>
       <c r="B5" s="2">
         <v>204.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>243</v>
+        <v>220</v>
       </c>
       <c r="B6" s="2">
         <v>56.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>244</v>
+        <v>224</v>
       </c>
       <c r="B7" s="2">
         <v>46.0</v>
@@ -5655,18 +5655,18 @@
         <v>41.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="B8" s="2">
         <v>211.0</v>
@@ -5675,86 +5675,86 @@
         <v>204.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>246</v>
+        <v>233</v>
       </c>
       <c r="B9" s="2">
         <v>174.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="B10" s="2">
         <v>136.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="B11" s="2">
         <v>230.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="B12" s="2">
         <v>98.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="B13" s="2">
         <v>101.0</v>
@@ -5763,18 +5763,18 @@
         <v>99.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B14" s="2">
         <v>34.0</v>
@@ -5783,52 +5783,52 @@
         <v>25.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="B15" s="2">
         <v>58.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="B16" s="2">
         <v>100.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="B17" s="2">
         <v>144.0</v>
@@ -5837,35 +5837,35 @@
         <v>138.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B18" s="2">
         <v>104.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B19" s="2">
         <v>152.0</v>
@@ -5874,30 +5874,30 @@
         <v>144.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B20" s="2">
         <v>205.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -5911,35 +5911,35 @@
         <v>51.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="B22" s="2">
         <v>172.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="B23" s="2">
         <v>93.0</v>
@@ -5948,52 +5948,52 @@
         <v>88.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B24" s="2">
         <v>167.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>312</v>
+        <v>290</v>
       </c>
       <c r="B25" s="2">
         <v>126.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>316</v>
+        <v>292</v>
       </c>
       <c r="B26" s="2">
         <v>250.0</v>
@@ -6002,18 +6002,18 @@
         <v>247.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>318</v>
+        <v>294</v>
       </c>
       <c r="B27" s="2">
         <v>118.0</v>
@@ -6022,81 +6022,81 @@
         <v>108.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>320</v>
+        <v>295</v>
       </c>
       <c r="B28" s="2">
         <v>62.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>322</v>
+        <v>296</v>
       </c>
       <c r="B29" s="2">
         <v>88.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>324</v>
+        <v>297</v>
       </c>
       <c r="B30" s="2">
         <v>18.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="B31" s="2">
         <v>197.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -7088,61 +7088,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>248</v>
+        <v>230</v>
       </c>
       <c r="B2" s="2">
         <v>119.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B3" s="2">
         <v>144.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="B4" s="2">
         <v>244.0</v>
@@ -7151,52 +7151,52 @@
         <v>234.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="B5" s="2">
         <v>28.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B6" s="2">
         <v>206.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="B7" s="2">
         <v>223.0</v>
@@ -7205,18 +7205,18 @@
         <v>220.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B8" s="2">
         <v>234.0</v>
@@ -7225,137 +7225,137 @@
         <v>230.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B9" s="2">
         <v>87.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B10" s="2">
         <v>147.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="B11" s="2">
         <v>141.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="B12" s="2">
         <v>152.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="B13" s="2">
         <v>124.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="B14" s="2">
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="B15" s="2">
         <v>213.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="B16" s="2">
         <v>167.0</v>
@@ -7364,35 +7364,35 @@
         <v>161.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="B17" s="2">
         <v>138.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="B18" s="2">
         <v>243.0</v>
@@ -7401,154 +7401,154 @@
         <v>241.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="B19" s="2">
         <v>166.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>290</v>
+        <v>273</v>
       </c>
       <c r="B20" s="2">
         <v>31.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>293</v>
+        <v>275</v>
       </c>
       <c r="B21" s="2">
         <v>243.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>296</v>
+        <v>276</v>
       </c>
       <c r="B22" s="2">
         <v>224.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>298</v>
+        <v>278</v>
       </c>
       <c r="B23" s="2">
         <v>160.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="B24" s="2">
         <v>233.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>303</v>
+        <v>282</v>
       </c>
       <c r="B25" s="2">
         <v>148.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>305</v>
+        <v>284</v>
       </c>
       <c r="B26" s="2">
         <v>195.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>306</v>
+        <v>286</v>
       </c>
       <c r="B27" s="2">
         <v>194.0</v>
@@ -7557,35 +7557,35 @@
         <v>191.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="B28" s="2">
         <v>48.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>311</v>
+        <v>289</v>
       </c>
       <c r="B29" s="2">
         <v>237.0</v>
@@ -7594,18 +7594,18 @@
         <v>228.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>313</v>
+        <v>291</v>
       </c>
       <c r="B30" s="2">
         <v>234.0</v>
@@ -7614,18 +7614,18 @@
         <v>228.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>315</v>
+        <v>293</v>
       </c>
       <c r="B31" s="2">
         <v>210.0</v>
@@ -7634,13 +7634,13 @@
         <v>201.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -8632,27 +8632,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>263</v>
+        <v>299</v>
       </c>
       <c r="B2" s="2">
         <v>103.0</v>
@@ -8661,35 +8661,35 @@
         <v>101.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>266</v>
+        <v>300</v>
       </c>
       <c r="B3" s="2">
         <v>46.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>269</v>
+        <v>301</v>
       </c>
       <c r="B4" s="2">
         <v>54.0</v>
@@ -8698,86 +8698,86 @@
         <v>44.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>272</v>
+        <v>302</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>275</v>
+        <v>303</v>
       </c>
       <c r="B6" s="2">
         <v>68.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>276</v>
+        <v>304</v>
       </c>
       <c r="B7" s="2">
         <v>116.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>279</v>
+        <v>305</v>
       </c>
       <c r="B8" s="2">
         <v>227.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>282</v>
+        <v>306</v>
       </c>
       <c r="B9" s="2">
         <v>199.0</v>
@@ -8786,35 +8786,35 @@
         <v>189.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>285</v>
+        <v>307</v>
       </c>
       <c r="B10" s="2">
         <v>179.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="B11" s="2">
         <v>164.0</v>
@@ -8823,18 +8823,18 @@
         <v>157.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>289</v>
+        <v>309</v>
       </c>
       <c r="B12" s="2">
         <v>60.0</v>
@@ -8843,35 +8843,35 @@
         <v>55.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B13" s="2">
         <v>54.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>294</v>
+        <v>311</v>
       </c>
       <c r="B14" s="2">
         <v>28.0</v>
@@ -8880,86 +8880,86 @@
         <v>19.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>295</v>
+        <v>312</v>
       </c>
       <c r="B15" s="2">
         <v>208.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="B16" s="2">
         <v>243.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="B17" s="2">
         <v>38.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B18" s="2">
         <v>181.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="B19" s="2">
         <v>71.0</v>
@@ -8968,52 +8968,52 @@
         <v>61.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>304</v>
+        <v>317</v>
       </c>
       <c r="B20" s="2">
         <v>240.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B21" s="2">
         <v>195.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="B22" s="2">
         <v>58.0</v>
@@ -9022,18 +9022,18 @@
         <v>49.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
       <c r="B23" s="2">
         <v>140.0</v>
@@ -9042,115 +9042,115 @@
         <v>130.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="B24" s="2">
         <v>214.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B25" s="2">
         <v>199.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B26" s="2">
         <v>84.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B27" s="2">
         <v>188.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B28" s="2">
         <v>139.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B29" s="2">
         <v>57.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -9161,13 +9161,13 @@
         <v>224.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -9178,13 +9178,13 @@
         <v>91.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -10178,7 +10178,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>56</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10186,34 +10186,34 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>69</v>
+        <v>20</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>76</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>77</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>78</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -11222,27 +11222,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2">
         <v>84.0</v>
@@ -11251,18 +11251,18 @@
         <v>77.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B3" s="2">
         <v>49.0</v>
@@ -11271,18 +11271,18 @@
         <v>40.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B4" s="2">
         <v>136.0</v>
@@ -11291,18 +11291,18 @@
         <v>131.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B5" s="2">
         <v>171.0</v>
@@ -11311,18 +11311,18 @@
         <v>161.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2">
         <v>31.0</v>
@@ -11331,18 +11331,18 @@
         <v>23.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2">
         <v>66.0</v>
@@ -11351,18 +11351,18 @@
         <v>60.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2">
         <v>129.0</v>
@@ -11371,18 +11371,18 @@
         <v>123.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2">
         <v>47.0</v>
@@ -11391,18 +11391,18 @@
         <v>39.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2">
         <v>103.0</v>
@@ -11411,18 +11411,18 @@
         <v>98.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B11" s="2">
         <v>33.0</v>
@@ -11431,18 +11431,18 @@
         <v>31.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2">
         <v>221.0</v>
@@ -11451,18 +11451,18 @@
         <v>214.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2">
         <v>149.0</v>
@@ -11471,18 +11471,18 @@
         <v>145.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2">
         <v>197.0</v>
@@ -11491,18 +11491,18 @@
         <v>187.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2">
         <v>173.0</v>
@@ -11511,18 +11511,18 @@
         <v>164.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B16" s="2">
         <v>89.0</v>
@@ -11531,18 +11531,18 @@
         <v>86.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B17" s="2">
         <v>159.0</v>
@@ -11551,18 +11551,18 @@
         <v>154.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B18" s="2">
         <v>21.0</v>
@@ -11571,18 +11571,18 @@
         <v>17.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B19" s="2">
         <v>41.0</v>
@@ -11591,18 +11591,18 @@
         <v>37.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2">
         <v>153.0</v>
@@ -11611,18 +11611,18 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B21" s="2">
         <v>183.0</v>
@@ -11631,13 +11631,13 @@
         <v>175.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -12641,7 +12641,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -12652,7 +12652,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3">
@@ -12660,7 +12660,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>46</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
@@ -12668,7 +12668,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>47</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5">
@@ -12676,7 +12676,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>48</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
@@ -12684,7 +12684,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>49</v>
+        <v>16</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -13689,82 +13689,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -14766,29 +14766,29 @@
     <col customWidth="1" min="2" max="2" width="11.71"/>
     <col customWidth="1" min="3" max="3" width="14.14"/>
     <col customWidth="1" min="4" max="4" width="6.14"/>
-    <col customWidth="1" min="5" max="5" width="21.57"/>
+    <col customWidth="1" min="5" max="5" width="23.29"/>
     <col customWidth="1" min="6" max="6" width="5.43"/>
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
@@ -14799,19 +14799,19 @@
         <v>53.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; (ROW(A1)  &amp; ").png")</f>
-        <v>images/proudect (1).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; (ROW(A1)  &amp; ").png")</f>
+        <v>images/proudect(1).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>106</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>92.0</v>
@@ -14820,37 +14820,37 @@
         <v>87.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (2).png</v>
+        <v>images/proudect(2).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="B4" s="2">
         <v>198.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (3).png</v>
+        <v>images/proudect(3).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B5" s="2">
         <v>84.0</v>
@@ -14859,19 +14859,19 @@
         <v>77.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (4).png</v>
+        <v>images/proudect(4).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="B6" s="2">
         <v>249.0</v>
@@ -14880,37 +14880,37 @@
         <v>245.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (5).png</v>
+        <v>images/proudect(5).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>127</v>
+        <v>83</v>
       </c>
       <c r="B7" s="2">
         <v>181.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (6).png</v>
+        <v>images/proudect(6).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="B8" s="2">
         <v>49.0</v>
@@ -14919,73 +14919,73 @@
         <v>40.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (7).png</v>
+        <v>images/proudect(7).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>134</v>
+        <v>84</v>
       </c>
       <c r="B9" s="2">
         <v>240.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (8).png</v>
+        <v>images/proudect(8).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>137</v>
+        <v>85</v>
       </c>
       <c r="B10" s="2">
         <v>203.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (9).png</v>
+        <v>images/proudect(9).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>140</v>
+        <v>86</v>
       </c>
       <c r="B11" s="2">
         <v>109.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (10).png</v>
+        <v>images/proudect(10).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="B12" s="2">
         <v>31.0</v>
@@ -14994,55 +14994,55 @@
         <v>24.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (11).png</v>
+        <v>images/proudect(11).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>148</v>
+        <v>88</v>
       </c>
       <c r="B13" s="2">
         <v>250.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (12).png</v>
+        <v>images/proudect(12).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>150</v>
+        <v>89</v>
       </c>
       <c r="B14" s="2">
         <v>242.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (13).png</v>
+        <v>images/proudect(13).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>21</v>
+        <v>36</v>
       </c>
       <c r="B15" s="2">
         <v>136.0</v>
@@ -15051,145 +15051,145 @@
         <v>131.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (14).png</v>
+        <v>images/proudect(14).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>156</v>
+        <v>93</v>
       </c>
       <c r="B16" s="2">
         <v>85.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (15).png</v>
+        <v>images/proudect(15).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>160</v>
+        <v>95</v>
       </c>
       <c r="B17" s="2">
         <v>184.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (16).png</v>
+        <v>images/proudect(16).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>163</v>
+        <v>97</v>
       </c>
       <c r="B18" s="2">
         <v>23.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (17).png</v>
+        <v>images/proudect(17).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>167</v>
+        <v>101</v>
       </c>
       <c r="B19" s="2">
         <v>52.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (18).png</v>
+        <v>images/proudect(18).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>169</v>
+        <v>104</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (19).png</v>
+        <v>images/proudect(19).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>172</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2">
         <v>32.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (20).png</v>
+        <v>images/proudect(20).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>173</v>
+        <v>108</v>
       </c>
       <c r="B22" s="2">
         <v>144.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (21).png</v>
+        <v>images/proudect(21).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B23" s="2">
         <v>171.0</v>
@@ -15198,19 +15198,19 @@
         <v>161.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (22).png</v>
+        <v>images/proudect(22).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="B24" s="2">
         <v>31.0</v>
@@ -15219,73 +15219,73 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (23).png</v>
+        <v>images/proudect(23).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>174</v>
+        <v>114</v>
       </c>
       <c r="B25" s="2">
         <v>41.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (24).png</v>
+        <v>images/proudect(24).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="B26" s="2">
         <v>170.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (25).png</v>
+        <v>images/proudect(25).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>176</v>
+        <v>118</v>
       </c>
       <c r="B27" s="2">
         <v>199.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (26).png</v>
+        <v>images/proudect(26).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2">
         <v>66.0</v>
@@ -15294,37 +15294,37 @@
         <v>60.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (27).png</v>
+        <v>images/proudect(27).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>177</v>
+        <v>123</v>
       </c>
       <c r="B29" s="2">
         <v>208.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (28).png</v>
+        <v>images/proudect(28).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="B30" s="2">
         <v>129.0</v>
@@ -15333,32 +15333,32 @@
         <v>123.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (29).png</v>
+        <v>images/proudect(29).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>129</v>
       </c>
       <c r="B31" s="2">
         <v>96.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (30).png</v>
+        <v>images/proudect(30).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -16349,34 +16349,34 @@
     <col customWidth="1" min="2" max="2" width="11.71"/>
     <col customWidth="1" min="3" max="3" width="14.14"/>
     <col customWidth="1" min="4" max="4" width="6.14"/>
-    <col customWidth="1" min="5" max="5" width="21.57"/>
+    <col customWidth="1" min="5" max="5" width="23.29"/>
     <col customWidth="1" min="6" max="6" width="5.43"/>
     <col customWidth="1" min="7" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2">
         <v>47.0</v>
@@ -16385,109 +16385,109 @@
         <v>39.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; (ROW(A1) + 30) &amp; ").png"</f>
-        <v>images/proudect (31).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; (ROW(A1) + 30) &amp; ").png"</f>
+        <v>images/proudect(31).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B3" s="2">
         <v>151.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (32).png</v>
+        <v>images/proudect(32).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="B4" s="2">
         <v>17.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (33).png</v>
+        <v>images/proudect(33).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B5" s="2">
         <v>175.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (34).png</v>
+        <v>images/proudect(34).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="B6" s="2">
         <v>32.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (35).png</v>
+        <v>images/proudect(35).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="B7" s="2">
         <v>215.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (36).png</v>
+        <v>images/proudect(36).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="B8" s="2">
         <v>103.0</v>
@@ -16496,37 +16496,37 @@
         <v>98.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (37).png</v>
+        <v>images/proudect(37).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="B9" s="2">
         <v>72.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (38).png</v>
+        <v>images/proudect(38).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B10" s="2">
         <v>33.0</v>
@@ -16535,73 +16535,73 @@
         <v>31.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (39).png</v>
+        <v>images/proudect(39).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B11" s="2">
         <v>187.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (40).png</v>
+        <v>images/proudect(40).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="B12" s="2">
         <v>125.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (41).png</v>
+        <v>images/proudect(41).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="B13" s="2">
         <v>80.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (42).png</v>
+        <v>images/proudect(42).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2">
         <v>221.0</v>
@@ -16610,145 +16610,145 @@
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (43).png</v>
+        <v>images/proudect(43).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>89</v>
+        <v>105</v>
       </c>
       <c r="B15" s="2">
         <v>231.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (44).png</v>
+        <v>images/proudect(44).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B16" s="2">
         <v>201.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (45).png</v>
+        <v>images/proudect(45).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B17" s="2">
         <v>162.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (46).png</v>
+        <v>images/proudect(46).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B18" s="2">
         <v>42.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (47).png</v>
+        <v>images/proudect(47).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="B19" s="2">
         <v>33.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (48).png</v>
+        <v>images/proudect(48).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="B20" s="2">
         <v>87.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (49).png</v>
+        <v>images/proudect(49).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B21" s="2">
         <v>110.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (50).png</v>
+        <v>images/proudect(50).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B22" s="2">
         <v>69.0</v>
@@ -16757,37 +16757,37 @@
         <v>62.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (51).png</v>
+        <v>images/proudect(51).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B23" s="2">
         <v>199.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (52).png</v>
+        <v>images/proudect(52).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2">
         <v>149.0</v>
@@ -16796,19 +16796,19 @@
         <v>145.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (53).png</v>
+        <v>images/proudect(53).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2">
         <v>197.0</v>
@@ -16817,19 +16817,19 @@
         <v>187.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (54).png</v>
+        <v>images/proudect(54).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="B26" s="2">
         <v>84.0</v>
@@ -16838,73 +16838,73 @@
         <v>76.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (55).png</v>
+        <v>images/proudect(55).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="B27" s="2">
         <v>119.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (56).png</v>
+        <v>images/proudect(56).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>113</v>
+        <v>125</v>
       </c>
       <c r="B28" s="2">
         <v>110.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (57).png</v>
+        <v>images/proudect(57).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B29" s="2">
         <v>212.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (58).png</v>
+        <v>images/proudect(58).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>37</v>
+        <v>52</v>
       </c>
       <c r="B30" s="2">
         <v>173.0</v>
@@ -16913,32 +16913,32 @@
         <v>164.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (59).png</v>
+        <v>images/proudect(59).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B31" s="2">
         <v>147.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (60).png</v>
+        <v>images/proudect(60).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -17936,27 +17936,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="B2" s="2">
         <v>189.0</v>
@@ -17965,19 +17965,19 @@
         <v>179.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; (ROW(A1) + 60) &amp; ").png"</f>
-        <v>images/proudect (61).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; (ROW(A1) + 60) &amp; ").png"</f>
+        <v>images/proudect(61).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>53</v>
       </c>
       <c r="B3" s="2">
         <v>89.0</v>
@@ -17986,109 +17986,109 @@
         <v>86.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (62).png</v>
+        <v>images/proudect(62).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="B4" s="2">
         <v>105.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (63).png</v>
+        <v>images/proudect(63).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>108</v>
+        <v>121</v>
       </c>
       <c r="B5" s="2">
         <v>25.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (64).png</v>
+        <v>images/proudect(64).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="B6" s="2">
         <v>49.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (65).png</v>
+        <v>images/proudect(65).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>114</v>
+        <v>126</v>
       </c>
       <c r="B7" s="2">
         <v>47.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (66).png</v>
+        <v>images/proudect(66).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>118</v>
+        <v>128</v>
       </c>
       <c r="B8" s="2">
         <v>164.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (67).png</v>
+        <v>images/proudect(67).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B9" s="2">
         <v>159.0</v>
@@ -18097,109 +18097,109 @@
         <v>154.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (68).png</v>
+        <v>images/proudect(68).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="B10" s="2">
         <v>124.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (69).png</v>
+        <v>images/proudect(69).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B11" s="2">
         <v>66.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (70).png</v>
+        <v>images/proudect(70).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B12" s="2">
         <v>38.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (71).png</v>
+        <v>images/proudect(71).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="B13" s="2">
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (72).png</v>
+        <v>images/proudect(72).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="B14" s="2">
         <v>73.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (73).png</v>
+        <v>images/proudect(73).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B15" s="2">
         <v>21.0</v>
@@ -18208,19 +18208,19 @@
         <v>17.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (74).png</v>
+        <v>images/proudect(74).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="B16" s="2">
         <v>41.0</v>
@@ -18229,73 +18229,73 @@
         <v>37.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (75).png</v>
+        <v>images/proudect(75).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B17" s="2">
         <v>98.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (76).png</v>
+        <v>images/proudect(76).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="B18" s="2">
         <v>40.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (77).png</v>
+        <v>images/proudect(77).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B19" s="2">
         <v>53.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (78).png</v>
+        <v>images/proudect(78).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="B20" s="2">
         <v>153.0</v>
@@ -18304,37 +18304,37 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (79).png</v>
+        <v>images/proudect(79).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="B21" s="2">
         <v>157.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (80).png</v>
+        <v>images/proudect(80).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="B22" s="2">
         <v>183.0</v>
@@ -18343,19 +18343,19 @@
         <v>175.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (81).png</v>
+        <v>images/proudect(81).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="B23" s="2">
         <v>38.0</v>
@@ -18364,91 +18364,91 @@
         <v>33.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (82).png</v>
+        <v>images/proudect(82).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="B24" s="2">
         <v>206.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (83).png</v>
+        <v>images/proudect(83).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="B25" s="2">
         <v>39.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (84).png</v>
+        <v>images/proudect(84).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="B26" s="2">
         <v>130.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (85).png</v>
+        <v>images/proudect(85).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>165</v>
+        <v>151</v>
       </c>
       <c r="B27" s="2">
         <v>145.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (86).png</v>
+        <v>images/proudect(86).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="B28" s="2">
         <v>75.0</v>
@@ -18457,55 +18457,55 @@
         <v>68.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (87).png</v>
+        <v>images/proudect(87).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="B29" s="2">
         <v>221.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (88).png</v>
+        <v>images/proudect(88).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="B30" s="2">
         <v>122.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (89).png</v>
+        <v>images/proudect(89).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="B31" s="2">
         <v>34.0</v>
@@ -18514,14 +18514,14 @@
         <v>25.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect (90).png</v>
+        <v>images/proudect(90).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -19513,44 +19513,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="B2" s="2">
         <v>161.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="B3" s="2">
         <v>62.0</v>
@@ -19559,18 +19559,18 @@
         <v>52.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="B4" s="2">
         <v>164.0</v>
@@ -19579,171 +19579,171 @@
         <v>155.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>102</v>
+        <v>144</v>
       </c>
       <c r="B5" s="2">
         <v>91.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>104</v>
+        <v>146</v>
       </c>
       <c r="B6" s="2">
         <v>120.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
       <c r="B7" s="2">
         <v>240.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>110</v>
+        <v>150</v>
       </c>
       <c r="B8" s="2">
         <v>68.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>112</v>
+        <v>152</v>
       </c>
       <c r="B9" s="2">
         <v>40.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>116</v>
+        <v>154</v>
       </c>
       <c r="B10" s="2">
         <v>137.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>119</v>
+        <v>156</v>
       </c>
       <c r="B11" s="2">
         <v>51.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="B12" s="2">
         <v>211.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>121</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2">
         <v>236.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>125</v>
+        <v>161</v>
       </c>
       <c r="B14" s="2">
         <v>69.0</v>
@@ -19752,18 +19752,18 @@
         <v>64.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>128</v>
+        <v>162</v>
       </c>
       <c r="B15" s="2">
         <v>78.0</v>
@@ -19772,120 +19772,120 @@
         <v>69.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="B16" s="2">
         <v>231.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>132</v>
+        <v>164</v>
       </c>
       <c r="B17" s="2">
         <v>155.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>135</v>
+        <v>165</v>
       </c>
       <c r="B18" s="2">
         <v>156.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="B19" s="2">
         <v>168.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>138</v>
+        <v>167</v>
       </c>
       <c r="B20" s="2">
         <v>70.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>141</v>
+        <v>168</v>
       </c>
       <c r="B21" s="2">
         <v>136.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="B22" s="2">
         <v>125.0</v>
@@ -19894,35 +19894,35 @@
         <v>119.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>144</v>
+        <v>170</v>
       </c>
       <c r="B23" s="2">
         <v>135.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>147</v>
+        <v>171</v>
       </c>
       <c r="B24" s="2">
         <v>250.0</v>
@@ -19931,69 +19931,69 @@
         <v>244.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>149</v>
+        <v>172</v>
       </c>
       <c r="B25" s="2">
         <v>83.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="B26" s="2">
         <v>117.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>153</v>
+        <v>174</v>
       </c>
       <c r="B27" s="2">
         <v>240.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>155</v>
+        <v>175</v>
       </c>
       <c r="B28" s="2">
         <v>174.0</v>
@@ -20002,35 +20002,35 @@
         <v>165.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B29" s="2">
         <v>152.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="B30" s="2">
         <v>162.0</v>
@@ -20039,30 +20039,30 @@
         <v>152.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>164</v>
+        <v>178</v>
       </c>
       <c r="B31" s="2">
         <v>189.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>15</v>
+        <v>28</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -26,10 +26,22 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="329">
   <si>
+    <t>صورة</t>
+  </si>
+  <si>
     <t>رقم_الصفحة</t>
   </si>
   <si>
-    <t>صورة</t>
+    <t>القسم_المستهدف</t>
+  </si>
+  <si>
+    <t>images/slider_1.jpg</t>
+  </si>
+  <si>
+    <t>الفواكه والخضروات</t>
+  </si>
+  <si>
+    <t>images/offer_page_1.jpg</t>
   </si>
   <si>
     <t>مكان_البانر</t>
@@ -38,120 +50,108 @@
     <t>الاسم</t>
   </si>
   <si>
+    <t>images/offer_page_2.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_3.jpg</t>
+  </si>
+  <si>
+    <t>images/slider_2.jpg</t>
+  </si>
+  <si>
+    <t>images/offer_page_4.jpg</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات</t>
+  </si>
+  <si>
+    <t>images/offer_page_5.jpg</t>
+  </si>
+  <si>
     <t>السعر الأساسي</t>
   </si>
   <si>
     <t>رئيسي_علوي</t>
   </si>
   <si>
-    <t>القسم_المستهدف</t>
+    <t>المشروبات</t>
   </si>
   <si>
     <t>السعر بعد الخصم</t>
   </si>
   <si>
-    <t>images/offer_page_1.jpg</t>
+    <t>images/top_banner.jpg</t>
+  </si>
+  <si>
+    <t>البقالة</t>
   </si>
   <si>
     <t>الوحدة</t>
   </si>
   <si>
-    <t>images/slider_1.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_2.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_3.jpg</t>
-  </si>
-  <si>
-    <t>الفواكه والخضروات</t>
+    <t>مقسم_يمين</t>
+  </si>
+  <si>
+    <t>images/split1.jpg</t>
+  </si>
+  <si>
+    <t>الألبان</t>
+  </si>
+  <si>
+    <t>مقسم_يسار</t>
   </si>
   <si>
     <t>متوفر</t>
   </si>
   <si>
-    <t>images/offer_page_4.jpg</t>
-  </si>
-  <si>
-    <t>images/offer_page_5.jpg</t>
-  </si>
-  <si>
-    <t>images/top_banner.jpg</t>
-  </si>
-  <si>
-    <t>images/slider_2.jpg</t>
+    <t>images/split2.jpg</t>
+  </si>
+  <si>
+    <t>المخبوزات</t>
+  </si>
+  <si>
+    <t>رئيسي_ثابت</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات</t>
   </si>
   <si>
     <t>خيار</t>
   </si>
   <si>
-    <t>مقسم_يمين</t>
-  </si>
-  <si>
-    <t>التسالي والمكسرات</t>
-  </si>
-  <si>
-    <t>images/split1.jpg</t>
-  </si>
-  <si>
-    <t>مقسم_يسار</t>
+    <t>images/static_banner.jpg</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي</t>
+  </si>
+  <si>
+    <t>منظفات</t>
   </si>
   <si>
     <t>لتر</t>
   </si>
   <si>
-    <t>المشروبات</t>
-  </si>
-  <si>
     <t>images/placeholder.png</t>
   </si>
   <si>
-    <t>images/split2.jpg</t>
-  </si>
-  <si>
     <t>نعم</t>
   </si>
   <si>
-    <t>البقالة</t>
-  </si>
-  <si>
-    <t>رئيسي_ثابت</t>
-  </si>
-  <si>
-    <t>images/static_banner.jpg</t>
-  </si>
-  <si>
     <t>موز</t>
   </si>
   <si>
-    <t>الألبان</t>
-  </si>
-  <si>
     <t>كيلو</t>
   </si>
   <si>
-    <t>المخبوزات</t>
-  </si>
-  <si>
     <t>خيار (14)</t>
   </si>
   <si>
-    <t>التوابل والبهارات</t>
-  </si>
-  <si>
-    <t>الحلويات والكاندي</t>
-  </si>
-  <si>
     <t>بطاطس (22)</t>
   </si>
   <si>
     <t>بصل (23)</t>
   </si>
   <si>
-    <t>منظفات</t>
-  </si>
-  <si>
     <t>قطعة</t>
   </si>
   <si>
@@ -266,6 +266,9 @@
     <t>طماطم</t>
   </si>
   <si>
+    <t>لب سوري</t>
+  </si>
+  <si>
     <t>بطاطس</t>
   </si>
   <si>
@@ -275,12 +278,24 @@
     <t>جزر</t>
   </si>
   <si>
+    <t>سوداني</t>
+  </si>
+  <si>
     <t>تفاح</t>
   </si>
   <si>
+    <t>لوز</t>
+  </si>
+  <si>
     <t>برتقال</t>
   </si>
   <si>
+    <t>عين جمل</t>
+  </si>
+  <si>
+    <t>كاجو</t>
+  </si>
+  <si>
     <t>عنب</t>
   </si>
   <si>
@@ -296,106 +311,142 @@
     <t>بصل (13)</t>
   </si>
   <si>
-    <t>لب سوري</t>
-  </si>
-  <si>
-    <t>سوداني</t>
-  </si>
-  <si>
-    <t>لوز</t>
+    <t>فشار</t>
   </si>
   <si>
     <t>جزر (15)</t>
   </si>
   <si>
-    <t>عين جمل</t>
+    <t>فستق</t>
   </si>
   <si>
     <t>تفاح (16)</t>
   </si>
   <si>
-    <t>كاجو</t>
+    <t>لب سوبر (11)</t>
   </si>
   <si>
     <t>موز (17)</t>
   </si>
   <si>
-    <t>فشار</t>
-  </si>
-  <si>
-    <t>فستق</t>
-  </si>
-  <si>
-    <t>لب سوبر (11)</t>
+    <t>لب سوري (12)</t>
+  </si>
+  <si>
+    <t>شاي</t>
   </si>
   <si>
     <t>برتقال (18)</t>
   </si>
   <si>
-    <t>شاي</t>
-  </si>
-  <si>
-    <t>لب سوري (12)</t>
+    <t>لوز (14)</t>
+  </si>
+  <si>
+    <t>أرز</t>
   </si>
   <si>
     <t>عنب (19)</t>
   </si>
   <si>
-    <t>لوز (14)</t>
+    <t>عين جمل (15)</t>
+  </si>
+  <si>
+    <t>مكرونة</t>
   </si>
   <si>
     <t>مانجو (20)</t>
   </si>
   <si>
-    <t>عين جمل (15)</t>
+    <t>كاجو (16)</t>
+  </si>
+  <si>
+    <t>سكر</t>
   </si>
   <si>
     <t>طماطم (21)</t>
   </si>
   <si>
-    <t>كاجو (16)</t>
+    <t>زيت</t>
   </si>
   <si>
     <t>شيبسي (17)</t>
   </si>
   <si>
+    <t>سمنة</t>
+  </si>
+  <si>
     <t>فشار (18)</t>
   </si>
   <si>
+    <t>صلصة</t>
+  </si>
+  <si>
     <t>مقرمشات (19)</t>
   </si>
   <si>
+    <t>تونة</t>
+  </si>
+  <si>
     <t>فستق (20)</t>
   </si>
   <si>
+    <t>فول</t>
+  </si>
+  <si>
     <t>خيار (24)</t>
   </si>
   <si>
+    <t>عدس</t>
+  </si>
+  <si>
     <t>لب سوبر (21)</t>
   </si>
   <si>
+    <t>دقيق</t>
+  </si>
+  <si>
+    <t>جزر (25)</t>
+  </si>
+  <si>
+    <t>أرز (11)</t>
+  </si>
+  <si>
     <t>لب سوري (22)</t>
   </si>
   <si>
-    <t>جزر (25)</t>
+    <t>مكرونة (12)</t>
   </si>
   <si>
     <t>تفاح (26)</t>
   </si>
   <si>
+    <t>سكر (13)</t>
+  </si>
+  <si>
+    <t>زيت (14)</t>
+  </si>
+  <si>
     <t>نسكافيه</t>
   </si>
   <si>
+    <t>سمنة (15)</t>
+  </si>
+  <si>
+    <t>برتقال (28)</t>
+  </si>
+  <si>
     <t>عين جمل (25)</t>
   </si>
   <si>
     <t>عصير برتقال</t>
   </si>
   <si>
+    <t>صلصة (16)</t>
+  </si>
+  <si>
     <t>كاجو (26)</t>
   </si>
   <si>
-    <t>برتقال (28)</t>
+    <t>تونة (17)</t>
   </si>
   <si>
     <t>عصير تفاح</t>
@@ -404,36 +455,75 @@
     <t>شيبسي (27)</t>
   </si>
   <si>
+    <t>فول (18)</t>
+  </si>
+  <si>
+    <t>مانجو (30)</t>
+  </si>
+  <si>
+    <t>عدس (19)</t>
+  </si>
+  <si>
     <t>كولا</t>
   </si>
   <si>
     <t>فشار (28)</t>
   </si>
   <si>
+    <t>دقيق (20)</t>
+  </si>
+  <si>
     <t>مياه معدنية</t>
   </si>
   <si>
-    <t>مانجو (30)</t>
+    <t>أرز (21)</t>
   </si>
   <si>
     <t>فستق (30)</t>
   </si>
   <si>
+    <t>مكرونة (22)</t>
+  </si>
+  <si>
     <t>كاكاو</t>
   </si>
   <si>
+    <t>سكر (23)</t>
+  </si>
+  <si>
+    <t>زيت (24)</t>
+  </si>
+  <si>
     <t>نعناع</t>
   </si>
   <si>
     <t>شاي (11)</t>
   </si>
   <si>
+    <t>سمنة (25)</t>
+  </si>
+  <si>
+    <t>صلصة (26)</t>
+  </si>
+  <si>
     <t>قهوة (12)</t>
   </si>
   <si>
+    <t>تونة (27)</t>
+  </si>
+  <si>
     <t>نسكافيه (13)</t>
   </si>
   <si>
+    <t>فول (28)</t>
+  </si>
+  <si>
+    <t>عدس (29)</t>
+  </si>
+  <si>
+    <t>دقيق (30)</t>
+  </si>
+  <si>
     <t>كولا (16)</t>
   </si>
   <si>
@@ -443,547 +533,457 @@
     <t>مشروب طاقة (18)</t>
   </si>
   <si>
-    <t>أرز</t>
-  </si>
-  <si>
     <t>نعناع (20)</t>
   </si>
   <si>
-    <t>مكرونة</t>
-  </si>
-  <si>
-    <t>سكر</t>
-  </si>
-  <si>
     <t>قهوة (22)</t>
   </si>
   <si>
-    <t>زيت</t>
-  </si>
-  <si>
     <t>نسكافيه (23)</t>
   </si>
   <si>
-    <t>سمنة</t>
-  </si>
-  <si>
     <t>عصير برتقال (24)</t>
   </si>
   <si>
-    <t>صلصة</t>
-  </si>
-  <si>
     <t>عصير تفاح (25)</t>
   </si>
   <si>
-    <t>تونة</t>
-  </si>
-  <si>
     <t>كولا (26)</t>
   </si>
   <si>
-    <t>فول</t>
-  </si>
-  <si>
     <t>مياه معدنية (27)</t>
   </si>
   <si>
-    <t>عدس</t>
-  </si>
-  <si>
     <t>مشروب طاقة (28)</t>
   </si>
   <si>
-    <t>دقيق</t>
-  </si>
-  <si>
     <t>كاكاو (29)</t>
   </si>
   <si>
-    <t>أرز (11)</t>
-  </si>
-  <si>
     <t>نعناع (30)</t>
   </si>
   <si>
-    <t>مكرونة (12)</t>
-  </si>
-  <si>
-    <t>سكر (13)</t>
-  </si>
-  <si>
-    <t>زيت (14)</t>
-  </si>
-  <si>
-    <t>سمنة (15)</t>
-  </si>
-  <si>
-    <t>صلصة (16)</t>
-  </si>
-  <si>
-    <t>تونة (17)</t>
-  </si>
-  <si>
-    <t>فول (18)</t>
-  </si>
-  <si>
-    <t>عدس (19)</t>
-  </si>
-  <si>
-    <t>دقيق (20)</t>
-  </si>
-  <si>
-    <t>أرز (21)</t>
-  </si>
-  <si>
-    <t>مكرونة (22)</t>
-  </si>
-  <si>
-    <t>سكر (23)</t>
-  </si>
-  <si>
-    <t>زيت (24)</t>
-  </si>
-  <si>
-    <t>سمنة (25)</t>
-  </si>
-  <si>
-    <t>صلصة (26)</t>
-  </si>
-  <si>
-    <t>تونة (27)</t>
-  </si>
-  <si>
-    <t>فول (28)</t>
-  </si>
-  <si>
-    <t>عدس (29)</t>
-  </si>
-  <si>
-    <t>دقيق (30)</t>
+    <t>لبن كامل الدسم</t>
+  </si>
+  <si>
+    <t>جبنة بيضاء</t>
+  </si>
+  <si>
+    <t>جبنة رومي</t>
+  </si>
+  <si>
+    <t>زبادي</t>
+  </si>
+  <si>
+    <t>قشطة</t>
+  </si>
+  <si>
+    <t>زبدة</t>
+  </si>
+  <si>
+    <t>جبنة شيدر</t>
+  </si>
+  <si>
+    <t>جبنة نستو</t>
+  </si>
+  <si>
+    <t>لبن رايب</t>
+  </si>
+  <si>
+    <t>سمن بلدي</t>
+  </si>
+  <si>
+    <t>لبن كامل الدسم (11)</t>
+  </si>
+  <si>
+    <t>جبنة بيضاء (12)</t>
+  </si>
+  <si>
+    <t>جبنة رومي (13)</t>
+  </si>
+  <si>
+    <t>زبادي (14)</t>
+  </si>
+  <si>
+    <t>قشطة (15)</t>
+  </si>
+  <si>
+    <t>زبدة (16)</t>
+  </si>
+  <si>
+    <t>جبنة شيدر (17)</t>
+  </si>
+  <si>
+    <t>جبنة نستو (18)</t>
+  </si>
+  <si>
+    <t>لبن رايب (19)</t>
+  </si>
+  <si>
+    <t>سمن بلدي (20)</t>
+  </si>
+  <si>
+    <t>لبن كامل الدسم (21)</t>
+  </si>
+  <si>
+    <t>جبنة بيضاء (22)</t>
+  </si>
+  <si>
+    <t>جبنة رومي (23)</t>
+  </si>
+  <si>
+    <t>زبادي (24)</t>
+  </si>
+  <si>
+    <t>قشطة (25)</t>
+  </si>
+  <si>
+    <t>زبدة (26)</t>
+  </si>
+  <si>
+    <t>جبنة شيدر (27)</t>
+  </si>
+  <si>
+    <t>جبنة نستو (28)</t>
+  </si>
+  <si>
+    <t>لبن رايب (29)</t>
+  </si>
+  <si>
+    <t>سمن بلدي (30)</t>
   </si>
   <si>
     <t>عيش فينو</t>
   </si>
   <si>
-    <t>لبن كامل الدسم</t>
-  </si>
-  <si>
     <t>عيش بلدي</t>
   </si>
   <si>
-    <t>جبنة بيضاء</t>
-  </si>
-  <si>
     <t>باتيه</t>
   </si>
   <si>
-    <t>جبنة رومي</t>
+    <t>كمون</t>
   </si>
   <si>
     <t>كرواسون</t>
   </si>
   <si>
-    <t>زبادي</t>
+    <t>فلفل أسود</t>
   </si>
   <si>
     <t>بقسماط</t>
   </si>
   <si>
-    <t>قشطة</t>
+    <t>كركم</t>
   </si>
   <si>
     <t>توست أبيض</t>
   </si>
   <si>
-    <t>زبدة</t>
+    <t>كزبرة</t>
   </si>
   <si>
     <t>توست أسمر</t>
   </si>
   <si>
+    <t>بهارات مشكلة</t>
+  </si>
+  <si>
     <t>فطير</t>
   </si>
   <si>
-    <t>جبنة شيدر</t>
+    <t>قرفة</t>
   </si>
   <si>
     <t>كيك</t>
   </si>
   <si>
+    <t>حبهان</t>
+  </si>
+  <si>
     <t>بسكويت</t>
   </si>
   <si>
-    <t>جبنة نستو</t>
+    <t>ورق لورا</t>
   </si>
   <si>
     <t>عيش فينو (11)</t>
   </si>
   <si>
-    <t>لبن رايب</t>
+    <t>بابريكا</t>
   </si>
   <si>
     <t>عيش بلدي (12)</t>
   </si>
   <si>
-    <t>سمن بلدي</t>
+    <t>قرنفل</t>
   </si>
   <si>
     <t>باتيه (13)</t>
   </si>
   <si>
+    <t>كمون (11)</t>
+  </si>
+  <si>
     <t>كرواسون (14)</t>
   </si>
   <si>
-    <t>كمون</t>
-  </si>
-  <si>
-    <t>لبن كامل الدسم (11)</t>
+    <t>فلفل أسود (12)</t>
   </si>
   <si>
     <t>بقسماط (15)</t>
   </si>
   <si>
-    <t>فلفل أسود</t>
+    <t>كركم (13)</t>
   </si>
   <si>
     <t>توست أبيض (16)</t>
   </si>
   <si>
-    <t>جبنة بيضاء (12)</t>
+    <t>كزبرة (14)</t>
   </si>
   <si>
     <t>توست أسمر (17)</t>
   </si>
   <si>
-    <t>جبنة رومي (13)</t>
+    <t>بهارات مشكلة (15)</t>
   </si>
   <si>
     <t>فطير (18)</t>
   </si>
   <si>
-    <t>كركم</t>
+    <t>قرفة (16)</t>
   </si>
   <si>
     <t>كيك (19)</t>
   </si>
   <si>
-    <t>زبادي (14)</t>
+    <t>شوكولاتة</t>
+  </si>
+  <si>
+    <t>حبهان (17)</t>
   </si>
   <si>
     <t>بسكويت (20)</t>
   </si>
   <si>
-    <t>كزبرة</t>
-  </si>
-  <si>
-    <t>قشطة (15)</t>
+    <t>ورق لورا (18)</t>
+  </si>
+  <si>
+    <t>جيلي</t>
   </si>
   <si>
     <t>عيش فينو (21)</t>
   </si>
   <si>
-    <t>زبدة (16)</t>
-  </si>
-  <si>
-    <t>بهارات مشكلة</t>
+    <t>بابريكا (19)</t>
+  </si>
+  <si>
+    <t>كريم كراميل</t>
   </si>
   <si>
     <t>عيش بلدي (22)</t>
   </si>
   <si>
-    <t>جبنة شيدر (17)</t>
+    <t>قرنفل (20)</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية</t>
   </si>
   <si>
     <t>باتيه (23)</t>
   </si>
   <si>
-    <t>قرفة</t>
+    <t>كمون (21)</t>
   </si>
   <si>
     <t>كرواسون (24)</t>
   </si>
   <si>
-    <t>جبنة نستو (18)</t>
-  </si>
-  <si>
-    <t>حبهان</t>
+    <t>ملبن</t>
+  </si>
+  <si>
+    <t>فلفل أسود (22)</t>
   </si>
   <si>
     <t>بقسماط (25)</t>
   </si>
   <si>
-    <t>لبن رايب (19)</t>
-  </si>
-  <si>
-    <t>شوكولاتة</t>
+    <t>بسكويت شيكولاتة</t>
+  </si>
+  <si>
+    <t>كركم (23)</t>
   </si>
   <si>
     <t>توست أبيض (26)</t>
   </si>
   <si>
-    <t>سمن بلدي (20)</t>
-  </si>
-  <si>
-    <t>ورق لورا</t>
-  </si>
-  <si>
-    <t>جيلي</t>
+    <t>لبان</t>
+  </si>
+  <si>
+    <t>كزبرة (24)</t>
   </si>
   <si>
     <t>توست أسمر (27)</t>
   </si>
   <si>
-    <t>بابريكا</t>
-  </si>
-  <si>
-    <t>لبن كامل الدسم (21)</t>
-  </si>
-  <si>
-    <t>كريم كراميل</t>
+    <t>مربى</t>
+  </si>
+  <si>
+    <t>بهارات مشكلة (25)</t>
   </si>
   <si>
     <t>فطير (28)</t>
   </si>
   <si>
-    <t>جبنة بيضاء (22)</t>
-  </si>
-  <si>
-    <t>قرنفل</t>
-  </si>
-  <si>
-    <t>حلاوة طحينية</t>
+    <t>عسل نحل</t>
   </si>
   <si>
     <t>كيك (29)</t>
   </si>
   <si>
-    <t>ملبن</t>
-  </si>
-  <si>
-    <t>كمون (11)</t>
-  </si>
-  <si>
-    <t>جبنة رومي (23)</t>
-  </si>
-  <si>
-    <t>بسكويت شيكولاتة</t>
+    <t>كيك شوكولاتة</t>
+  </si>
+  <si>
+    <t>قرفة (26)</t>
   </si>
   <si>
     <t>بسكويت (30)</t>
   </si>
   <si>
-    <t>فلفل أسود (12)</t>
-  </si>
-  <si>
-    <t>زبادي (24)</t>
-  </si>
-  <si>
-    <t>لبان</t>
-  </si>
-  <si>
-    <t>كركم (13)</t>
-  </si>
-  <si>
-    <t>قشطة (25)</t>
-  </si>
-  <si>
-    <t>مربى</t>
-  </si>
-  <si>
-    <t>كزبرة (14)</t>
-  </si>
-  <si>
-    <t>عسل نحل</t>
-  </si>
-  <si>
-    <t>زبدة (26)</t>
-  </si>
-  <si>
-    <t>كيك شوكولاتة</t>
-  </si>
-  <si>
-    <t>جبنة شيدر (27)</t>
-  </si>
-  <si>
     <t>شوكولاتة (11)</t>
   </si>
   <si>
-    <t>جبنة نستو (28)</t>
+    <t>حبهان (27)</t>
   </si>
   <si>
     <t>جيلي (12)</t>
   </si>
   <si>
-    <t>لبن رايب (29)</t>
+    <t>ورق لورا (28)</t>
   </si>
   <si>
     <t>كريم كراميل (13)</t>
   </si>
   <si>
+    <t>بابريكا (29)</t>
+  </si>
+  <si>
     <t>حلاوة طحينية (14)</t>
   </si>
   <si>
-    <t>سمن بلدي (30)</t>
-  </si>
-  <si>
     <t>ملبن (15)</t>
   </si>
   <si>
+    <t>قرنفل (30)</t>
+  </si>
+  <si>
     <t>بسكويت شيكولاتة (16)</t>
   </si>
   <si>
     <t>لبان (17)</t>
   </si>
   <si>
-    <t>بهارات مشكلة (15)</t>
-  </si>
-  <si>
     <t>مربى (18)</t>
   </si>
   <si>
-    <t>قرفة (16)</t>
-  </si>
-  <si>
     <t>عسل نحل (19)</t>
   </si>
   <si>
-    <t>حبهان (17)</t>
+    <t>مسحوق غسيل</t>
+  </si>
+  <si>
+    <t>صابون سائل</t>
+  </si>
+  <si>
+    <t>كلور</t>
+  </si>
+  <si>
+    <t>معطر جو</t>
+  </si>
+  <si>
+    <t>ديتول</t>
+  </si>
+  <si>
+    <t>صابون وجه</t>
   </si>
   <si>
     <t>كيك شوكولاتة (20)</t>
   </si>
   <si>
+    <t>شامبو</t>
+  </si>
+  <si>
+    <t>مناديل</t>
+  </si>
+  <si>
     <t>شوكولاتة (21)</t>
   </si>
   <si>
-    <t>ورق لورا (18)</t>
+    <t>سلك مواعين</t>
+  </si>
+  <si>
+    <t>ملمع زجاج</t>
   </si>
   <si>
     <t>جيلي (22)</t>
   </si>
   <si>
-    <t>بابريكا (19)</t>
+    <t>مسحوق غسيل (11)</t>
   </si>
   <si>
     <t>كريم كراميل (23)</t>
   </si>
   <si>
-    <t>قرنفل (20)</t>
+    <t>صابون سائل (12)</t>
   </si>
   <si>
     <t>حلاوة طحينية (24)</t>
   </si>
   <si>
-    <t>كمون (21)</t>
+    <t>كلور (13)</t>
   </si>
   <si>
     <t>ملبن (25)</t>
   </si>
   <si>
-    <t>فلفل أسود (22)</t>
+    <t>معطر جو (14)</t>
+  </si>
+  <si>
+    <t>ديتول (15)</t>
   </si>
   <si>
     <t>بسكويت شيكولاتة (26)</t>
   </si>
   <si>
+    <t>صابون وجه (16)</t>
+  </si>
+  <si>
+    <t>شامبو (17)</t>
+  </si>
+  <si>
     <t>لبان (27)</t>
   </si>
   <si>
-    <t>كركم (23)</t>
+    <t>مناديل (18)</t>
   </si>
   <si>
     <t>مربى (28)</t>
   </si>
   <si>
-    <t>كزبرة (24)</t>
+    <t>سلك مواعين (19)</t>
+  </si>
+  <si>
+    <t>ملمع زجاج (20)</t>
   </si>
   <si>
     <t>عسل نحل (29)</t>
   </si>
   <si>
-    <t>بهارات مشكلة (25)</t>
+    <t>مسحوق غسيل (21)</t>
   </si>
   <si>
     <t>كيك شوكولاتة (30)</t>
-  </si>
-  <si>
-    <t>قرفة (26)</t>
-  </si>
-  <si>
-    <t>حبهان (27)</t>
-  </si>
-  <si>
-    <t>ورق لورا (28)</t>
-  </si>
-  <si>
-    <t>بابريكا (29)</t>
-  </si>
-  <si>
-    <t>قرنفل (30)</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل</t>
-  </si>
-  <si>
-    <t>صابون سائل</t>
-  </si>
-  <si>
-    <t>كلور</t>
-  </si>
-  <si>
-    <t>معطر جو</t>
-  </si>
-  <si>
-    <t>ديتول</t>
-  </si>
-  <si>
-    <t>صابون وجه</t>
-  </si>
-  <si>
-    <t>شامبو</t>
-  </si>
-  <si>
-    <t>مناديل</t>
-  </si>
-  <si>
-    <t>سلك مواعين</t>
-  </si>
-  <si>
-    <t>ملمع زجاج</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل (11)</t>
-  </si>
-  <si>
-    <t>صابون سائل (12)</t>
-  </si>
-  <si>
-    <t>كلور (13)</t>
-  </si>
-  <si>
-    <t>معطر جو (14)</t>
-  </si>
-  <si>
-    <t>ديتول (15)</t>
-  </si>
-  <si>
-    <t>صابون وجه (16)</t>
-  </si>
-  <si>
-    <t>شامبو (17)</t>
-  </si>
-  <si>
-    <t>مناديل (18)</t>
-  </si>
-  <si>
-    <t>سلك مواعين (19)</t>
-  </si>
-  <si>
-    <t>ملمع زجاج (20)</t>
-  </si>
-  <si>
-    <t>مسحوق غسيل (21)</t>
   </si>
   <si>
     <t>صابون سائل (22)</t>
@@ -1351,82 +1351,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>13</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>25</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2429,27 +2429,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B2" s="2">
         <v>243.0</v>
@@ -2458,83 +2458,83 @@
         <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B3" s="2">
         <v>228.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="B4" s="2">
         <v>30.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="B5" s="2">
         <v>199.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="B6" s="2">
         <v>121.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="B7" s="2">
         <v>232.0</v>
@@ -2543,15 +2543,15 @@
         <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="B8" s="2">
         <v>49.0</v>
@@ -2560,18 +2560,18 @@
         <v>39.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="B9" s="2">
         <v>137.0</v>
@@ -2580,35 +2580,35 @@
         <v>135.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="B10" s="2">
         <v>214.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="B11" s="2">
         <v>67.0</v>
@@ -2617,15 +2617,15 @@
         <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="B12" s="2">
         <v>134.0</v>
@@ -2637,15 +2637,15 @@
         <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="B13" s="2">
         <v>126.0</v>
@@ -2654,18 +2654,18 @@
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="B14" s="2">
         <v>21.0</v>
@@ -2674,15 +2674,15 @@
         <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>214</v>
+        <v>192</v>
       </c>
       <c r="B15" s="2">
         <v>148.0</v>
@@ -2691,18 +2691,18 @@
         <v>141.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>217</v>
+        <v>193</v>
       </c>
       <c r="B16" s="2">
         <v>222.0</v>
@@ -2711,15 +2711,15 @@
         <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>219</v>
+        <v>194</v>
       </c>
       <c r="B17" s="2">
         <v>196.0</v>
@@ -2731,15 +2731,15 @@
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>222</v>
+        <v>195</v>
       </c>
       <c r="B18" s="2">
         <v>71.0</v>
@@ -2748,18 +2748,18 @@
         <v>66.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>226</v>
+        <v>196</v>
       </c>
       <c r="B19" s="2">
         <v>53.0</v>
@@ -2768,49 +2768,49 @@
         <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="B20" s="2">
         <v>202.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>232</v>
+        <v>198</v>
       </c>
       <c r="B21" s="2">
         <v>65.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>237</v>
+        <v>199</v>
       </c>
       <c r="B22" s="2">
         <v>35.0</v>
@@ -2819,15 +2819,15 @@
         <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>240</v>
+        <v>200</v>
       </c>
       <c r="B23" s="2">
         <v>29.0</v>
@@ -2836,35 +2836,35 @@
         <v>25.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>246</v>
+        <v>201</v>
       </c>
       <c r="B24" s="2">
         <v>165.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>250</v>
+        <v>202</v>
       </c>
       <c r="B25" s="2">
         <v>118.0</v>
@@ -2876,15 +2876,15 @@
         <v>42</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>253</v>
+        <v>203</v>
       </c>
       <c r="B26" s="2">
         <v>210.0</v>
@@ -2893,35 +2893,35 @@
         <v>202.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>257</v>
+        <v>204</v>
       </c>
       <c r="B27" s="2">
         <v>24.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>259</v>
+        <v>205</v>
       </c>
       <c r="B28" s="2">
         <v>191.0</v>
@@ -2933,15 +2933,15 @@
         <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>261</v>
+        <v>206</v>
       </c>
       <c r="B29" s="2">
         <v>172.0</v>
@@ -2950,32 +2950,32 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="B30" s="2">
         <v>104.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>266</v>
+        <v>208</v>
       </c>
       <c r="B31" s="2">
         <v>59.0</v>
@@ -2984,10 +2984,10 @@
         <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -3979,27 +3979,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>179</v>
+        <v>209</v>
       </c>
       <c r="B2" s="2">
         <v>79.0</v>
@@ -4008,15 +4008,15 @@
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>181</v>
+        <v>210</v>
       </c>
       <c r="B3" s="2">
         <v>191.0</v>
@@ -4025,32 +4025,32 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>183</v>
+        <v>211</v>
       </c>
       <c r="B4" s="2">
         <v>91.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>185</v>
+        <v>213</v>
       </c>
       <c r="B5" s="2">
         <v>66.0</v>
@@ -4059,15 +4059,15 @@
         <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>187</v>
+        <v>215</v>
       </c>
       <c r="B6" s="2">
         <v>51.0</v>
@@ -4076,15 +4076,15 @@
         <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>189</v>
+        <v>217</v>
       </c>
       <c r="B7" s="2">
         <v>198.0</v>
@@ -4093,18 +4093,18 @@
         <v>192.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>191</v>
+        <v>219</v>
       </c>
       <c r="B8" s="2">
         <v>32.0</v>
@@ -4113,18 +4113,18 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>192</v>
+        <v>221</v>
       </c>
       <c r="B9" s="2">
         <v>189.0</v>
@@ -4136,15 +4136,15 @@
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>194</v>
+        <v>223</v>
       </c>
       <c r="B10" s="2">
         <v>101.0</v>
@@ -4153,15 +4153,15 @@
         <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>195</v>
+        <v>225</v>
       </c>
       <c r="B11" s="2">
         <v>124.0</v>
@@ -4173,15 +4173,15 @@
         <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>197</v>
+        <v>227</v>
       </c>
       <c r="B12" s="2">
         <v>30.0</v>
@@ -4190,15 +4190,15 @@
         <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="B13" s="2">
         <v>69.0</v>
@@ -4207,18 +4207,18 @@
         <v>60.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>201</v>
+        <v>231</v>
       </c>
       <c r="B14" s="2">
         <v>140.0</v>
@@ -4227,18 +4227,18 @@
         <v>131.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>202</v>
+        <v>233</v>
       </c>
       <c r="B15" s="2">
         <v>216.0</v>
@@ -4247,103 +4247,103 @@
         <v>209.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>205</v>
+        <v>235</v>
       </c>
       <c r="B16" s="2">
         <v>214.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>207</v>
+        <v>237</v>
       </c>
       <c r="B17" s="2">
         <v>108.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>209</v>
+        <v>239</v>
       </c>
       <c r="B18" s="2">
         <v>158.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>211</v>
+        <v>241</v>
       </c>
       <c r="B19" s="2">
         <v>246.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>213</v>
+        <v>243</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>215</v>
+        <v>246</v>
       </c>
       <c r="B21" s="2">
         <v>99.0</v>
@@ -4352,32 +4352,32 @@
         <v>42</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>218</v>
+        <v>249</v>
       </c>
       <c r="B22" s="2">
         <v>54.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>221</v>
+        <v>252</v>
       </c>
       <c r="B23" s="2">
         <v>29.0</v>
@@ -4389,15 +4389,15 @@
         <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>223</v>
+        <v>255</v>
       </c>
       <c r="B24" s="2">
         <v>135.0</v>
@@ -4406,15 +4406,15 @@
         <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>225</v>
+        <v>257</v>
       </c>
       <c r="B25" s="2">
         <v>76.0</v>
@@ -4426,32 +4426,32 @@
         <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="B26" s="2">
         <v>181.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>231</v>
+        <v>263</v>
       </c>
       <c r="B27" s="2">
         <v>58.0</v>
@@ -4463,15 +4463,15 @@
         <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>235</v>
+        <v>266</v>
       </c>
       <c r="B28" s="2">
         <v>16.0</v>
@@ -4483,32 +4483,32 @@
         <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>239</v>
+        <v>269</v>
       </c>
       <c r="B29" s="2">
         <v>87.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>243</v>
+        <v>271</v>
       </c>
       <c r="B30" s="2">
         <v>77.0</v>
@@ -4517,18 +4517,18 @@
         <v>74.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>248</v>
+        <v>274</v>
       </c>
       <c r="B31" s="2">
         <v>98.0</v>
@@ -4540,10 +4540,10 @@
         <v>42</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -5535,27 +5535,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="B2" s="2">
         <v>214.0</v>
@@ -5567,15 +5567,15 @@
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="B3" s="2">
         <v>65.0</v>
@@ -5587,44 +5587,44 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B4" s="2">
         <v>101.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="B5" s="2">
         <v>204.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
@@ -5635,18 +5635,18 @@
         <v>56.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B7" s="2">
         <v>46.0</v>
@@ -5658,15 +5658,15 @@
         <v>42</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B8" s="2">
         <v>211.0</v>
@@ -5675,52 +5675,52 @@
         <v>204.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="B9" s="2">
         <v>174.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="B10" s="2">
         <v>136.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="B11" s="2">
         <v>230.0</v>
@@ -5729,32 +5729,32 @@
         <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>245</v>
+        <v>232</v>
       </c>
       <c r="B12" s="2">
         <v>98.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B13" s="2">
         <v>101.0</v>
@@ -5766,15 +5766,15 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B14" s="2">
         <v>34.0</v>
@@ -5783,35 +5783,35 @@
         <v>25.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>255</v>
+        <v>238</v>
       </c>
       <c r="B15" s="2">
         <v>58.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>270</v>
+        <v>240</v>
       </c>
       <c r="B16" s="2">
         <v>100.0</v>
@@ -5820,15 +5820,15 @@
         <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>272</v>
+        <v>242</v>
       </c>
       <c r="B17" s="2">
         <v>144.0</v>
@@ -5837,35 +5837,35 @@
         <v>138.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="B18" s="2">
         <v>104.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>277</v>
+        <v>247</v>
       </c>
       <c r="B19" s="2">
         <v>152.0</v>
@@ -5877,32 +5877,32 @@
         <v>42</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="B20" s="2">
         <v>205.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>281</v>
+        <v>253</v>
       </c>
       <c r="B21" s="2">
         <v>60.0</v>
@@ -5911,18 +5911,18 @@
         <v>51.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>283</v>
+        <v>256</v>
       </c>
       <c r="B22" s="2">
         <v>172.0</v>
@@ -5931,15 +5931,15 @@
         <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>285</v>
+        <v>259</v>
       </c>
       <c r="B23" s="2">
         <v>93.0</v>
@@ -5948,18 +5948,18 @@
         <v>88.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>288</v>
+        <v>262</v>
       </c>
       <c r="B24" s="2">
         <v>167.0</v>
@@ -5968,32 +5968,32 @@
         <v>42</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>290</v>
+        <v>265</v>
       </c>
       <c r="B25" s="2">
         <v>126.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="B26" s="2">
         <v>250.0</v>
@@ -6005,15 +6005,15 @@
         <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>294</v>
+        <v>273</v>
       </c>
       <c r="B27" s="2">
         <v>118.0</v>
@@ -6025,15 +6025,15 @@
         <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>295</v>
+        <v>276</v>
       </c>
       <c r="B28" s="2">
         <v>62.0</v>
@@ -6042,15 +6042,15 @@
         <v>42</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>296</v>
+        <v>278</v>
       </c>
       <c r="B29" s="2">
         <v>88.0</v>
@@ -6059,32 +6059,32 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="B30" s="2">
         <v>18.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="B31" s="2">
         <v>197.0</v>
@@ -6093,10 +6093,10 @@
         <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -7088,44 +7088,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>230</v>
+        <v>244</v>
       </c>
       <c r="B2" s="2">
         <v>119.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>234</v>
+        <v>248</v>
       </c>
       <c r="B3" s="2">
         <v>144.0</v>
@@ -7134,15 +7134,15 @@
         <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B4" s="2">
         <v>244.0</v>
@@ -7154,49 +7154,49 @@
         <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>242</v>
+        <v>254</v>
       </c>
       <c r="B5" s="2">
         <v>28.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>244</v>
+        <v>258</v>
       </c>
       <c r="B6" s="2">
         <v>206.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="B7" s="2">
         <v>223.0</v>
@@ -7205,18 +7205,18 @@
         <v>220.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B8" s="2">
         <v>234.0</v>
@@ -7225,35 +7225,35 @@
         <v>230.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B9" s="2">
         <v>87.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>256</v>
+        <v>270</v>
       </c>
       <c r="B10" s="2">
         <v>147.0</v>
@@ -7262,32 +7262,32 @@
         <v>42</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>258</v>
+        <v>272</v>
       </c>
       <c r="B11" s="2">
         <v>141.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B12" s="2">
         <v>152.0</v>
@@ -7296,15 +7296,15 @@
         <v>42</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="B13" s="2">
         <v>124.0</v>
@@ -7313,32 +7313,32 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="B14" s="2">
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="B15" s="2">
         <v>213.0</v>
@@ -7347,15 +7347,15 @@
         <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="B16" s="2">
         <v>167.0</v>
@@ -7367,15 +7367,15 @@
         <v>42</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="B17" s="2">
         <v>138.0</v>
@@ -7384,15 +7384,15 @@
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="B18" s="2">
         <v>243.0</v>
@@ -7404,32 +7404,32 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="B19" s="2">
         <v>166.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="B20" s="2">
         <v>31.0</v>
@@ -7438,49 +7438,49 @@
         <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="B21" s="2">
         <v>243.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>276</v>
+        <v>297</v>
       </c>
       <c r="B22" s="2">
         <v>224.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>278</v>
+        <v>300</v>
       </c>
       <c r="B23" s="2">
         <v>160.0</v>
@@ -7489,15 +7489,15 @@
         <v>42</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>280</v>
+        <v>302</v>
       </c>
       <c r="B24" s="2">
         <v>233.0</v>
@@ -7506,32 +7506,32 @@
         <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>282</v>
+        <v>304</v>
       </c>
       <c r="B25" s="2">
         <v>148.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>284</v>
+        <v>306</v>
       </c>
       <c r="B26" s="2">
         <v>195.0</v>
@@ -7540,15 +7540,15 @@
         <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>286</v>
+        <v>309</v>
       </c>
       <c r="B27" s="2">
         <v>194.0</v>
@@ -7557,35 +7557,35 @@
         <v>191.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="B28" s="2">
         <v>48.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>289</v>
+        <v>314</v>
       </c>
       <c r="B29" s="2">
         <v>237.0</v>
@@ -7594,18 +7594,18 @@
         <v>228.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>291</v>
+        <v>317</v>
       </c>
       <c r="B30" s="2">
         <v>234.0</v>
@@ -7617,15 +7617,15 @@
         <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="B31" s="2">
         <v>210.0</v>
@@ -7634,13 +7634,13 @@
         <v>201.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -8632,27 +8632,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="B2" s="2">
         <v>103.0</v>
@@ -8661,18 +8661,18 @@
         <v>101.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="B3" s="2">
         <v>46.0</v>
@@ -8681,15 +8681,15 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>301</v>
+        <v>290</v>
       </c>
       <c r="B4" s="2">
         <v>54.0</v>
@@ -8701,15 +8701,15 @@
         <v>42</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
@@ -8718,32 +8718,32 @@
         <v>42</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>303</v>
+        <v>292</v>
       </c>
       <c r="B6" s="2">
         <v>68.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>304</v>
+        <v>293</v>
       </c>
       <c r="B7" s="2">
         <v>116.0</v>
@@ -8752,15 +8752,15 @@
         <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="B8" s="2">
         <v>227.0</v>
@@ -8769,15 +8769,15 @@
         <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="B9" s="2">
         <v>199.0</v>
@@ -8786,18 +8786,18 @@
         <v>189.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="B10" s="2">
         <v>179.0</v>
@@ -8806,15 +8806,15 @@
         <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="B11" s="2">
         <v>164.0</v>
@@ -8823,18 +8823,18 @@
         <v>157.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="B12" s="2">
         <v>60.0</v>
@@ -8843,18 +8843,18 @@
         <v>55.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B13" s="2">
         <v>54.0</v>
@@ -8863,15 +8863,15 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B14" s="2">
         <v>28.0</v>
@@ -8883,15 +8883,15 @@
         <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="B15" s="2">
         <v>208.0</v>
@@ -8900,32 +8900,32 @@
         <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="B16" s="2">
         <v>243.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B17" s="2">
         <v>38.0</v>
@@ -8934,15 +8934,15 @@
         <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B18" s="2">
         <v>181.0</v>
@@ -8951,15 +8951,15 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="B19" s="2">
         <v>71.0</v>
@@ -8968,35 +8968,35 @@
         <v>61.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B20" s="2">
         <v>240.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B21" s="2">
         <v>195.0</v>
@@ -9005,15 +9005,15 @@
         <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B22" s="2">
         <v>58.0</v>
@@ -9025,10 +9025,10 @@
         <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -9042,13 +9042,13 @@
         <v>130.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -9062,10 +9062,10 @@
         <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -9079,10 +9079,10 @@
         <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -9093,13 +9093,13 @@
         <v>84.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -9113,10 +9113,10 @@
         <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -9130,10 +9130,10 @@
         <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -9147,10 +9147,10 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -9161,13 +9161,13 @@
         <v>224.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -9178,13 +9178,13 @@
         <v>91.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -10178,23 +10178,23 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>22</v>
@@ -10202,15 +10202,15 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
@@ -11222,27 +11222,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2">
         <v>84.0</v>
@@ -11251,18 +11251,18 @@
         <v>77.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B3" s="2">
         <v>49.0</v>
@@ -11271,18 +11271,18 @@
         <v>40.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B4" s="2">
         <v>136.0</v>
@@ -11291,18 +11291,18 @@
         <v>131.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="2">
         <v>171.0</v>
@@ -11311,18 +11311,18 @@
         <v>161.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B6" s="2">
         <v>31.0</v>
@@ -11334,10 +11334,10 @@
         <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
@@ -11351,13 +11351,13 @@
         <v>60.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -11371,13 +11371,13 @@
         <v>123.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -11394,10 +11394,10 @@
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -11411,13 +11411,13 @@
         <v>98.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
@@ -11434,10 +11434,10 @@
         <v>42</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
@@ -11451,13 +11451,13 @@
         <v>214.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
@@ -11471,13 +11471,13 @@
         <v>145.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -11494,10 +11494,10 @@
         <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -11511,13 +11511,13 @@
         <v>164.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -11531,13 +11531,13 @@
         <v>86.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
@@ -11554,10 +11554,10 @@
         <v>42</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
@@ -11574,10 +11574,10 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
@@ -11591,13 +11591,13 @@
         <v>37.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -11611,13 +11611,13 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -11631,13 +11631,13 @@
         <v>175.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -12641,10 +12641,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
     <row r="2">
@@ -12652,7 +12652,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -12660,7 +12660,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4">
@@ -12668,7 +12668,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -12676,7 +12676,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6">
@@ -12684,7 +12684,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -14773,22 +14773,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -14799,19 +14799,19 @@
         <v>53.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E2" s="2" t="str">
         <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; (ROW(A1)  &amp; ").png")</f>
         <v>images/proudect(1).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B3" s="2">
         <v>92.0</v>
@@ -14820,37 +14820,37 @@
         <v>87.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(2).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" s="2">
         <v>198.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(3).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="B5" s="2">
         <v>84.0</v>
@@ -14859,19 +14859,19 @@
         <v>77.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(4).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B6" s="2">
         <v>249.0</v>
@@ -14887,30 +14887,30 @@
         <v>images/proudect(5).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B7" s="2">
         <v>181.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(6).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="B8" s="2">
         <v>49.0</v>
@@ -14919,19 +14919,19 @@
         <v>40.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(7).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B9" s="2">
         <v>240.0</v>
@@ -14944,30 +14944,30 @@
         <v>images/proudect(8).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="B10" s="2">
         <v>203.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(9).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="B11" s="2">
         <v>109.0</v>
@@ -14980,12 +14980,12 @@
         <v>images/proudect(10).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="B12" s="2">
         <v>31.0</v>
@@ -14994,19 +14994,19 @@
         <v>24.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(11).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="B13" s="2">
         <v>250.0</v>
@@ -15019,12 +15019,12 @@
         <v>images/proudect(12).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="B14" s="2">
         <v>242.0</v>
@@ -15037,12 +15037,12 @@
         <v>images/proudect(13).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B15" s="2">
         <v>136.0</v>
@@ -15051,19 +15051,19 @@
         <v>131.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(14).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B16" s="2">
         <v>85.0</v>
@@ -15076,12 +15076,12 @@
         <v>images/proudect(15).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B17" s="2">
         <v>184.0</v>
@@ -15094,48 +15094,48 @@
         <v>images/proudect(16).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B18" s="2">
         <v>23.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(17).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B19" s="2">
         <v>52.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(18).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
@@ -15148,12 +15148,12 @@
         <v>images/proudect(19).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B21" s="2">
         <v>32.0</v>
@@ -15166,30 +15166,30 @@
         <v>images/proudect(20).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="B22" s="2">
         <v>144.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(21).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B23" s="2">
         <v>171.0</v>
@@ -15198,19 +15198,19 @@
         <v>161.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(22).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="2">
         <v>31.0</v>
@@ -15226,30 +15226,30 @@
         <v>images/proudect(23).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="B25" s="2">
         <v>41.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(24).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="B26" s="2">
         <v>170.0</v>
@@ -15262,12 +15262,12 @@
         <v>images/proudect(25).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>118</v>
+        <v>130</v>
       </c>
       <c r="B27" s="2">
         <v>199.0</v>
@@ -15280,7 +15280,7 @@
         <v>images/proudect(26).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -15294,19 +15294,19 @@
         <v>60.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(27).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="B29" s="2">
         <v>208.0</v>
@@ -15319,7 +15319,7 @@
         <v>images/proudect(28).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -15333,19 +15333,19 @@
         <v>123.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(29).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="B31" s="2">
         <v>96.0</v>
@@ -15358,7 +15358,7 @@
         <v>images/proudect(30).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -16356,22 +16356,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -16388,16 +16388,16 @@
         <v>46</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; (ROW(A1) + 30) &amp; ").png"</f>
+        <f>"images/proudect(" &amp; ROW(A31) &amp; ").png"</f>
         <v>images/proudect(31).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B3" s="2">
         <v>151.0</v>
@@ -16406,83 +16406,83 @@
         <v>42</v>
       </c>
       <c r="E3" s="2" t="str">
+        <f t="shared" ref="E3:E6" si="1">"images/proudect(" &amp; (ROW(A31) &amp; ").png")</f>
+        <v>images/proudect(31).png</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(32).png</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B4" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="2" t="str">
+      <c r="F4" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" s="2">
+        <v>175.0</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(33).png</v>
       </c>
-      <c r="F4" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="2">
-        <v>175.0</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" s="2" t="str">
+      <c r="F5" s="3" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B6" s="2">
+        <v>32.0</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(34).png</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B6" s="2">
-        <v>32.0</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="2" t="str">
-        <f t="shared" si="1"/>
-        <v>images/proudect(35).png</v>
-      </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>96</v>
+        <v>89</v>
       </c>
       <c r="B7" s="2">
         <v>215.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E7" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E7:E31" si="2">"images/proudect(" &amp; (ROW(A6) + 30) &amp; ").png"</f>
         <v>images/proudect(36).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
@@ -16496,19 +16496,19 @@
         <v>98.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(37).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B9" s="2">
         <v>72.0</v>
@@ -16517,11 +16517,11 @@
         <v>42</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(38).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
@@ -16538,34 +16538,34 @@
         <v>42</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(39).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B11" s="2">
         <v>187.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(40).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B12" s="2">
         <v>125.0</v>
@@ -16574,16 +16574,16 @@
         <v>42</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(41).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B13" s="2">
         <v>80.0</v>
@@ -16592,11 +16592,11 @@
         <v>42</v>
       </c>
       <c r="E13" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(42).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
@@ -16610,32 +16610,32 @@
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(43).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B15" s="2">
         <v>231.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(44).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -16649,52 +16649,52 @@
         <v>46</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(45).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B17" s="2">
         <v>162.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(46).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="B18" s="2">
         <v>42.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(47).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="B19" s="2">
         <v>33.0</v>
@@ -16703,52 +16703,52 @@
         <v>42</v>
       </c>
       <c r="E19" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(48).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="B20" s="2">
         <v>87.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(49).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B21" s="2">
         <v>110.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E21" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(50).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B22" s="2">
         <v>69.0</v>
@@ -16760,16 +16760,16 @@
         <v>46</v>
       </c>
       <c r="E22" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(51).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>116</v>
+        <v>128</v>
       </c>
       <c r="B23" s="2">
         <v>199.0</v>
@@ -16778,11 +16778,11 @@
         <v>42</v>
       </c>
       <c r="E23" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(52).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -16796,14 +16796,14 @@
         <v>145.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(53).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -16820,16 +16820,16 @@
         <v>46</v>
       </c>
       <c r="E25" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(54).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2">
         <v>84.0</v>
@@ -16841,52 +16841,52 @@
         <v>46</v>
       </c>
       <c r="E26" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(55).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="B27" s="2">
         <v>119.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(56).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="B28" s="2">
         <v>110.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E28" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(57).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B29" s="2">
         <v>212.0</v>
@@ -16895,11 +16895,11 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(58).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -16913,32 +16913,32 @@
         <v>164.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(59).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B31" s="2">
         <v>147.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E31" s="2" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>images/proudect(60).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -17936,22 +17936,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -17965,14 +17965,14 @@
         <v>179.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; (ROW(A1) + 60) &amp; ").png"</f>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; ROW(A61) &amp; ").png"</f>
         <v>images/proudect(61).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -17986,37 +17986,37 @@
         <v>86.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(62).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="B4" s="2">
         <v>105.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(63).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
       <c r="B5" s="2">
         <v>25.0</v>
@@ -18029,30 +18029,30 @@
         <v>images/proudect(64).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B6" s="2">
         <v>49.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(65).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>146</v>
       </c>
       <c r="B7" s="2">
         <v>47.0</v>
@@ -18065,25 +18065,25 @@
         <v>images/proudect(66).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B8" s="2">
         <v>164.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(67).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
@@ -18104,97 +18104,97 @@
         <v>images/proudect(68).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="B10" s="2">
         <v>124.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(69).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="B11" s="2">
         <v>66.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(70).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>133</v>
+        <v>157</v>
       </c>
       <c r="B12" s="2">
         <v>38.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(71).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>134</v>
+        <v>160</v>
       </c>
       <c r="B13" s="2">
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(72).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>135</v>
+        <v>162</v>
       </c>
       <c r="B14" s="2">
         <v>73.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(73).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
@@ -18215,7 +18215,7 @@
         <v>images/proudect(74).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
@@ -18229,55 +18229,55 @@
         <v>37.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(75).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>166</v>
       </c>
       <c r="B17" s="2">
         <v>98.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(76).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>137</v>
+        <v>167</v>
       </c>
       <c r="B18" s="2">
         <v>40.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(77).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="B19" s="2">
         <v>53.0</v>
@@ -18290,7 +18290,7 @@
         <v>images/proudect(78).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
@@ -18304,19 +18304,19 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(79).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>169</v>
       </c>
       <c r="B21" s="2">
         <v>157.0</v>
@@ -18329,7 +18329,7 @@
         <v>images/proudect(80).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -18343,19 +18343,19 @@
         <v>175.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(81).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>143</v>
+        <v>170</v>
       </c>
       <c r="B23" s="2">
         <v>38.0</v>
@@ -18371,12 +18371,12 @@
         <v>images/proudect(82).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>145</v>
+        <v>171</v>
       </c>
       <c r="B24" s="2">
         <v>206.0</v>
@@ -18389,48 +18389,48 @@
         <v>images/proudect(83).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>147</v>
+        <v>172</v>
       </c>
       <c r="B25" s="2">
         <v>39.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(84).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>149</v>
+        <v>173</v>
       </c>
       <c r="B26" s="2">
         <v>130.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(85).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>151</v>
+        <v>174</v>
       </c>
       <c r="B27" s="2">
         <v>145.0</v>
@@ -18443,12 +18443,12 @@
         <v>images/proudect(86).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>153</v>
+        <v>175</v>
       </c>
       <c r="B28" s="2">
         <v>75.0</v>
@@ -18464,48 +18464,48 @@
         <v>images/proudect(87).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>155</v>
+        <v>176</v>
       </c>
       <c r="B29" s="2">
         <v>221.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(88).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>157</v>
+        <v>177</v>
       </c>
       <c r="B30" s="2">
         <v>122.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(89).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="B31" s="2">
         <v>34.0</v>
@@ -18514,14 +18514,14 @@
         <v>25.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
         <v>images/proudect(90).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -19513,44 +19513,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>14</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>139</v>
+        <v>105</v>
       </c>
       <c r="B2" s="2">
         <v>161.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="B3" s="2">
         <v>62.0</v>
@@ -19562,15 +19562,15 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>142</v>
+        <v>111</v>
       </c>
       <c r="B4" s="2">
         <v>164.0</v>
@@ -19582,32 +19582,32 @@
         <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="B5" s="2">
         <v>91.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="B6" s="2">
         <v>120.0</v>
@@ -19616,49 +19616,49 @@
         <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="B7" s="2">
         <v>240.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>150</v>
+        <v>119</v>
       </c>
       <c r="B8" s="2">
         <v>68.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>152</v>
+        <v>121</v>
       </c>
       <c r="B9" s="2">
         <v>40.0</v>
@@ -19667,15 +19667,15 @@
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>154</v>
+        <v>123</v>
       </c>
       <c r="B10" s="2">
         <v>137.0</v>
@@ -19684,66 +19684,66 @@
         <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2">
         <v>51.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>158</v>
+        <v>127</v>
       </c>
       <c r="B12" s="2">
         <v>211.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="B13" s="2">
         <v>236.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="B14" s="2">
         <v>69.0</v>
@@ -19752,18 +19752,18 @@
         <v>64.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="B15" s="2">
         <v>78.0</v>
@@ -19775,32 +19775,32 @@
         <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>163</v>
+        <v>134</v>
       </c>
       <c r="B16" s="2">
         <v>231.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>164</v>
+        <v>138</v>
       </c>
       <c r="B17" s="2">
         <v>155.0</v>
@@ -19809,15 +19809,15 @@
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>165</v>
+        <v>140</v>
       </c>
       <c r="B18" s="2">
         <v>156.0</v>
@@ -19826,66 +19826,66 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>166</v>
+        <v>143</v>
       </c>
       <c r="B19" s="2">
         <v>168.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>167</v>
+        <v>145</v>
       </c>
       <c r="B20" s="2">
         <v>70.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>168</v>
+        <v>148</v>
       </c>
       <c r="B21" s="2">
         <v>136.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>169</v>
+        <v>150</v>
       </c>
       <c r="B22" s="2">
         <v>125.0</v>
@@ -19897,15 +19897,15 @@
         <v>42</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>170</v>
+        <v>152</v>
       </c>
       <c r="B23" s="2">
         <v>135.0</v>
@@ -19914,15 +19914,15 @@
         <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>171</v>
+        <v>154</v>
       </c>
       <c r="B24" s="2">
         <v>250.0</v>
@@ -19931,35 +19931,35 @@
         <v>244.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>172</v>
+        <v>155</v>
       </c>
       <c r="B25" s="2">
         <v>83.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="B26" s="2">
         <v>117.0</v>
@@ -19968,32 +19968,32 @@
         <v>42</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
       <c r="B27" s="2">
         <v>240.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>175</v>
+        <v>161</v>
       </c>
       <c r="B28" s="2">
         <v>174.0</v>
@@ -20002,35 +20002,35 @@
         <v>165.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>176</v>
+        <v>163</v>
       </c>
       <c r="B29" s="2">
         <v>152.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>177</v>
+        <v>164</v>
       </c>
       <c r="B30" s="2">
         <v>162.0</v>
@@ -20042,27 +20042,27 @@
         <v>42</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>165</v>
       </c>
       <c r="B31" s="2">
         <v>189.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -26,138 +26,138 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1187" uniqueCount="329">
   <si>
+    <t>الاسم</t>
+  </si>
+  <si>
+    <t>مكان_البانر</t>
+  </si>
+  <si>
     <t>صورة</t>
   </si>
   <si>
+    <t>السعر الأساسي</t>
+  </si>
+  <si>
+    <t>السعر بعد الخصم</t>
+  </si>
+  <si>
+    <t>القسم_المستهدف</t>
+  </si>
+  <si>
+    <t>الوحدة</t>
+  </si>
+  <si>
+    <t>متوفر</t>
+  </si>
+  <si>
+    <t>images/slider_1.jpg</t>
+  </si>
+  <si>
+    <t>خيار</t>
+  </si>
+  <si>
+    <t>رئيسي_علوي</t>
+  </si>
+  <si>
+    <t>الفواكه والخضروات</t>
+  </si>
+  <si>
     <t>رقم_الصفحة</t>
   </si>
   <si>
-    <t>القسم_المستهدف</t>
-  </si>
-  <si>
-    <t>images/slider_1.jpg</t>
-  </si>
-  <si>
-    <t>الفواكه والخضروات</t>
+    <t>images/top_banner.jpg</t>
+  </si>
+  <si>
+    <t>لتر</t>
+  </si>
+  <si>
+    <t>images/placeholder.png</t>
+  </si>
+  <si>
+    <t>مقسم_يمين</t>
+  </si>
+  <si>
+    <t>نعم</t>
+  </si>
+  <si>
+    <t>images/slider_2.jpg</t>
+  </si>
+  <si>
+    <t>images/split1.jpg</t>
+  </si>
+  <si>
+    <t>التسالي والمكسرات</t>
+  </si>
+  <si>
+    <t>موز</t>
+  </si>
+  <si>
+    <t>مقسم_يسار</t>
+  </si>
+  <si>
+    <t>images/split2.jpg</t>
+  </si>
+  <si>
+    <t>كيلو</t>
+  </si>
+  <si>
+    <t>المشروبات</t>
+  </si>
+  <si>
+    <t>رئيسي_ثابت</t>
+  </si>
+  <si>
+    <t>البقالة</t>
   </si>
   <si>
     <t>images/offer_page_1.jpg</t>
   </si>
   <si>
-    <t>مكان_البانر</t>
-  </si>
-  <si>
-    <t>الاسم</t>
+    <t>images/static_banner.jpg</t>
+  </si>
+  <si>
+    <t>خيار (14)</t>
+  </si>
+  <si>
+    <t>الألبان</t>
+  </si>
+  <si>
+    <t>المخبوزات</t>
   </si>
   <si>
     <t>images/offer_page_2.jpg</t>
   </si>
   <si>
+    <t>بطاطس (22)</t>
+  </si>
+  <si>
+    <t>التوابل والبهارات</t>
+  </si>
+  <si>
     <t>images/offer_page_3.jpg</t>
   </si>
   <si>
-    <t>images/slider_2.jpg</t>
+    <t>بصل (23)</t>
+  </si>
+  <si>
+    <t>الحلويات والكاندي</t>
   </si>
   <si>
     <t>images/offer_page_4.jpg</t>
   </si>
   <si>
-    <t>التسالي والمكسرات</t>
+    <t>قطعة</t>
+  </si>
+  <si>
+    <t>موز (27)</t>
+  </si>
+  <si>
+    <t>منظفات</t>
   </si>
   <si>
     <t>images/offer_page_5.jpg</t>
   </si>
   <si>
-    <t>السعر الأساسي</t>
-  </si>
-  <si>
-    <t>رئيسي_علوي</t>
-  </si>
-  <si>
-    <t>المشروبات</t>
-  </si>
-  <si>
-    <t>السعر بعد الخصم</t>
-  </si>
-  <si>
-    <t>images/top_banner.jpg</t>
-  </si>
-  <si>
-    <t>البقالة</t>
-  </si>
-  <si>
-    <t>الوحدة</t>
-  </si>
-  <si>
-    <t>مقسم_يمين</t>
-  </si>
-  <si>
-    <t>images/split1.jpg</t>
-  </si>
-  <si>
-    <t>الألبان</t>
-  </si>
-  <si>
-    <t>مقسم_يسار</t>
-  </si>
-  <si>
-    <t>متوفر</t>
-  </si>
-  <si>
-    <t>images/split2.jpg</t>
-  </si>
-  <si>
-    <t>المخبوزات</t>
-  </si>
-  <si>
-    <t>رئيسي_ثابت</t>
-  </si>
-  <si>
-    <t>التوابل والبهارات</t>
-  </si>
-  <si>
-    <t>خيار</t>
-  </si>
-  <si>
-    <t>images/static_banner.jpg</t>
-  </si>
-  <si>
-    <t>الحلويات والكاندي</t>
-  </si>
-  <si>
-    <t>منظفات</t>
-  </si>
-  <si>
-    <t>لتر</t>
-  </si>
-  <si>
-    <t>images/placeholder.png</t>
-  </si>
-  <si>
-    <t>نعم</t>
-  </si>
-  <si>
-    <t>موز</t>
-  </si>
-  <si>
-    <t>كيلو</t>
-  </si>
-  <si>
-    <t>خيار (14)</t>
-  </si>
-  <si>
-    <t>بطاطس (22)</t>
-  </si>
-  <si>
-    <t>بصل (23)</t>
-  </si>
-  <si>
-    <t>قطعة</t>
-  </si>
-  <si>
-    <t>موز (27)</t>
-  </si>
-  <si>
     <t>عنب (29)</t>
   </si>
   <si>
@@ -272,36 +272,42 @@
     <t>بطاطس</t>
   </si>
   <si>
+    <t>سوداني</t>
+  </si>
+  <si>
     <t>بصل</t>
   </si>
   <si>
+    <t>لوز</t>
+  </si>
+  <si>
     <t>جزر</t>
   </si>
   <si>
-    <t>سوداني</t>
+    <t>عين جمل</t>
   </si>
   <si>
     <t>تفاح</t>
   </si>
   <si>
-    <t>لوز</t>
+    <t>شاي</t>
+  </si>
+  <si>
+    <t>كاجو</t>
   </si>
   <si>
     <t>برتقال</t>
   </si>
   <si>
-    <t>عين جمل</t>
-  </si>
-  <si>
-    <t>كاجو</t>
-  </si>
-  <si>
     <t>عنب</t>
   </si>
   <si>
     <t>مانجو</t>
   </si>
   <si>
+    <t>فشار</t>
+  </si>
+  <si>
     <t>طماطم (11)</t>
   </si>
   <si>
@@ -311,258 +317,252 @@
     <t>بصل (13)</t>
   </si>
   <si>
-    <t>فشار</t>
+    <t>فستق</t>
   </si>
   <si>
     <t>جزر (15)</t>
   </si>
   <si>
-    <t>فستق</t>
+    <t>لب سوبر (11)</t>
   </si>
   <si>
     <t>تفاح (16)</t>
   </si>
   <si>
-    <t>لب سوبر (11)</t>
+    <t>لب سوري (12)</t>
   </si>
   <si>
     <t>موز (17)</t>
   </si>
   <si>
-    <t>لب سوري (12)</t>
-  </si>
-  <si>
-    <t>شاي</t>
+    <t>نسكافيه</t>
   </si>
   <si>
     <t>برتقال (18)</t>
   </si>
   <si>
+    <t>عنب (19)</t>
+  </si>
+  <si>
+    <t>مانجو (20)</t>
+  </si>
+  <si>
+    <t>عصير برتقال</t>
+  </si>
+  <si>
     <t>لوز (14)</t>
   </si>
   <si>
+    <t>طماطم (21)</t>
+  </si>
+  <si>
+    <t>عصير تفاح</t>
+  </si>
+  <si>
+    <t>عين جمل (15)</t>
+  </si>
+  <si>
+    <t>كولا</t>
+  </si>
+  <si>
+    <t>كاجو (16)</t>
+  </si>
+  <si>
+    <t>خيار (24)</t>
+  </si>
+  <si>
+    <t>جزر (25)</t>
+  </si>
+  <si>
+    <t>مياه معدنية</t>
+  </si>
+  <si>
+    <t>شيبسي (17)</t>
+  </si>
+  <si>
+    <t>تفاح (26)</t>
+  </si>
+  <si>
+    <t>فشار (18)</t>
+  </si>
+  <si>
+    <t>برتقال (28)</t>
+  </si>
+  <si>
+    <t>مقرمشات (19)</t>
+  </si>
+  <si>
+    <t>كاكاو</t>
+  </si>
+  <si>
+    <t>فستق (20)</t>
+  </si>
+  <si>
+    <t>مانجو (30)</t>
+  </si>
+  <si>
+    <t>نعناع</t>
+  </si>
+  <si>
+    <t>لب سوبر (21)</t>
+  </si>
+  <si>
+    <t>شاي (11)</t>
+  </si>
+  <si>
+    <t>لب سوري (22)</t>
+  </si>
+  <si>
+    <t>قهوة (12)</t>
+  </si>
+  <si>
+    <t>نسكافيه (13)</t>
+  </si>
+  <si>
+    <t>عين جمل (25)</t>
+  </si>
+  <si>
+    <t>كاجو (26)</t>
+  </si>
+  <si>
+    <t>شيبسي (27)</t>
+  </si>
+  <si>
+    <t>كولا (16)</t>
+  </si>
+  <si>
+    <t>فشار (28)</t>
+  </si>
+  <si>
+    <t>مياه معدنية (17)</t>
+  </si>
+  <si>
+    <t>مشروب طاقة (18)</t>
+  </si>
+  <si>
+    <t>نعناع (20)</t>
+  </si>
+  <si>
+    <t>قهوة (22)</t>
+  </si>
+  <si>
+    <t>نسكافيه (23)</t>
+  </si>
+  <si>
+    <t>عصير برتقال (24)</t>
+  </si>
+  <si>
+    <t>عصير تفاح (25)</t>
+  </si>
+  <si>
+    <t>كولا (26)</t>
+  </si>
+  <si>
+    <t>مياه معدنية (27)</t>
+  </si>
+  <si>
+    <t>مشروب طاقة (28)</t>
+  </si>
+  <si>
     <t>أرز</t>
   </si>
   <si>
-    <t>عنب (19)</t>
-  </si>
-  <si>
-    <t>عين جمل (15)</t>
+    <t>كاكاو (29)</t>
   </si>
   <si>
     <t>مكرونة</t>
   </si>
   <si>
-    <t>مانجو (20)</t>
-  </si>
-  <si>
-    <t>كاجو (16)</t>
+    <t>نعناع (30)</t>
   </si>
   <si>
     <t>سكر</t>
   </si>
   <si>
-    <t>طماطم (21)</t>
-  </si>
-  <si>
     <t>زيت</t>
   </si>
   <si>
-    <t>شيبسي (17)</t>
-  </si>
-  <si>
     <t>سمنة</t>
   </si>
   <si>
-    <t>فشار (18)</t>
-  </si>
-  <si>
     <t>صلصة</t>
   </si>
   <si>
-    <t>مقرمشات (19)</t>
-  </si>
-  <si>
     <t>تونة</t>
   </si>
   <si>
-    <t>فستق (20)</t>
-  </si>
-  <si>
     <t>فول</t>
   </si>
   <si>
-    <t>خيار (24)</t>
-  </si>
-  <si>
     <t>عدس</t>
   </si>
   <si>
-    <t>لب سوبر (21)</t>
-  </si>
-  <si>
     <t>دقيق</t>
   </si>
   <si>
-    <t>جزر (25)</t>
-  </si>
-  <si>
     <t>أرز (11)</t>
   </si>
   <si>
-    <t>لب سوري (22)</t>
-  </si>
-  <si>
     <t>مكرونة (12)</t>
   </si>
   <si>
-    <t>تفاح (26)</t>
-  </si>
-  <si>
     <t>سكر (13)</t>
   </si>
   <si>
     <t>زيت (14)</t>
   </si>
   <si>
-    <t>نسكافيه</t>
-  </si>
-  <si>
     <t>سمنة (15)</t>
   </si>
   <si>
-    <t>برتقال (28)</t>
-  </si>
-  <si>
-    <t>عين جمل (25)</t>
-  </si>
-  <si>
-    <t>عصير برتقال</t>
-  </si>
-  <si>
     <t>صلصة (16)</t>
   </si>
   <si>
-    <t>كاجو (26)</t>
-  </si>
-  <si>
     <t>تونة (17)</t>
   </si>
   <si>
-    <t>عصير تفاح</t>
-  </si>
-  <si>
-    <t>شيبسي (27)</t>
-  </si>
-  <si>
     <t>فول (18)</t>
   </si>
   <si>
-    <t>مانجو (30)</t>
-  </si>
-  <si>
     <t>عدس (19)</t>
   </si>
   <si>
-    <t>كولا</t>
-  </si>
-  <si>
-    <t>فشار (28)</t>
-  </si>
-  <si>
     <t>دقيق (20)</t>
   </si>
   <si>
-    <t>مياه معدنية</t>
-  </si>
-  <si>
     <t>أرز (21)</t>
   </si>
   <si>
+    <t>مكرونة (22)</t>
+  </si>
+  <si>
+    <t>سكر (23)</t>
+  </si>
+  <si>
+    <t>زيت (24)</t>
+  </si>
+  <si>
+    <t>سمنة (25)</t>
+  </si>
+  <si>
+    <t>صلصة (26)</t>
+  </si>
+  <si>
+    <t>تونة (27)</t>
+  </si>
+  <si>
+    <t>فول (28)</t>
+  </si>
+  <si>
+    <t>عدس (29)</t>
+  </si>
+  <si>
+    <t>دقيق (30)</t>
+  </si>
+  <si>
     <t>فستق (30)</t>
   </si>
   <si>
-    <t>مكرونة (22)</t>
-  </si>
-  <si>
-    <t>كاكاو</t>
-  </si>
-  <si>
-    <t>سكر (23)</t>
-  </si>
-  <si>
-    <t>زيت (24)</t>
-  </si>
-  <si>
-    <t>نعناع</t>
-  </si>
-  <si>
-    <t>شاي (11)</t>
-  </si>
-  <si>
-    <t>سمنة (25)</t>
-  </si>
-  <si>
-    <t>صلصة (26)</t>
-  </si>
-  <si>
-    <t>قهوة (12)</t>
-  </si>
-  <si>
-    <t>تونة (27)</t>
-  </si>
-  <si>
-    <t>نسكافيه (13)</t>
-  </si>
-  <si>
-    <t>فول (28)</t>
-  </si>
-  <si>
-    <t>عدس (29)</t>
-  </si>
-  <si>
-    <t>دقيق (30)</t>
-  </si>
-  <si>
-    <t>كولا (16)</t>
-  </si>
-  <si>
-    <t>مياه معدنية (17)</t>
-  </si>
-  <si>
-    <t>مشروب طاقة (18)</t>
-  </si>
-  <si>
-    <t>نعناع (20)</t>
-  </si>
-  <si>
-    <t>قهوة (22)</t>
-  </si>
-  <si>
-    <t>نسكافيه (23)</t>
-  </si>
-  <si>
-    <t>عصير برتقال (24)</t>
-  </si>
-  <si>
-    <t>عصير تفاح (25)</t>
-  </si>
-  <si>
-    <t>كولا (26)</t>
-  </si>
-  <si>
-    <t>مياه معدنية (27)</t>
-  </si>
-  <si>
-    <t>مشروب طاقة (28)</t>
-  </si>
-  <si>
-    <t>كاكاو (29)</t>
-  </si>
-  <si>
-    <t>نعناع (30)</t>
-  </si>
-  <si>
     <t>لبن كامل الدسم</t>
   </si>
   <si>
@@ -662,222 +662,222 @@
     <t>باتيه</t>
   </si>
   <si>
+    <t>كرواسون</t>
+  </si>
+  <si>
+    <t>بقسماط</t>
+  </si>
+  <si>
+    <t>توست أبيض</t>
+  </si>
+  <si>
     <t>كمون</t>
   </si>
   <si>
-    <t>كرواسون</t>
+    <t>توست أسمر</t>
+  </si>
+  <si>
+    <t>فطير</t>
   </si>
   <si>
     <t>فلفل أسود</t>
   </si>
   <si>
-    <t>بقسماط</t>
+    <t>كيك</t>
   </si>
   <si>
     <t>كركم</t>
   </si>
   <si>
-    <t>توست أبيض</t>
-  </si>
-  <si>
     <t>كزبرة</t>
   </si>
   <si>
-    <t>توست أسمر</t>
+    <t>بسكويت</t>
   </si>
   <si>
     <t>بهارات مشكلة</t>
   </si>
   <si>
-    <t>فطير</t>
+    <t>عيش فينو (11)</t>
   </si>
   <si>
     <t>قرفة</t>
   </si>
   <si>
-    <t>كيك</t>
+    <t>عيش بلدي (12)</t>
   </si>
   <si>
     <t>حبهان</t>
   </si>
   <si>
-    <t>بسكويت</t>
+    <t>باتيه (13)</t>
   </si>
   <si>
     <t>ورق لورا</t>
   </si>
   <si>
-    <t>عيش فينو (11)</t>
+    <t>كرواسون (14)</t>
   </si>
   <si>
     <t>بابريكا</t>
   </si>
   <si>
-    <t>عيش بلدي (12)</t>
-  </si>
-  <si>
     <t>قرنفل</t>
   </si>
   <si>
-    <t>باتيه (13)</t>
+    <t>بقسماط (15)</t>
   </si>
   <si>
     <t>كمون (11)</t>
   </si>
   <si>
-    <t>كرواسون (14)</t>
+    <t>توست أبيض (16)</t>
+  </si>
+  <si>
+    <t>توست أسمر (17)</t>
   </si>
   <si>
     <t>فلفل أسود (12)</t>
   </si>
   <si>
-    <t>بقسماط (15)</t>
+    <t>فطير (18)</t>
   </si>
   <si>
     <t>كركم (13)</t>
   </si>
   <si>
-    <t>توست أبيض (16)</t>
-  </si>
-  <si>
     <t>كزبرة (14)</t>
   </si>
   <si>
-    <t>توست أسمر (17)</t>
+    <t>كيك (19)</t>
   </si>
   <si>
     <t>بهارات مشكلة (15)</t>
   </si>
   <si>
-    <t>فطير (18)</t>
+    <t>بسكويت (20)</t>
   </si>
   <si>
     <t>قرفة (16)</t>
   </si>
   <si>
-    <t>كيك (19)</t>
+    <t>حبهان (17)</t>
+  </si>
+  <si>
+    <t>عيش فينو (21)</t>
+  </si>
+  <si>
+    <t>ورق لورا (18)</t>
+  </si>
+  <si>
+    <t>بابريكا (19)</t>
+  </si>
+  <si>
+    <t>قرنفل (20)</t>
+  </si>
+  <si>
+    <t>عيش بلدي (22)</t>
+  </si>
+  <si>
+    <t>كمون (21)</t>
+  </si>
+  <si>
+    <t>فلفل أسود (22)</t>
+  </si>
+  <si>
+    <t>كركم (23)</t>
+  </si>
+  <si>
+    <t>باتيه (23)</t>
+  </si>
+  <si>
+    <t>كزبرة (24)</t>
+  </si>
+  <si>
+    <t>بهارات مشكلة (25)</t>
+  </si>
+  <si>
+    <t>كرواسون (24)</t>
+  </si>
+  <si>
+    <t>قرفة (26)</t>
+  </si>
+  <si>
+    <t>حبهان (27)</t>
+  </si>
+  <si>
+    <t>ورق لورا (28)</t>
+  </si>
+  <si>
+    <t>بقسماط (25)</t>
+  </si>
+  <si>
+    <t>بابريكا (29)</t>
+  </si>
+  <si>
+    <t>قرنفل (30)</t>
+  </si>
+  <si>
+    <t>توست أبيض (26)</t>
+  </si>
+  <si>
+    <t>توست أسمر (27)</t>
+  </si>
+  <si>
+    <t>فطير (28)</t>
+  </si>
+  <si>
+    <t>كيك (29)</t>
   </si>
   <si>
     <t>شوكولاتة</t>
   </si>
   <si>
-    <t>حبهان (17)</t>
-  </si>
-  <si>
-    <t>بسكويت (20)</t>
-  </si>
-  <si>
-    <t>ورق لورا (18)</t>
+    <t>بسكويت (30)</t>
   </si>
   <si>
     <t>جيلي</t>
   </si>
   <si>
-    <t>عيش فينو (21)</t>
-  </si>
-  <si>
-    <t>بابريكا (19)</t>
-  </si>
-  <si>
     <t>كريم كراميل</t>
   </si>
   <si>
-    <t>عيش بلدي (22)</t>
-  </si>
-  <si>
-    <t>قرنفل (20)</t>
-  </si>
-  <si>
     <t>حلاوة طحينية</t>
   </si>
   <si>
-    <t>باتيه (23)</t>
-  </si>
-  <si>
-    <t>كمون (21)</t>
-  </si>
-  <si>
-    <t>كرواسون (24)</t>
-  </si>
-  <si>
     <t>ملبن</t>
   </si>
   <si>
-    <t>فلفل أسود (22)</t>
-  </si>
-  <si>
-    <t>بقسماط (25)</t>
-  </si>
-  <si>
     <t>بسكويت شيكولاتة</t>
   </si>
   <si>
-    <t>كركم (23)</t>
-  </si>
-  <si>
-    <t>توست أبيض (26)</t>
-  </si>
-  <si>
     <t>لبان</t>
   </si>
   <si>
-    <t>كزبرة (24)</t>
-  </si>
-  <si>
-    <t>توست أسمر (27)</t>
-  </si>
-  <si>
     <t>مربى</t>
   </si>
   <si>
-    <t>بهارات مشكلة (25)</t>
-  </si>
-  <si>
-    <t>فطير (28)</t>
-  </si>
-  <si>
     <t>عسل نحل</t>
   </si>
   <si>
-    <t>كيك (29)</t>
-  </si>
-  <si>
     <t>كيك شوكولاتة</t>
   </si>
   <si>
-    <t>قرفة (26)</t>
-  </si>
-  <si>
-    <t>بسكويت (30)</t>
-  </si>
-  <si>
     <t>شوكولاتة (11)</t>
   </si>
   <si>
-    <t>حبهان (27)</t>
-  </si>
-  <si>
     <t>جيلي (12)</t>
   </si>
   <si>
-    <t>ورق لورا (28)</t>
-  </si>
-  <si>
     <t>كريم كراميل (13)</t>
   </si>
   <si>
-    <t>بابريكا (29)</t>
-  </si>
-  <si>
     <t>حلاوة طحينية (14)</t>
   </si>
   <si>
     <t>ملبن (15)</t>
   </si>
   <si>
-    <t>قرنفل (30)</t>
-  </si>
-  <si>
     <t>بسكويت شيكولاتة (16)</t>
   </si>
   <si>
@@ -890,12 +890,45 @@
     <t>عسل نحل (19)</t>
   </si>
   <si>
+    <t>كيك شوكولاتة (20)</t>
+  </si>
+  <si>
+    <t>شوكولاتة (21)</t>
+  </si>
+  <si>
+    <t>جيلي (22)</t>
+  </si>
+  <si>
+    <t>كريم كراميل (23)</t>
+  </si>
+  <si>
+    <t>حلاوة طحينية (24)</t>
+  </si>
+  <si>
+    <t>ملبن (25)</t>
+  </si>
+  <si>
+    <t>بسكويت شيكولاتة (26)</t>
+  </si>
+  <si>
+    <t>لبان (27)</t>
+  </si>
+  <si>
+    <t>مربى (28)</t>
+  </si>
+  <si>
     <t>مسحوق غسيل</t>
   </si>
   <si>
+    <t>عسل نحل (29)</t>
+  </si>
+  <si>
     <t>صابون سائل</t>
   </si>
   <si>
+    <t>كيك شوكولاتة (30)</t>
+  </si>
+  <si>
     <t>كلور</t>
   </si>
   <si>
@@ -908,82 +941,49 @@
     <t>صابون وجه</t>
   </si>
   <si>
-    <t>كيك شوكولاتة (20)</t>
-  </si>
-  <si>
     <t>شامبو</t>
   </si>
   <si>
     <t>مناديل</t>
   </si>
   <si>
-    <t>شوكولاتة (21)</t>
-  </si>
-  <si>
     <t>سلك مواعين</t>
   </si>
   <si>
     <t>ملمع زجاج</t>
   </si>
   <si>
-    <t>جيلي (22)</t>
-  </si>
-  <si>
     <t>مسحوق غسيل (11)</t>
   </si>
   <si>
-    <t>كريم كراميل (23)</t>
-  </si>
-  <si>
     <t>صابون سائل (12)</t>
   </si>
   <si>
-    <t>حلاوة طحينية (24)</t>
-  </si>
-  <si>
     <t>كلور (13)</t>
   </si>
   <si>
-    <t>ملبن (25)</t>
-  </si>
-  <si>
     <t>معطر جو (14)</t>
   </si>
   <si>
     <t>ديتول (15)</t>
   </si>
   <si>
-    <t>بسكويت شيكولاتة (26)</t>
-  </si>
-  <si>
     <t>صابون وجه (16)</t>
   </si>
   <si>
     <t>شامبو (17)</t>
   </si>
   <si>
-    <t>لبان (27)</t>
-  </si>
-  <si>
     <t>مناديل (18)</t>
   </si>
   <si>
-    <t>مربى (28)</t>
-  </si>
-  <si>
     <t>سلك مواعين (19)</t>
   </si>
   <si>
     <t>ملمع زجاج (20)</t>
   </si>
   <si>
-    <t>عسل نحل (29)</t>
-  </si>
-  <si>
     <t>مسحوق غسيل (21)</t>
-  </si>
-  <si>
-    <t>كيك شوكولاتة (30)</t>
   </si>
   <si>
     <t>صابون سائل (22)</t>
@@ -1351,82 +1351,82 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>16</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>33</v>
+        <v>42</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -2429,22 +2429,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -2455,13 +2455,13 @@
         <v>243.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -2472,13 +2472,13 @@
         <v>228.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -2489,13 +2489,13 @@
         <v>30.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
@@ -2506,13 +2506,13 @@
         <v>199.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
@@ -2523,13 +2523,13 @@
         <v>121.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -2543,10 +2543,10 @@
         <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -2560,13 +2560,13 @@
         <v>39.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -2580,13 +2580,13 @@
         <v>135.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -2597,13 +2597,13 @@
         <v>214.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -2617,10 +2617,10 @@
         <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -2634,13 +2634,13 @@
         <v>124.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -2654,13 +2654,13 @@
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -2671,13 +2671,13 @@
         <v>21.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -2691,13 +2691,13 @@
         <v>141.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -2711,10 +2711,10 @@
         <v>46</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -2731,10 +2731,10 @@
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -2748,13 +2748,13 @@
         <v>66.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -2765,13 +2765,13 @@
         <v>53.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -2782,13 +2782,13 @@
         <v>202.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -2799,13 +2799,13 @@
         <v>65.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -2819,10 +2819,10 @@
         <v>46</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -2836,13 +2836,13 @@
         <v>25.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -2853,13 +2853,13 @@
         <v>165.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -2873,13 +2873,13 @@
         <v>114.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -2893,13 +2893,13 @@
         <v>202.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -2910,13 +2910,13 @@
         <v>24.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -2933,10 +2933,10 @@
         <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -2950,10 +2950,10 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -2964,13 +2964,13 @@
         <v>104.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -2981,13 +2981,13 @@
         <v>59.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -3979,22 +3979,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -4008,10 +4008,10 @@
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -4025,10 +4025,10 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
@@ -4039,52 +4039,52 @@
         <v>91.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B5" s="2">
         <v>66.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B6" s="2">
         <v>51.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B7" s="2">
         <v>198.0</v>
@@ -4093,18 +4093,18 @@
         <v>192.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B8" s="2">
         <v>32.0</v>
@@ -4113,18 +4113,18 @@
         <v>24.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="B9" s="2">
         <v>189.0</v>
@@ -4136,32 +4136,32 @@
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="B10" s="2">
         <v>101.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B11" s="2">
         <v>124.0</v>
@@ -4170,35 +4170,35 @@
         <v>118.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B12" s="2">
         <v>30.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B13" s="2">
         <v>69.0</v>
@@ -4207,18 +4207,18 @@
         <v>60.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B14" s="2">
         <v>140.0</v>
@@ -4227,18 +4227,18 @@
         <v>131.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="B15" s="2">
         <v>216.0</v>
@@ -4247,137 +4247,137 @@
         <v>209.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B16" s="2">
         <v>214.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="B17" s="2">
         <v>108.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="B18" s="2">
         <v>158.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="B19" s="2">
         <v>246.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="B21" s="2">
         <v>99.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="B22" s="2">
         <v>54.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B23" s="2">
         <v>29.0</v>
@@ -4386,18 +4386,18 @@
         <v>21.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B24" s="2">
         <v>135.0</v>
@@ -4406,10 +4406,10 @@
         <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -4426,32 +4426,32 @@
         <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B26" s="2">
         <v>181.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B27" s="2">
         <v>58.0</v>
@@ -4463,15 +4463,15 @@
         <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B28" s="2">
         <v>16.0</v>
@@ -4483,32 +4483,32 @@
         <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="B29" s="2">
         <v>87.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="B30" s="2">
         <v>77.0</v>
@@ -4517,18 +4517,18 @@
         <v>74.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B31" s="2">
         <v>98.0</v>
@@ -4537,13 +4537,13 @@
         <v>91.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -5535,27 +5535,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B2" s="2">
         <v>214.0</v>
@@ -5567,15 +5567,15 @@
         <v>46</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="B3" s="2">
         <v>65.0</v>
@@ -5587,66 +5587,66 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="B4" s="2">
         <v>101.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B5" s="2">
         <v>204.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="B6" s="2">
         <v>56.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="B7" s="2">
         <v>46.0</v>
@@ -5655,18 +5655,18 @@
         <v>41.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="B8" s="2">
         <v>211.0</v>
@@ -5675,52 +5675,52 @@
         <v>204.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="B9" s="2">
         <v>174.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="B10" s="2">
         <v>136.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B11" s="2">
         <v>230.0</v>
@@ -5729,32 +5729,32 @@
         <v>46</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B12" s="2">
         <v>98.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="B13" s="2">
         <v>101.0</v>
@@ -5766,15 +5766,15 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B14" s="2">
         <v>34.0</v>
@@ -5783,52 +5783,52 @@
         <v>25.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B15" s="2">
         <v>58.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B16" s="2">
         <v>100.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B17" s="2">
         <v>144.0</v>
@@ -5837,13 +5837,13 @@
         <v>138.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -5854,13 +5854,13 @@
         <v>104.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -5874,35 +5874,35 @@
         <v>144.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="B20" s="2">
         <v>205.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B21" s="2">
         <v>60.0</v>
@@ -5911,35 +5911,35 @@
         <v>51.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="B22" s="2">
         <v>172.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B23" s="2">
         <v>93.0</v>
@@ -5948,52 +5948,52 @@
         <v>88.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="B24" s="2">
         <v>167.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="B25" s="2">
         <v>126.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
       <c r="B26" s="2">
         <v>250.0</v>
@@ -6002,18 +6002,18 @@
         <v>247.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="B27" s="2">
         <v>118.0</v>
@@ -6025,32 +6025,32 @@
         <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>276</v>
+        <v>259</v>
       </c>
       <c r="B28" s="2">
         <v>62.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>278</v>
+        <v>260</v>
       </c>
       <c r="B29" s="2">
         <v>88.0</v>
@@ -6059,32 +6059,32 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>280</v>
+        <v>262</v>
       </c>
       <c r="B30" s="2">
         <v>18.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="B31" s="2">
         <v>197.0</v>
@@ -6093,10 +6093,10 @@
         <v>46</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -7088,61 +7088,61 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B2" s="2">
         <v>119.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>248</v>
+        <v>270</v>
       </c>
       <c r="B3" s="2">
         <v>144.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="B4" s="2">
         <v>244.0</v>
@@ -7151,52 +7151,52 @@
         <v>234.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B5" s="2">
         <v>28.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="B6" s="2">
         <v>206.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B7" s="2">
         <v>223.0</v>
@@ -7205,18 +7205,18 @@
         <v>220.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="B8" s="2">
         <v>234.0</v>
@@ -7225,86 +7225,86 @@
         <v>230.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
       <c r="B9" s="2">
         <v>87.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
       <c r="B10" s="2">
         <v>147.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B11" s="2">
         <v>141.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B12" s="2">
         <v>152.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B13" s="2">
         <v>124.0</v>
@@ -7313,32 +7313,32 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B14" s="2">
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B15" s="2">
         <v>213.0</v>
@@ -7347,15 +7347,15 @@
         <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B16" s="2">
         <v>167.0</v>
@@ -7364,13 +7364,13 @@
         <v>161.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -7384,10 +7384,10 @@
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -7404,10 +7404,10 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -7418,13 +7418,13 @@
         <v>166.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -7438,66 +7438,66 @@
         <v>46</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>294</v>
+        <v>288</v>
       </c>
       <c r="B21" s="2">
         <v>243.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="B22" s="2">
         <v>224.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="B23" s="2">
         <v>160.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="B24" s="2">
         <v>233.0</v>
@@ -7506,32 +7506,32 @@
         <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>304</v>
+        <v>292</v>
       </c>
       <c r="B25" s="2">
         <v>148.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="B26" s="2">
         <v>195.0</v>
@@ -7540,15 +7540,15 @@
         <v>46</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="B27" s="2">
         <v>194.0</v>
@@ -7557,35 +7557,35 @@
         <v>191.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>312</v>
+        <v>295</v>
       </c>
       <c r="B28" s="2">
         <v>48.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>314</v>
+        <v>296</v>
       </c>
       <c r="B29" s="2">
         <v>237.0</v>
@@ -7594,18 +7594,18 @@
         <v>228.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>317</v>
+        <v>298</v>
       </c>
       <c r="B30" s="2">
         <v>234.0</v>
@@ -7614,18 +7614,18 @@
         <v>228.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>319</v>
+        <v>300</v>
       </c>
       <c r="B31" s="2">
         <v>210.0</v>
@@ -7634,13 +7634,13 @@
         <v>201.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -8632,27 +8632,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="B2" s="2">
         <v>103.0</v>
@@ -8661,18 +8661,18 @@
         <v>101.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B3" s="2">
         <v>46.0</v>
@@ -8681,15 +8681,15 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="B4" s="2">
         <v>54.0</v>
@@ -8698,52 +8698,52 @@
         <v>44.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="B5" s="2">
         <v>26.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="B6" s="2">
         <v>68.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="B7" s="2">
         <v>116.0</v>
@@ -8752,32 +8752,32 @@
         <v>46</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B8" s="2">
         <v>227.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="B9" s="2">
         <v>199.0</v>
@@ -8786,18 +8786,18 @@
         <v>189.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="B10" s="2">
         <v>179.0</v>
@@ -8806,15 +8806,15 @@
         <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="B11" s="2">
         <v>164.0</v>
@@ -8823,18 +8823,18 @@
         <v>157.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B12" s="2">
         <v>60.0</v>
@@ -8843,18 +8843,18 @@
         <v>55.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="B13" s="2">
         <v>54.0</v>
@@ -8863,15 +8863,15 @@
         <v>46</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B14" s="2">
         <v>28.0</v>
@@ -8883,15 +8883,15 @@
         <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="B15" s="2">
         <v>208.0</v>
@@ -8900,49 +8900,49 @@
         <v>46</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="B16" s="2">
         <v>243.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B17" s="2">
         <v>38.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="B18" s="2">
         <v>181.0</v>
@@ -8951,15 +8951,15 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B19" s="2">
         <v>71.0</v>
@@ -8968,35 +8968,35 @@
         <v>61.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B20" s="2">
         <v>240.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B21" s="2">
         <v>195.0</v>
@@ -9005,15 +9005,15 @@
         <v>46</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B22" s="2">
         <v>58.0</v>
@@ -9022,13 +9022,13 @@
         <v>49.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -9042,13 +9042,13 @@
         <v>130.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -9062,10 +9062,10 @@
         <v>46</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -9079,10 +9079,10 @@
         <v>46</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -9093,13 +9093,13 @@
         <v>84.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
@@ -9113,10 +9113,10 @@
         <v>46</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -9130,10 +9130,10 @@
         <v>46</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
@@ -9147,10 +9147,10 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -9161,13 +9161,13 @@
         <v>224.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
@@ -9178,13 +9178,13 @@
         <v>91.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -10178,42 +10178,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -11222,27 +11222,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B2" s="2">
         <v>84.0</v>
@@ -11251,18 +11251,18 @@
         <v>77.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B3" s="2">
         <v>49.0</v>
@@ -11271,18 +11271,18 @@
         <v>40.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B4" s="2">
         <v>136.0</v>
@@ -11291,18 +11291,18 @@
         <v>131.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2">
         <v>171.0</v>
@@ -11311,18 +11311,18 @@
         <v>161.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B6" s="2">
         <v>31.0</v>
@@ -11331,18 +11331,18 @@
         <v>23.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B7" s="2">
         <v>66.0</v>
@@ -11351,13 +11351,13 @@
         <v>60.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -11371,13 +11371,13 @@
         <v>123.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -11394,10 +11394,10 @@
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -11411,13 +11411,13 @@
         <v>98.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -11431,13 +11431,13 @@
         <v>31.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -11451,13 +11451,13 @@
         <v>214.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -11471,13 +11471,13 @@
         <v>145.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -11494,10 +11494,10 @@
         <v>46</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -11511,13 +11511,13 @@
         <v>164.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -11531,13 +11531,13 @@
         <v>86.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
@@ -11551,13 +11551,13 @@
         <v>154.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
@@ -11574,10 +11574,10 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
@@ -11591,13 +11591,13 @@
         <v>37.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -11611,13 +11611,13 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
@@ -11631,13 +11631,13 @@
         <v>175.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -12641,10 +12641,10 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2">
@@ -12652,7 +12652,7 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="3">
@@ -12660,7 +12660,7 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4">
@@ -12668,7 +12668,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>9</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
@@ -12676,7 +12676,7 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>11</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
@@ -12684,7 +12684,7 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>13</v>
+        <v>43</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -14773,22 +14773,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -14799,14 +14799,14 @@
         <v>53.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; (ROW(A1)  &amp; ").png")</f>
-        <v>images/proudect(1).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; (ROW(A1)  &amp; ").png")</f>
+        <v>images/proudect (1).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -14820,37 +14820,37 @@
         <v>87.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(2).png</v>
+        <v>images/proudect (2).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" s="2">
         <v>198.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(3).png</v>
+        <v>images/proudect (3).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B5" s="2">
         <v>84.0</v>
@@ -14859,19 +14859,19 @@
         <v>77.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(4).png</v>
+        <v>images/proudect (4).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B6" s="2">
         <v>249.0</v>
@@ -14884,33 +14884,33 @@
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(5).png</v>
+        <v>images/proudect (5).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B7" s="2">
         <v>181.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(6).png</v>
+        <v>images/proudect (6).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="B8" s="2">
         <v>49.0</v>
@@ -14919,19 +14919,19 @@
         <v>40.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(7).png</v>
+        <v>images/proudect (7).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B9" s="2">
         <v>240.0</v>
@@ -14941,51 +14941,51 @@
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(8).png</v>
+        <v>images/proudect (8).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B10" s="2">
         <v>203.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(9).png</v>
+        <v>images/proudect (9).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B11" s="2">
         <v>109.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(10).png</v>
+        <v>images/proudect (10).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B12" s="2">
         <v>31.0</v>
@@ -14994,19 +14994,19 @@
         <v>24.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(11).png</v>
+        <v>images/proudect (11).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B13" s="2">
         <v>250.0</v>
@@ -15016,33 +15016,33 @@
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(12).png</v>
+        <v>images/proudect (12).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B14" s="2">
         <v>242.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(13).png</v>
+        <v>images/proudect (13).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B15" s="2">
         <v>136.0</v>
@@ -15051,19 +15051,19 @@
         <v>131.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(14).png</v>
+        <v>images/proudect (14).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B16" s="2">
         <v>85.0</v>
@@ -15073,69 +15073,69 @@
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(15).png</v>
+        <v>images/proudect (15).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="B17" s="2">
         <v>184.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(16).png</v>
+        <v>images/proudect (16).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B18" s="2">
         <v>23.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(17).png</v>
+        <v>images/proudect (17).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B19" s="2">
         <v>52.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(18).png</v>
+        <v>images/proudect (18).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B20" s="2">
         <v>151.0</v>
@@ -15145,15 +15145,15 @@
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(19).png</v>
+        <v>images/proudect (19).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B21" s="2">
         <v>32.0</v>
@@ -15163,33 +15163,33 @@
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(20).png</v>
+        <v>images/proudect (20).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B22" s="2">
         <v>144.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(21).png</v>
+        <v>images/proudect (21).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2">
         <v>171.0</v>
@@ -15198,19 +15198,19 @@
         <v>161.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(22).png</v>
+        <v>images/proudect (22).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B24" s="2">
         <v>31.0</v>
@@ -15219,73 +15219,73 @@
         <v>23.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(23).png</v>
+        <v>images/proudect (23).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B25" s="2">
         <v>41.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(24).png</v>
+        <v>images/proudect (24).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B26" s="2">
         <v>170.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(25).png</v>
+        <v>images/proudect (25).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="B27" s="2">
         <v>199.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(26).png</v>
+        <v>images/proudect (26).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B28" s="2">
         <v>66.0</v>
@@ -15294,19 +15294,19 @@
         <v>60.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(27).png</v>
+        <v>images/proudect (27).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B29" s="2">
         <v>208.0</v>
@@ -15316,10 +15316,10 @@
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(28).png</v>
+        <v>images/proudect (28).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -15333,32 +15333,32 @@
         <v>123.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(29).png</v>
+        <v>images/proudect (29).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>144</v>
+        <v>124</v>
       </c>
       <c r="B31" s="2">
         <v>96.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(30).png</v>
+        <v>images/proudect (30).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -16356,22 +16356,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
@@ -16388,11 +16388,11 @@
         <v>46</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f>"images/proudect(" &amp; ROW(A31) &amp; ").png"</f>
-        <v>images/proudect(31).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; ROW(A31) &amp; ").png"</f>
+        <v>images/proudect (31).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -16403,68 +16403,68 @@
         <v>151.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" s="2" t="str">
-        <f t="shared" ref="E3:E6" si="1">"images/proudect(" &amp; (ROW(A31) &amp; ").png")</f>
-        <v>images/proudect(31).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (32).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B4" s="2">
         <v>17.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(32).png</v>
+        <v>images/proudect (33).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" s="2">
         <v>175.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(33).png</v>
+        <v>images/proudect (34).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B6" s="2">
         <v>32.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(34).png</v>
+        <v>images/proudect (35).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -16475,14 +16475,14 @@
         <v>215.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E7" s="2" t="str">
-        <f t="shared" ref="E7:E31" si="2">"images/proudect(" &amp; (ROW(A6) + 30) &amp; ").png"</f>
-        <v>images/proudect(36).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (36).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
@@ -16496,32 +16496,32 @@
         <v>98.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E8" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(37).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (37).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B9" s="2">
         <v>72.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(38).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (38).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
@@ -16535,14 +16535,14 @@
         <v>31.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E10" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(39).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (39).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
@@ -16553,14 +16553,14 @@
         <v>187.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E11" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(40).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (40).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
@@ -16571,14 +16571,14 @@
         <v>125.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E12" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(41).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (41).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
@@ -16589,14 +16589,14 @@
         <v>80.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E13" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(42).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (42).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
@@ -16610,37 +16610,37 @@
         <v>214.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(43).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (43).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="B15" s="2">
         <v>231.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E15" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(44).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (44).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="B16" s="2">
         <v>201.0</v>
@@ -16649,106 +16649,106 @@
         <v>46</v>
       </c>
       <c r="E16" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(45).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (45).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B17" s="2">
         <v>162.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(46).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (46).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B18" s="2">
         <v>42.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(47).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (47).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="B19" s="2">
         <v>33.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(48).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (48).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="B20" s="2">
         <v>87.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E20" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(49).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (49).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="B21" s="2">
         <v>110.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E21" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(50).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (50).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B22" s="2">
         <v>69.0</v>
@@ -16760,11 +16760,11 @@
         <v>46</v>
       </c>
       <c r="E22" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(51).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (51).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
@@ -16775,14 +16775,14 @@
         <v>199.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E23" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(52).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (52).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -16796,14 +16796,14 @@
         <v>145.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E24" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(53).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (53).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
@@ -16820,16 +16820,16 @@
         <v>46</v>
       </c>
       <c r="E25" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(54).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (54).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="B26" s="2">
         <v>84.0</v>
@@ -16841,52 +16841,52 @@
         <v>46</v>
       </c>
       <c r="E26" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(55).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (55).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>132</v>
       </c>
       <c r="B27" s="2">
         <v>119.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(56).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (56).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>133</v>
       </c>
       <c r="B28" s="2">
         <v>110.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E28" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(57).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (57).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="B29" s="2">
         <v>212.0</v>
@@ -16895,11 +16895,11 @@
         <v>46</v>
       </c>
       <c r="E29" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(58).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (58).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -16913,32 +16913,32 @@
         <v>164.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(59).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (59).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>151</v>
+        <v>178</v>
       </c>
       <c r="B31" s="2">
         <v>147.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2" t="str">
-        <f t="shared" si="2"/>
-        <v>images/proudect(60).png</v>
+        <f t="shared" si="1"/>
+        <v>images/proudect (60).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -17936,27 +17936,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="B2" s="2">
         <v>189.0</v>
@@ -17965,14 +17965,14 @@
         <v>179.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="str">
-        <f t="shared" ref="E2:E31" si="1">"images/proudect(" &amp; ROW(A61) &amp; ").png"</f>
-        <v>images/proudect(61).png</v>
+        <f t="shared" ref="E2:E31" si="1">"images/proudect (" &amp; ROW(A61) &amp; ").png"</f>
+        <v>images/proudect (61).png</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -17986,104 +17986,104 @@
         <v>86.0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E3" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(62).png</v>
+        <v>images/proudect (62).png</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="B4" s="2">
         <v>105.0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E4" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(63).png</v>
+        <v>images/proudect (63).png</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="B5" s="2">
         <v>25.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E5" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(64).png</v>
+        <v>images/proudect (64).png</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>141</v>
+        <v>110</v>
       </c>
       <c r="B6" s="2">
         <v>49.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E6" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(65).png</v>
+        <v>images/proudect (65).png</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="B7" s="2">
         <v>47.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E7" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(66).png</v>
+        <v>images/proudect (66).png</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>149</v>
+        <v>116</v>
       </c>
       <c r="B8" s="2">
         <v>164.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(67).png</v>
+        <v>images/proudect (67).png</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
@@ -18097,104 +18097,104 @@
         <v>154.0</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E9" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(68).png</v>
+        <v>images/proudect (68).png</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>153</v>
+        <v>122</v>
       </c>
       <c r="B10" s="2">
         <v>124.0</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(69).png</v>
+        <v>images/proudect (69).png</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>156</v>
+        <v>125</v>
       </c>
       <c r="B11" s="2">
         <v>66.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(70).png</v>
+        <v>images/proudect (70).png</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="B12" s="2">
         <v>38.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(71).png</v>
+        <v>images/proudect (71).png</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>160</v>
+        <v>129</v>
       </c>
       <c r="B13" s="2">
         <v>116.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(72).png</v>
+        <v>images/proudect (72).png</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>162</v>
+        <v>130</v>
       </c>
       <c r="B14" s="2">
         <v>73.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E14" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(73).png</v>
+        <v>images/proudect (73).png</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
@@ -18212,10 +18212,10 @@
       </c>
       <c r="E15" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(74).png</v>
+        <v>images/proudect (74).png</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
@@ -18229,68 +18229,68 @@
         <v>37.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E16" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(75).png</v>
+        <v>images/proudect (75).png</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>166</v>
+        <v>134</v>
       </c>
       <c r="B17" s="2">
         <v>98.0</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E17" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(76).png</v>
+        <v>images/proudect (76).png</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>167</v>
+        <v>136</v>
       </c>
       <c r="B18" s="2">
         <v>40.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E18" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(77).png</v>
+        <v>images/proudect (77).png</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>168</v>
+        <v>137</v>
       </c>
       <c r="B19" s="2">
         <v>53.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E19" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(78).png</v>
+        <v>images/proudect (78).png</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
@@ -18304,32 +18304,32 @@
         <v>145.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(79).png</v>
+        <v>images/proudect (79).png</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="B21" s="2">
         <v>157.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(80).png</v>
+        <v>images/proudect (80).png</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
@@ -18343,19 +18343,19 @@
         <v>175.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E22" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(81).png</v>
+        <v>images/proudect (81).png</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="B23" s="2">
         <v>38.0</v>
@@ -18368,15 +18368,15 @@
       </c>
       <c r="E23" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(82).png</v>
+        <v>images/proudect (82).png</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="B24" s="2">
         <v>206.0</v>
@@ -18386,51 +18386,51 @@
       </c>
       <c r="E24" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(83).png</v>
+        <v>images/proudect (83).png</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>172</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2">
         <v>39.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E25" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(84).png</v>
+        <v>images/proudect (84).png</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>173</v>
+        <v>142</v>
       </c>
       <c r="B26" s="2">
         <v>130.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E26" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(85).png</v>
+        <v>images/proudect (85).png</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>174</v>
+        <v>143</v>
       </c>
       <c r="B27" s="2">
         <v>145.0</v>
@@ -18440,15 +18440,15 @@
       </c>
       <c r="E27" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(86).png</v>
+        <v>images/proudect (86).png</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>175</v>
+        <v>144</v>
       </c>
       <c r="B28" s="2">
         <v>75.0</v>
@@ -18457,55 +18457,55 @@
         <v>68.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E28" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(87).png</v>
+        <v>images/proudect (87).png</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>176</v>
+        <v>145</v>
       </c>
       <c r="B29" s="2">
         <v>221.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E29" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(88).png</v>
+        <v>images/proudect (88).png</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="B30" s="2">
         <v>122.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E30" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(89).png</v>
+        <v>images/proudect (89).png</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="B31" s="2">
         <v>34.0</v>
@@ -18514,14 +18514,14 @@
         <v>25.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E31" s="2" t="str">
         <f t="shared" si="1"/>
-        <v>images/proudect(90).png</v>
+        <v>images/proudect (90).png</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
@@ -19513,44 +19513,44 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>146</v>
       </c>
       <c r="B2" s="2">
         <v>161.0</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="B3" s="2">
         <v>62.0</v>
@@ -19562,15 +19562,15 @@
         <v>46</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="B4" s="2">
         <v>164.0</v>
@@ -19582,83 +19582,83 @@
         <v>46</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>113</v>
+        <v>151</v>
       </c>
       <c r="B5" s="2">
         <v>91.0</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="B6" s="2">
         <v>120.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>117</v>
+        <v>153</v>
       </c>
       <c r="B7" s="2">
         <v>240.0</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>119</v>
+        <v>154</v>
       </c>
       <c r="B8" s="2">
         <v>68.0</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>121</v>
+        <v>155</v>
       </c>
       <c r="B9" s="2">
         <v>40.0</v>
@@ -19667,15 +19667,15 @@
         <v>46</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>123</v>
+        <v>156</v>
       </c>
       <c r="B10" s="2">
         <v>137.0</v>
@@ -19684,66 +19684,66 @@
         <v>46</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="B11" s="2">
         <v>51.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>127</v>
+        <v>158</v>
       </c>
       <c r="B12" s="2">
         <v>211.0</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>129</v>
+        <v>159</v>
       </c>
       <c r="B13" s="2">
         <v>236.0</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>131</v>
+        <v>160</v>
       </c>
       <c r="B14" s="2">
         <v>69.0</v>
@@ -19752,18 +19752,18 @@
         <v>64.0</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>132</v>
+        <v>161</v>
       </c>
       <c r="B15" s="2">
         <v>78.0</v>
@@ -19772,35 +19772,35 @@
         <v>69.0</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>134</v>
+        <v>162</v>
       </c>
       <c r="B16" s="2">
         <v>231.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>138</v>
+        <v>163</v>
       </c>
       <c r="B17" s="2">
         <v>155.0</v>
@@ -19809,15 +19809,15 @@
         <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>140</v>
+        <v>164</v>
       </c>
       <c r="B18" s="2">
         <v>156.0</v>
@@ -19826,66 +19826,66 @@
         <v>46</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>143</v>
+        <v>165</v>
       </c>
       <c r="B19" s="2">
         <v>168.0</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="B20" s="2">
         <v>70.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>148</v>
+        <v>167</v>
       </c>
       <c r="B21" s="2">
         <v>136.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B22" s="2">
         <v>125.0</v>
@@ -19894,18 +19894,18 @@
         <v>119.0</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B23" s="2">
         <v>135.0</v>
@@ -19914,15 +19914,15 @@
         <v>46</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="B24" s="2">
         <v>250.0</v>
@@ -19931,69 +19931,69 @@
         <v>244.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="B25" s="2">
         <v>83.0</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="B26" s="2">
         <v>117.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="B27" s="2">
         <v>240.0</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="B28" s="2">
         <v>174.0</v>
@@ -20002,35 +20002,35 @@
         <v>165.0</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>34</v>
+        <v>14</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>163</v>
+        <v>175</v>
       </c>
       <c r="B29" s="2">
         <v>152.0</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="B30" s="2">
         <v>162.0</v>
@@ -20039,30 +20039,30 @@
         <v>152.0</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="B31" s="2">
         <v>189.0</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>36</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1"/>
